--- a/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3D-道具" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="3D-物品" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="域变更日志" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -1495,22 +1495,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="51">
       <c r="A6" s="56">
-        <f>COUNTA('资产主表'!$A$6:$A$25)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$26)</f>
         <v/>
       </c>
       <c r="B6" s="54" t="n"/>
       <c r="C6" s="56">
-        <f>COUNTIF('资产主表'!$K$6:$K$25,"已完成")+COUNTIF('资产主表'!$K$6:$K$25,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$25,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$25,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$25,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$25,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$25,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$26,"已完成")+COUNTIF('资产主表'!$K$6:$K$26,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$26,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$26,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$26,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$26,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$26,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="54" t="n"/>
       <c r="E6" s="56">
-        <f>COUNTIF('资产主表'!$K$6:$K$25,"待制作")+COUNTIF('资产主表'!$K$6:$K$25,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$26,"待制作")+COUNTIF('资产主表'!$K$6:$K$26,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="54" t="n"/>
       <c r="G6" s="56">
-        <f>COUNTIF('资产主表'!$S$6:$S$25,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$26,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="54" t="n"/>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B10" s="61">
-        <f>COUNTIF('资产主表'!$C$6:$C$25,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$26,A10)</f>
         <v/>
       </c>
       <c r="C10" s="61">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$25=A10)*(('资产主表'!$K$6:$K$25="已完成")+('资产主表'!$K$6:$K$25="原型已接入")+('资产主表'!$K$6:$K$25="正式美术已接入")+('资产主表'!$K$6:$K$25="已优化并正式接入")+('资产主表'!$K$6:$K$25="Blender源已完成")+('资产主表'!$K$6:$K$25="已导入；优化完成")+('资产主表'!$K$6:$K$25="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$26=A10)*(('资产主表'!$K$6:$K$26="已完成")+('资产主表'!$K$6:$K$26="原型已接入")+('资产主表'!$K$6:$K$26="正式美术已接入")+('资产主表'!$K$6:$K$26="已优化并正式接入")+('资产主表'!$K$6:$K$26="Blender源已完成")+('资产主表'!$K$6:$K$26="已导入；优化完成")+('资产主表'!$K$6:$K$26="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="61" t="n"/>
@@ -1601,11 +1601,11 @@
         </is>
       </c>
       <c r="B11" s="57">
-        <f>COUNTIF('资产主表'!$C$6:$C$25,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$26,A11)</f>
         <v/>
       </c>
       <c r="C11" s="57">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$25=A11)*(('资产主表'!$K$6:$K$25="已完成")+('资产主表'!$K$6:$K$25="原型已接入")+('资产主表'!$K$6:$K$25="正式美术已接入")+('资产主表'!$K$6:$K$25="已优化并正式接入")+('资产主表'!$K$6:$K$25="Blender源已完成")+('资产主表'!$K$6:$K$25="已导入；优化完成")+('资产主表'!$K$6:$K$25="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$26=A11)*(('资产主表'!$K$6:$K$26="已完成")+('资产主表'!$K$6:$K$26="原型已接入")+('资产主表'!$K$6:$K$26="正式美术已接入")+('资产主表'!$K$6:$K$26="已优化并正式接入")+('资产主表'!$K$6:$K$26="Blender源已完成")+('资产主表'!$K$6:$K$26="已导入；优化完成")+('资产主表'!$K$6:$K$26="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="57" t="n"/>
@@ -2173,7 +2173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="50" min="1" max="1"/>
@@ -2449,7 +2449,7 @@
         <v/>
       </c>
       <c r="S6" s="62">
-        <f>IF(COUNTIF($R$6:$R$25,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="62" t="n"/>
@@ -2552,7 +2552,7 @@
         <v/>
       </c>
       <c r="S7" s="62">
-        <f>IF(COUNTIF($R$6:$R$25,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="62" t="n"/>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="S8" s="62">
-        <f>IF(COUNTIF($R$6:$R$25,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="62" t="n"/>
@@ -2758,7 +2758,7 @@
         <v/>
       </c>
       <c r="S9" s="62">
-        <f>IF(COUNTIF($R$6:$R$25,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="62" t="n"/>
@@ -2865,7 +2865,7 @@
         <v/>
       </c>
       <c r="S10" s="62">
-        <f>IF(COUNTIF($R$6:$R$25,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="75" t="inlineStr">
@@ -2982,7 +2982,7 @@
         <v/>
       </c>
       <c r="S11" s="62">
-        <f>IF(COUNTIF($R$6:$R$25,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="75" t="inlineStr">
@@ -3103,7 +3103,7 @@
         <v/>
       </c>
       <c r="S12" s="62">
-        <f>IF(COUNTIF($R$6:$R$25,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="75" t="inlineStr">
@@ -3224,7 +3224,7 @@
         <v/>
       </c>
       <c r="S13" s="62">
-        <f>IF(COUNTIF($R$6:$R$25,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="75" t="inlineStr">
@@ -3341,7 +3341,7 @@
         <v/>
       </c>
       <c r="S14" s="54">
-        <f>IF(COUNTIF($R$6:$R$25,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="78" t="n"/>
@@ -3460,7 +3460,7 @@
         <v/>
       </c>
       <c r="S15" s="80">
-        <f>IF(COUNTIF($R$6:$R$25,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="81" t="inlineStr">
@@ -3586,7 +3586,7 @@
         <v/>
       </c>
       <c r="S16" s="80">
-        <f>IF(COUNTIF($R$6:$R$25,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="81" t="inlineStr">
@@ -3712,7 +3712,7 @@
         <v/>
       </c>
       <c r="S17" s="80">
-        <f>IF(COUNTIF($R$6:$R$25,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="81" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="I18" s="81" t="inlineStr">
         <is>
-          <t>default / 独立装饰场景</t>
+          <t>default / pushable / seated / swivel / driveable</t>
         </is>
       </c>
       <c r="J18" s="80" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="M18" s="81" t="inlineStr">
         <is>
-          <t>v001</t>
+          <t>v004</t>
         </is>
       </c>
       <c r="N18" s="80" t="inlineStr">
         <is>
-          <t>最多4材质；独立GLB/PackedScene；无交互碰撞</t>
+          <t>分体座面旋转与轮脚底座滑行；乘坐限速=角色步速1.3倍；松手惯性衰减；离座防弹射；实体场景碰撞</t>
         </is>
       </c>
       <c r="O18" s="81" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="P18" s="81" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/workshop_stool/prp_base_workshop_stool_source_v001.blend</t>
+          <t>assets/art/props/base_world_3d/source/workshop_stool/prp_base_workshop_stool_source_v004.blend; assets/art/props/base_world_3d/components/workshop_stool/prp_base_workshop_stool_base_visual_v004.glb; assets/art/props/base_world_3d/components/workshop_stool/prp_base_workshop_stool_swivel_visual_v004.glb</t>
         </is>
       </c>
       <c r="Q18" s="81" t="inlineStr">
@@ -3834,12 +3834,12 @@
         <v/>
       </c>
       <c r="S18" s="80">
-        <f>IF(COUNTIF($R$6:$R$25,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="81" t="inlineStr">
         <is>
-          <t>4554304e33b3d714e76ee1cf4c0d5bac5f4c08ef499f5a2c84ad59e69ef5a3fe</t>
+          <t>ca07e39e57a6509a659f70cc245b20295cf1bb9ecd381841df0836d729235804</t>
         </is>
       </c>
       <c r="U18" s="81" t="inlineStr">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="V18" s="82" t="n">
-        <v>46264</v>
+        <v>46294</v>
       </c>
       <c r="W18" s="80" t="inlineStr">
         <is>
@@ -3864,7 +3864,10 @@
         <is>
           <t>已从对应设施主体拆出；在场景装饰集合中独立摆放，不绑定facility_id。
 2026-08-30 AST-01规范化（原制作状态：正式美术已接入；原大类：3D道具）
-2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_base_facility_framework；verify_base_facility_interaction_zones；SHA a09164b2f643→24c43b83564e。</t>
+2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_base_facility_framework；verify_base_facility_interaction_zones；SHA a09164b2f643→24c43b83564e。
+2026-09-29：99F 基地座椅接入 PushableSeat3D，角色碰撞可推动；E 上下座，方向输入通过刚体受力滑行；场景墙/地面碰撞保留，安全下座查询；verify_pushable_base_chairs 通过。
+2026-09-29：维修圆凳 v004 从 v003 Blender 源分离旋转上部与滑行底座，GLB 双件；角色碰撞改走独立 PlayerBlocker 代理以消除离座刚体弹射。乘坐速度=玩家步速×1.3，松手后短距滑行并衰减；Godot 物理回归通过。
+2026-09-29：v004 分体 GLB 导入设置补回设施共享色盘后处理；99F 实例验证底座和旋转上部均绑定色盘；离座碰撞与镜头回归通过。</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3910,7 @@
       </c>
       <c r="I19" s="81" t="inlineStr">
         <is>
-          <t>default / 独立装饰场景</t>
+          <t>default / pushable / seated / swivel / driveable</t>
         </is>
       </c>
       <c r="J19" s="80" t="inlineStr">
@@ -3927,12 +3930,12 @@
       </c>
       <c r="M19" s="81" t="inlineStr">
         <is>
-          <t>v001</t>
+          <t>v004</t>
         </is>
       </c>
       <c r="N19" s="80" t="inlineStr">
         <is>
-          <t>最多4材质；独立GLB/PackedScene；无交互碰撞</t>
+          <t>分体座面旋转与轮脚底座滑行；乘坐限速=角色步速1.3倍；松手惯性衰减；离座防弹射；实体场景碰撞</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -3942,7 +3945,7 @@
       </c>
       <c r="P19" s="81" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/mission_command_chair/prp_base_mission_command_chair_source_v001.blend</t>
+          <t>assets/art/props/base_world_3d/source/mission_command_chair/prp_base_mission_command_chair_source_v004.blend; assets/art/props/base_world_3d/components/mission_command_chair/prp_base_mission_command_chair_base_visual_v004.glb; assets/art/props/base_world_3d/components/mission_command_chair/prp_base_mission_command_chair_swivel_visual_v004.glb</t>
         </is>
       </c>
       <c r="Q19" s="81" t="inlineStr">
@@ -3955,12 +3958,12 @@
         <v/>
       </c>
       <c r="S19" s="80">
-        <f>IF(COUNTIF($R$6:$R$25,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="81" t="inlineStr">
         <is>
-          <t>ce1fbe01d87b8b1fae06f225cf4c85846ab4f38d76ddca097ead78315248df76</t>
+          <t>b8920a3b2ad4142208d2b6ae79107bc55d5e744c346acf5376ccc14a908bc537</t>
         </is>
       </c>
       <c r="U19" s="81" t="inlineStr">
@@ -3969,7 +3972,7 @@
         </is>
       </c>
       <c r="V19" s="82" t="n">
-        <v>46264</v>
+        <v>46294</v>
       </c>
       <c r="W19" s="80" t="inlineStr">
         <is>
@@ -3985,7 +3988,10 @@
         <is>
           <t>已从对应设施主体拆出；在场景装饰集合中独立摆放，不绑定facility_id。
 2026-08-30 AST-01规范化（原制作状态：正式美术已接入；原大类：3D道具）
-2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_base_facility_framework；verify_base_facility_interaction_zones；SHA f16271a4dc23→a8c70158f3af。</t>
+2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_base_facility_framework；verify_base_facility_interaction_zones；SHA f16271a4dc23→a8c70158f3af。
+2026-09-29：99F 基地座椅接入 PushableSeat3D，角色碰撞可推动；E 上下座，方向输入通过刚体受力滑行；场景墙/地面碰撞保留，安全下座查询；verify_pushable_base_chairs 通过。
+2026-09-29：战术指挥椅 v004 从 v003 Blender 源分离旋转上部与滑行底座，GLB 双件；角色碰撞改走独立 PlayerBlocker 代理以消除离座刚体弹射。乘坐速度=玩家步速×1.3，松手后短距滑行并衰减；Godot 物理回归通过。
+2026-09-29：v004 分体 GLB 导入设置补回设施共享色盘后处理；99F 实例验证底座和旋转上部均绑定色盘；离座碰撞与镜头回归通过。</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4086,7 @@
         <v/>
       </c>
       <c r="S20" s="50">
-        <f>IF(COUNTIF($R$6:$R$25,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="83" t="inlineStr">
@@ -4203,7 +4209,7 @@
         <v/>
       </c>
       <c r="S21" s="50">
-        <f>IF(COUNTIF($R$6:$R$25,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="83" t="inlineStr">
@@ -4326,7 +4332,7 @@
         <v/>
       </c>
       <c r="S22" s="50">
-        <f>IF(COUNTIF($R$6:$R$25,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="83" t="inlineStr">
@@ -4449,7 +4455,7 @@
         <v/>
       </c>
       <c r="S23" s="50">
-        <f>IF(COUNTIF($R$6:$R$25,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="83" t="inlineStr">
@@ -4572,7 +4578,7 @@
         <v/>
       </c>
       <c r="S24" s="50">
-        <f>IF(COUNTIF($R$6:$R$25,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="83" t="inlineStr">
@@ -4695,7 +4701,7 @@
         <v/>
       </c>
       <c r="S25" s="50">
-        <f>IF(COUNTIF($R$6:$R$25,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$26,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="83" t="inlineStr">
@@ -4724,6 +4730,125 @@
       <c r="Y25" s="83" t="inlineStr">
         <is>
           <t>2026-09-12：TowerDescent99F的avatar_wardrobe迁移到36_墨绿三人休闲沙发_资产包；包装场景保持源包世界坐标与碰撞，打开WardrobeMenu3D，交互区锁定为源包碰撞包围盒+0.8m。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="410.4" customHeight="1" s="51">
+      <c r="A26" s="79" t="inlineStr">
+        <is>
+          <t>PRP-BASE99-TELESCOPIC-LADDER-3D</t>
+        </is>
+      </c>
+      <c r="B26" s="80" t="inlineStr">
+        <is>
+          <t>99F东阁楼双段伸缩直梯</t>
+        </is>
+      </c>
+      <c r="C26" s="80" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D26" s="81" t="inlineStr">
+        <is>
+          <t>decor_prop</t>
+        </is>
+      </c>
+      <c r="E26" s="81" t="inlineStr">
+        <is>
+          <t>base99_rooftop_telescopic_ladder</t>
+        </is>
+      </c>
+      <c r="F26" s="81" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="G26" s="80" t="n"/>
+      <c r="H26" s="81" t="inlineStr">
+        <is>
+          <t>Top3D / 固定位置</t>
+        </is>
+      </c>
+      <c r="I26" s="81" t="inlineStr">
+        <is>
+          <t>retracted / deploying / deployed / climbing</t>
+        </is>
+      </c>
+      <c r="J26" s="80" t="inlineStr">
+        <is>
+          <t>TowerDescent99F / base100_rooftop</t>
+        </is>
+      </c>
+      <c r="K26" s="80" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L26" s="81" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M26" s="81" t="inlineStr">
+        <is>
+          <t>v002</t>
+        </is>
+      </c>
+      <c r="N26" s="80" t="inlineStr">
+        <is>
+          <t>双段6m直梯；上端E放下；展开后两端E自动攀爬、反向输入折返；顶部穿东门至100F平台、底部落99F阁楼；场景实体碰撞；展开状态存档</t>
+        </is>
+      </c>
+      <c r="O26" s="81" t="inlineStr">
+        <is>
+          <t>assets/art/props/base_world_3d/runtime/base99_telescopic_ladder/prp_base99_telescopic_ladder_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P26" s="81" t="inlineStr">
+        <is>
+          <t>assets/art/props/base_world_3d/source/base99_telescopic_ladder/prp_base99_telescopic_ladder_source_v002.blend; assets/art/props/base_world_3d/components/base99_telescopic_ladder/prp_base99_telescopic_ladder_upper_visual_top3d.glb; assets/art/props/base_world_3d/components/base99_telescopic_ladder/prp_base99_telescopic_ladder_lower_visual_top3d.glb; src/base3d/Base99TelescopicLadder3D.gd; src/player3d/states/Player3DClimbingState.gd</t>
+        </is>
+      </c>
+      <c r="Q26" s="81" t="inlineStr">
+        <is>
+          <t>99F;100F;伸缩直梯;可使用道具;攀爬;双段梯</t>
+        </is>
+      </c>
+      <c r="R26" s="80">
+        <f>LOWER(TRIM(C26)&amp;"|"&amp;TRIM(D26)&amp;"|"&amp;TRIM(E26)&amp;"|"&amp;TRIM(F26)&amp;"|"&amp;TRIM(H26)&amp;"|"&amp;TRIM(I26))</f>
+        <v/>
+      </c>
+      <c r="S26" s="80">
+        <f>IF(COUNTIF($R$6:$R$26,R26)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T26" s="81" t="inlineStr">
+        <is>
+          <t>26a53eee81db5dd6f5ce6a0dc7fe80b8de20044d64a7948b643adf503af98e83</t>
+        </is>
+      </c>
+      <c r="U26" s="81" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V26" s="82" t="n">
+        <v>46294</v>
+      </c>
+      <c r="W26" s="80" t="inlineStr">
+        <is>
+          <t>用户指定Blender资产</t>
+        </is>
+      </c>
+      <c r="X26" s="77" t="inlineStr">
+        <is>
+          <t>99F-100F-EAST-LADDER</t>
+        </is>
+      </c>
+      <c r="Y26" s="80" t="inlineStr">
+        <is>
+          <t>2026-09-29：梯子贴合99F东墙并朝向阁楼；上端跨东门落100F平台。Blender v002 直接复用基地母版的四种既有材质，不新增或调整材质参数。展开一次后永久保持并写入基地存档。</t>
         </is>
       </c>
     </row>
@@ -4935,7 +5060,7 @@
     <row r="427" ht="84.75" customHeight="1" s="51"/>
     <row r="429" ht="120" customHeight="1" s="51"/>
   </sheetData>
-  <autoFilter ref="A5:X25"/>
+  <autoFilter ref="A5:X26"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
@@ -4954,15 +5079,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="C6:C26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K6:K25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="K6:K26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L6:L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="L6:L26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5016,7 +5141,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="51">
       <c r="A4" s="86" t="inlineStr">
         <is>
@@ -5394,7 +5518,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="51">
       <c r="A4" s="86" t="inlineStr">
         <is>
@@ -5508,7 +5631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="50" min="1" max="1"/>
@@ -5609,6 +5732,154 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.1</t>
+        </is>
+      </c>
+      <c r="B7" s="68" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C7" s="61" t="inlineStr">
+        <is>
+          <t>99F座椅乘坐与驾驶</t>
+        </is>
+      </c>
+      <c r="D7" s="61" t="inlineStr">
+        <is>
+          <t>道具 / 基地座椅</t>
+        </is>
+      </c>
+      <c r="E7" s="61" t="inlineStr">
+        <is>
+          <t>维修圆凳与战术指挥椅改为可推刚体、可乘坐驾驶；与场景碰撞交互。</t>
+        </is>
+      </c>
+      <c r="F7" s="61" t="inlineStr">
+        <is>
+          <t>更新两条既有资产的状态、规格、v003 源、SHA、备注和日期；AssetID 与运行时路径不变。</t>
+        </is>
+      </c>
+      <c r="G7" s="61" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.2</t>
+        </is>
+      </c>
+      <c r="B8" s="68" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C8" s="61" t="inlineStr">
+        <is>
+          <t>99F旋转椅分体与离座防弹射</t>
+        </is>
+      </c>
+      <c r="D8" s="61" t="inlineStr">
+        <is>
+          <t>道具 / 基地座椅</t>
+        </is>
+      </c>
+      <c r="E8" s="61" t="inlineStr">
+        <is>
+          <t>两把椅子从 v003 源派生 v004；轮脚底座物理滑行、座面/靠背独立转向；乘坐1.3倍步速与松手惯性。</t>
+        </is>
+      </c>
+      <c r="F8" s="61" t="inlineStr">
+        <is>
+          <t>更新两条既有资产的版本、双GLB来源、物理规格、SHA与备注；AssetID和运行时PackedScene路径不变。</t>
+        </is>
+      </c>
+      <c r="G8" s="61" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.3</t>
+        </is>
+      </c>
+      <c r="B9" s="68" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C9" s="61" t="inlineStr">
+        <is>
+          <t>99F座椅材质与上下座回归</t>
+        </is>
+      </c>
+      <c r="D9" s="61" t="inlineStr">
+        <is>
+          <t>道具 / 基地座椅</t>
+        </is>
+      </c>
+      <c r="E9" s="61" t="inlineStr">
+        <is>
+          <t>两把椅子的分体视觉恢复共享材质；验证上下座碰撞、镜头高度及座中射击。</t>
+        </is>
+      </c>
+      <c r="F9" s="61" t="inlineStr">
+        <is>
+          <t>更新既有资产记录与验收契约；保留 AssetID 和稳定 PackedScene 路径。</t>
+        </is>
+      </c>
+      <c r="G9" s="61" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.4</t>
+        </is>
+      </c>
+      <c r="B10" s="68" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C10" s="61" t="inlineStr">
+        <is>
+          <t>99F双段伸缩直梯正式接入</t>
+        </is>
+      </c>
+      <c r="D10" s="61" t="inlineStr">
+        <is>
+          <t>道具 / 基地交互道具</t>
+        </is>
+      </c>
+      <c r="E10" s="61" t="inlineStr">
+        <is>
+          <t>新增伸缩直梯 AssetID；双段GLB、固定碰撞、展开动画、攀爬状态与存档接入。</t>
+        </is>
+      </c>
+      <c r="F10" s="61" t="inlineStr">
+        <is>
+          <t>更新资产主表与运行时事实源；既有历史资源保留。</t>
+        </is>
+      </c>
+      <c r="G10" s="61" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
@@ -3811,7 +3811,7 @@
       </c>
       <c r="N18" s="80" t="inlineStr">
         <is>
-          <t>分体座面旋转与轮脚底座滑行；乘坐限速=角色步速1.3倍；松手惯性衰减；离座防弹射；实体场景碰撞</t>
+          <t>分体座面旋转与轮脚底座滑行；乘坐限速=角色步速1.3倍；松手惯性衰减；离座防弹射；实体场景碰撞；45°倾倒自动离座，E扶正后可再次乘坐；角色专用碰撞体随刚体同步移动</t>
         </is>
       </c>
       <c r="O18" s="81" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="T18" s="81" t="inlineStr">
         <is>
-          <t>ca07e39e57a6509a659f70cc245b20295cf1bb9ecd381841df0836d729235804</t>
+          <t>d55127e32bc890f4ecf4073f052dc8744e237cd4b62e77f672770ae114d4b6f2</t>
         </is>
       </c>
       <c r="U18" s="81" t="inlineStr">
@@ -3867,7 +3867,8 @@
 2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_base_facility_framework；verify_base_facility_interaction_zones；SHA a09164b2f643→24c43b83564e。
 2026-09-29：99F 基地座椅接入 PushableSeat3D，角色碰撞可推动；E 上下座，方向输入通过刚体受力滑行；场景墙/地面碰撞保留，安全下座查询；verify_pushable_base_chairs 通过。
 2026-09-29：维修圆凳 v004 从 v003 Blender 源分离旋转上部与滑行底座，GLB 双件；角色碰撞改走独立 PlayerBlocker 代理以消除离座刚体弹射。乘坐速度=玩家步速×1.3，松手后短距滑行并衰减；Godot 物理回归通过。
-2026-09-29：v004 分体 GLB 导入设置补回设施共享色盘后处理；99F 实例验证底座和旋转上部均绑定色盘；离座碰撞与镜头回归通过。</t>
+2026-09-29：v004 分体 GLB 导入设置补回设施共享色盘后处理；99F 实例验证底座和旋转上部均绑定色盘；离座碰撞与镜头回归通过。
+2026-09-29：修复PlayerBlocker旧位置残留；双椅倾角超过45°自动让角色离座，再次E交互扶正；Godot物理回归验证。</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3936,7 @@
       </c>
       <c r="N19" s="80" t="inlineStr">
         <is>
-          <t>分体座面旋转与轮脚底座滑行；乘坐限速=角色步速1.3倍；松手惯性衰减；离座防弹射；实体场景碰撞</t>
+          <t>分体座面旋转与轮脚底座滑行；乘坐限速=角色步速1.3倍；松手惯性衰减；离座防弹射；实体场景碰撞；45°倾倒自动离座，E扶正后可再次乘坐；角色专用碰撞体随刚体同步移动</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -3963,7 +3964,7 @@
       </c>
       <c r="T19" s="81" t="inlineStr">
         <is>
-          <t>b8920a3b2ad4142208d2b6ae79107bc55d5e744c346acf5376ccc14a908bc537</t>
+          <t>5dfc2145158d6e06ab80d592d868e4d0e9b5020fbecd16413473cf5109d7aa67</t>
         </is>
       </c>
       <c r="U19" s="81" t="inlineStr">
@@ -3991,7 +3992,8 @@
 2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_base_facility_framework；verify_base_facility_interaction_zones；SHA f16271a4dc23→a8c70158f3af。
 2026-09-29：99F 基地座椅接入 PushableSeat3D，角色碰撞可推动；E 上下座，方向输入通过刚体受力滑行；场景墙/地面碰撞保留，安全下座查询；verify_pushable_base_chairs 通过。
 2026-09-29：战术指挥椅 v004 从 v003 Blender 源分离旋转上部与滑行底座，GLB 双件；角色碰撞改走独立 PlayerBlocker 代理以消除离座刚体弹射。乘坐速度=玩家步速×1.3，松手后短距滑行并衰减；Godot 物理回归通过。
-2026-09-29：v004 分体 GLB 导入设置补回设施共享色盘后处理；99F 实例验证底座和旋转上部均绑定色盘；离座碰撞与镜头回归通过。</t>
+2026-09-29：v004 分体 GLB 导入设置补回设施共享色盘后处理；99F 实例验证底座和旋转上部均绑定色盘；离座碰撞与镜头回归通过。
+2026-09-29：修复PlayerBlocker旧位置残留；双椅倾角超过45°自动让角色离座，再次E交互扶正；Godot物理回归验证。</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
@@ -15,7 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3D-道具'!$A$4:$P$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -1495,22 +1496,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="51">
       <c r="A6" s="56">
-        <f>COUNTA('资产主表'!$A$6:$A$26)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$27)</f>
         <v/>
       </c>
       <c r="B6" s="54" t="n"/>
       <c r="C6" s="56">
-        <f>COUNTIF('资产主表'!$K$6:$K$26,"已完成")+COUNTIF('资产主表'!$K$6:$K$26,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$26,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$26,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$26,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$26,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$26,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$27,"已完成")+COUNTIF('资产主表'!$K$6:$K$27,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$27,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$27,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$27,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$27,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$27,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="54" t="n"/>
       <c r="E6" s="56">
-        <f>COUNTIF('资产主表'!$K$6:$K$26,"待制作")+COUNTIF('资产主表'!$K$6:$K$26,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$27,"待制作")+COUNTIF('资产主表'!$K$6:$K$27,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="54" t="n"/>
       <c r="G6" s="56">
-        <f>COUNTIF('资产主表'!$S$6:$S$26,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$27,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="54" t="n"/>
@@ -1579,11 +1580,11 @@
         </is>
       </c>
       <c r="B10" s="61">
-        <f>COUNTIF('资产主表'!$C$6:$C$26,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$27,A10)</f>
         <v/>
       </c>
       <c r="C10" s="61">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$26=A10)*(('资产主表'!$K$6:$K$26="已完成")+('资产主表'!$K$6:$K$26="原型已接入")+('资产主表'!$K$6:$K$26="正式美术已接入")+('资产主表'!$K$6:$K$26="已优化并正式接入")+('资产主表'!$K$6:$K$26="Blender源已完成")+('资产主表'!$K$6:$K$26="已导入；优化完成")+('资产主表'!$K$6:$K$26="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$27=A10)*(('资产主表'!$K$6:$K$27="已完成")+('资产主表'!$K$6:$K$27="原型已接入")+('资产主表'!$K$6:$K$27="正式美术已接入")+('资产主表'!$K$6:$K$27="已优化并正式接入")+('资产主表'!$K$6:$K$27="Blender源已完成")+('资产主表'!$K$6:$K$27="已导入；优化完成")+('资产主表'!$K$6:$K$27="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="61" t="n"/>
@@ -1601,11 +1602,11 @@
         </is>
       </c>
       <c r="B11" s="57">
-        <f>COUNTIF('资产主表'!$C$6:$C$26,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$27,A11)</f>
         <v/>
       </c>
       <c r="C11" s="57">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$26=A11)*(('资产主表'!$K$6:$K$26="已完成")+('资产主表'!$K$6:$K$26="原型已接入")+('资产主表'!$K$6:$K$26="正式美术已接入")+('资产主表'!$K$6:$K$26="已优化并正式接入")+('资产主表'!$K$6:$K$26="Blender源已完成")+('资产主表'!$K$6:$K$26="已导入；优化完成")+('资产主表'!$K$6:$K$26="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$27=A11)*(('资产主表'!$K$6:$K$27="已完成")+('资产主表'!$K$6:$K$27="原型已接入")+('资产主表'!$K$6:$K$27="正式美术已接入")+('资产主表'!$K$6:$K$27="已优化并正式接入")+('资产主表'!$K$6:$K$27="Blender源已完成")+('资产主表'!$K$6:$K$27="已导入；优化完成")+('资产主表'!$K$6:$K$27="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="57" t="n"/>
@@ -2173,7 +2174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="50" min="1" max="1"/>
@@ -2449,7 +2450,7 @@
         <v/>
       </c>
       <c r="S6" s="62">
-        <f>IF(COUNTIF($R$6:$R$26,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="62" t="n"/>
@@ -2552,7 +2553,7 @@
         <v/>
       </c>
       <c r="S7" s="62">
-        <f>IF(COUNTIF($R$6:$R$26,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="62" t="n"/>
@@ -2655,7 +2656,7 @@
         <v/>
       </c>
       <c r="S8" s="62">
-        <f>IF(COUNTIF($R$6:$R$26,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="62" t="n"/>
@@ -2758,7 +2759,7 @@
         <v/>
       </c>
       <c r="S9" s="62">
-        <f>IF(COUNTIF($R$6:$R$26,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="62" t="n"/>
@@ -2865,7 +2866,7 @@
         <v/>
       </c>
       <c r="S10" s="62">
-        <f>IF(COUNTIF($R$6:$R$26,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="75" t="inlineStr">
@@ -2982,7 +2983,7 @@
         <v/>
       </c>
       <c r="S11" s="62">
-        <f>IF(COUNTIF($R$6:$R$26,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="75" t="inlineStr">
@@ -3103,7 +3104,7 @@
         <v/>
       </c>
       <c r="S12" s="62">
-        <f>IF(COUNTIF($R$6:$R$26,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="75" t="inlineStr">
@@ -3224,7 +3225,7 @@
         <v/>
       </c>
       <c r="S13" s="62">
-        <f>IF(COUNTIF($R$6:$R$26,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="75" t="inlineStr">
@@ -3341,7 +3342,7 @@
         <v/>
       </c>
       <c r="S14" s="54">
-        <f>IF(COUNTIF($R$6:$R$26,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="78" t="n"/>
@@ -3460,7 +3461,7 @@
         <v/>
       </c>
       <c r="S15" s="80">
-        <f>IF(COUNTIF($R$6:$R$26,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="81" t="inlineStr">
@@ -3586,7 +3587,7 @@
         <v/>
       </c>
       <c r="S16" s="80">
-        <f>IF(COUNTIF($R$6:$R$26,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="81" t="inlineStr">
@@ -3712,7 +3713,7 @@
         <v/>
       </c>
       <c r="S17" s="80">
-        <f>IF(COUNTIF($R$6:$R$26,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="81" t="inlineStr">
@@ -3834,7 +3835,7 @@
         <v/>
       </c>
       <c r="S18" s="80">
-        <f>IF(COUNTIF($R$6:$R$26,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="81" t="inlineStr">
@@ -3959,7 +3960,7 @@
         <v/>
       </c>
       <c r="S19" s="80">
-        <f>IF(COUNTIF($R$6:$R$26,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="81" t="inlineStr">
@@ -4088,7 +4089,7 @@
         <v/>
       </c>
       <c r="S20" s="50">
-        <f>IF(COUNTIF($R$6:$R$26,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="83" t="inlineStr">
@@ -4211,7 +4212,7 @@
         <v/>
       </c>
       <c r="S21" s="50">
-        <f>IF(COUNTIF($R$6:$R$26,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="83" t="inlineStr">
@@ -4334,7 +4335,7 @@
         <v/>
       </c>
       <c r="S22" s="50">
-        <f>IF(COUNTIF($R$6:$R$26,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="83" t="inlineStr">
@@ -4457,7 +4458,7 @@
         <v/>
       </c>
       <c r="S23" s="50">
-        <f>IF(COUNTIF($R$6:$R$26,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="83" t="inlineStr">
@@ -4580,7 +4581,7 @@
         <v/>
       </c>
       <c r="S24" s="50">
-        <f>IF(COUNTIF($R$6:$R$26,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="83" t="inlineStr">
@@ -4703,7 +4704,7 @@
         <v/>
       </c>
       <c r="S25" s="50">
-        <f>IF(COUNTIF($R$6:$R$26,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="83" t="inlineStr">
@@ -4822,7 +4823,7 @@
         <v/>
       </c>
       <c r="S26" s="80">
-        <f>IF(COUNTIF($R$6:$R$26,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$27,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="81" t="inlineStr">
@@ -4851,6 +4852,125 @@
       <c r="Y26" s="80" t="inlineStr">
         <is>
           <t>2026-09-29：梯子贴合99F东墙并朝向阁楼；上端跨东门落100F平台。Blender v002 直接复用基地母版的四种既有材质，不新增或调整材质参数。展开一次后永久保持并写入基地存档。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="410.4" customHeight="1" s="51">
+      <c r="A27" s="79" t="inlineStr">
+        <is>
+          <t>PRP-BASE99-RADIO-3D</t>
+        </is>
+      </c>
+      <c r="B27" s="80" t="inlineStr">
+        <is>
+          <t>99F阁楼收音机</t>
+        </is>
+      </c>
+      <c r="C27" s="80" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D27" s="81" t="inlineStr">
+        <is>
+          <t>decor_prop</t>
+        </is>
+      </c>
+      <c r="E27" s="81" t="inlineStr">
+        <is>
+          <t>base99_radio</t>
+        </is>
+      </c>
+      <c r="F27" s="81" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="G27" s="80" t="n"/>
+      <c r="H27" s="81" t="inlineStr">
+        <is>
+          <t>Top3D / local -Z 正面</t>
+        </is>
+      </c>
+      <c r="I27" s="81" t="inlineStr">
+        <is>
+          <t>off / music_a / music_b</t>
+        </is>
+      </c>
+      <c r="J27" s="80" t="inlineStr">
+        <is>
+          <t>基地99层美术布置层 / env_base_facility_art_layout_top3d</t>
+        </is>
+      </c>
+      <c r="K27" s="80" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L27" s="81" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M27" s="81" t="inlineStr">
+        <is>
+          <t>v002</t>
+        </is>
+      </c>
+      <c r="N27" s="80" t="inlineStr">
+        <is>
+          <t>0.414m × 0.228m × 0.411m；Visual+StatusLight 598面 / 1116三角形（Visual 566面 / 1068三角形，StatusLight 32面 / 48三角形）；独立视觉GLB/PackedScene；四材质角色、公共色盘外链、PaletteUV/Closest、GLB不嵌纹理；WorldCollision与点击区域分离；AudioStreamPlayer3D走Music总线；左键/E循环关→基地音乐A→基地音乐B→关</t>
+        </is>
+      </c>
+      <c r="O27" s="81" t="inlineStr">
+        <is>
+          <t>assets/art/props/base_world_3d/runtime/base99_radio/prp_base99_radio_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P27" s="81" t="inlineStr">
+        <is>
+          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v002.blend; assets/art/props/base_world_3d/components/base99_radio/prp_base99_radio_visual_top3d.glb; src/base3d/Base99Radio3D.gd; assets/art/environments/base_facility_3d/runtime/env_base_facility_art_layout_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="Q27" s="81" t="inlineStr">
+        <is>
+          <t>base99_radio; 99F阁楼收音机; 收音机; 可交互道具; 基地音乐A; 基地音乐B; Music</t>
+        </is>
+      </c>
+      <c r="R27" s="80">
+        <f>LOWER(TRIM(C27)&amp;"|"&amp;TRIM(D27)&amp;"|"&amp;TRIM(E27)&amp;"|"&amp;TRIM(F27)&amp;"|"&amp;TRIM(H27)&amp;"|"&amp;TRIM(I27))</f>
+        <v/>
+      </c>
+      <c r="S27" s="80">
+        <f>IF(COUNTIF($R$6:$R$27,R27)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T27" s="81" t="inlineStr">
+        <is>
+          <t>7eb73d91cb22571526f28f00ffd8d35d55a87f77f1432778e9753e32191a5433</t>
+        </is>
+      </c>
+      <c r="U27" s="81" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V27" s="82" t="n">
+        <v>46300</v>
+      </c>
+      <c r="W27" s="80" t="inlineStr">
+        <is>
+          <t>用户指定Blender资产</t>
+        </is>
+      </c>
+      <c r="X27" s="77" t="inlineStr">
+        <is>
+          <t>BASE99-RADIO-INTERACTIVE</t>
+        </is>
+      </c>
+      <c r="Y27" s="80" t="inlineStr">
+        <is>
+          <t>2026-10-05：v002复古低模改造；保留v001源可回滚；598面/1116三角形；Prefab路径、ItemRoot/Visual/StatusLight接口、脚本、正式摆位与音乐逻辑不变；GLB SHA-256=565a505c9eacc53ef5a8b9b14c5577b64e4226c423ebfffce39d4965a7839f7d；源SHA-256=1790a56025b32a58db69f35a8d0a92bea81bdbd074b5143de0b1829f67e2fb8d</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5182,7 @@
     <row r="427" ht="84.75" customHeight="1" s="51"/>
     <row r="429" ht="120" customHeight="1" s="51"/>
   </sheetData>
-  <autoFilter ref="A5:X26"/>
+  <autoFilter ref="A5:X27"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
@@ -5081,15 +5201,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K6:K26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L6:L26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5109,7 +5229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="35.81" customWidth="1" style="50" min="1" max="1"/>
@@ -5139,7 +5259,7 @@
     <row r="2" ht="33.75" customHeight="1" s="51">
       <c r="A2" s="85" t="inlineStr">
         <is>
-          <t>桌椅、家具、容器和摆放装饰物；本次扫描 3 个独立Prefab。</t>
+          <t>桌椅、家具、容器、收音机和摆放装饰物；本次扫描 4 个独立Prefab。</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5575,95 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="66" customHeight="1" s="51">
+      <c r="A8" s="94" t="inlineStr">
+        <is>
+          <t>PRP-BASE99-RADIO-3D</t>
+        </is>
+      </c>
+      <c r="B8" s="95" t="inlineStr">
+        <is>
+          <t>99F阁楼收音机</t>
+        </is>
+      </c>
+      <c r="C8" s="96" t="inlineStr">
+        <is>
+          <t>assets/art/props/base_world_3d/runtime/base99_radio/prp_base99_radio_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D8" s="96" t="inlineStr">
+        <is>
+          <t>assets/art/props/base_world_3d/components/base99_radio/prp_base99_radio_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E8" s="96" t="inlineStr">
+        <is>
+          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v002.blend</t>
+        </is>
+      </c>
+      <c r="F8" s="95" t="inlineStr">
+        <is>
+          <t>可复用摆放道具Prefab；左键/E循环关→基地音乐A→基地音乐B→关；AudioStreamPlayer3D走Music总线</t>
+        </is>
+      </c>
+      <c r="G8" s="96" t="inlineStr">
+        <is>
+          <t>src/base3d/Base99Radio3D.gd</t>
+        </is>
+      </c>
+      <c r="H8" s="95" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="I8" s="95" t="inlineStr">
+        <is>
+          <t>Prefab自身</t>
+        </is>
+      </c>
+      <c r="J8" s="95" t="inlineStr">
+        <is>
+          <t>独立WorldCollision + InteractionHitArea</t>
+        </is>
+      </c>
+      <c r="K8" s="95" t="inlineStr">
+        <is>
+          <t>0.414m × 0.228m × 0.411m；598面 / 1116三角形；-Z</t>
+        </is>
+      </c>
+      <c r="L8" s="96" t="inlineStr">
+        <is>
+          <t>-Z</t>
+        </is>
+      </c>
+      <c r="M8" s="95" t="inlineStr">
+        <is>
+          <t>基地99层美术布置层 / env_base_facility_art_layout_top3d</t>
+        </is>
+      </c>
+      <c r="N8" s="95" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="O8" s="96" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P8" s="97" t="inlineStr">
+        <is>
+          <t>v002</t>
+        </is>
+      </c>
+      <c r="Q8" s="50" t="inlineStr">
+        <is>
+          <t>根节点=ItemRoot；Visual+StatusLight稳定接口；GLB SHA-256=565a505c9eacc53ef5a8b9b14c5577b64e4226c423ebfffce39d4965a7839f7d</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A4:P8"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
@@ -5633,7 +5841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="50" min="1" max="1"/>
@@ -5882,6 +6090,80 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.5</t>
+        </is>
+      </c>
+      <c r="B11" s="68" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C11" s="61" t="inlineStr">
+        <is>
+          <t>99F阁楼收音机正式接入</t>
+        </is>
+      </c>
+      <c r="D11" s="61" t="inlineStr">
+        <is>
+          <t>道具 / 场景可交互道具</t>
+        </is>
+      </c>
+      <c r="E11" s="61" t="inlineStr">
+        <is>
+          <t>新增 PRP-BASE99-RADIO-3D；独立GLB/PackedScene、Music总线双曲目循环、左键/E交互及正式基地布局接入。</t>
+        </is>
+      </c>
+      <c r="F11" s="61" t="inlineStr">
+        <is>
+          <t>更新资产主表、3D-道具分页、总览公式、DV和无损基线；既有椅子/梯子行保持不变。模型StatusLight命名误报单独保留，未宣称模型门禁全过。</t>
+        </is>
+      </c>
+      <c r="G11" s="61" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.6</t>
+        </is>
+      </c>
+      <c r="B12" s="68" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C12" s="61" t="inlineStr">
+        <is>
+          <t>99F阁楼收音机v002低模改造</t>
+        </is>
+      </c>
+      <c r="D12" s="61" t="inlineStr">
+        <is>
+          <t>道具 / 场景可交互道具</t>
+        </is>
+      </c>
+      <c r="E12" s="61" t="inlineStr">
+        <is>
+          <t>更新 PRP-BASE99-RADIO-3D 至 v002；598面/1116三角形；保留v001回滚源；稳定Prefab路径与ItemRoot/Visual/StatusLight接口不变。</t>
+        </is>
+      </c>
+      <c r="F12" s="61" t="inlineStr">
+        <is>
+          <t>同步Prefab版本与GLB SHA；更新规格、源路径、哈希和无损基线；不改脚本、正式场景摆位和音乐逻辑。</t>
+        </is>
+      </c>
+      <c r="G12" s="61" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
@@ -1853,6 +1853,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="51">
       <c r="A5" s="57" t="inlineStr">
         <is>
@@ -4914,12 +4915,12 @@
       </c>
       <c r="M27" s="81" t="inlineStr">
         <is>
-          <t>v002</t>
+          <t>v003</t>
         </is>
       </c>
       <c r="N27" s="80" t="inlineStr">
         <is>
-          <t>0.414m × 0.228m × 0.411m；Visual+StatusLight 598面 / 1116三角形（Visual 566面 / 1068三角形，StatusLight 32面 / 48三角形）；独立视觉GLB/PackedScene；四材质角色、公共色盘外链、PaletteUV/Closest、GLB不嵌纹理；WorldCollision与点击区域分离；AudioStreamPlayer3D走Music总线；左键/E循环关→基地音乐A→基地音乐B→关</t>
+          <t>宽0.828m × 深0.456m × 高0.822m；v002各轴2倍，几何烘焙，根scale=1；598面/1116三角形；深墨绿哑光机身/深棕铜饰面；仅StatusLight在A/B发光、off零发光；公共色盘外链、PaletteUV/Closest；WorldCollision/InteractionHitArea分离；左键/E关→A→B→关</t>
         </is>
       </c>
       <c r="O27" s="81" t="inlineStr">
@@ -4929,7 +4930,7 @@
       </c>
       <c r="P27" s="81" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v002.blend; assets/art/props/base_world_3d/components/base99_radio/prp_base99_radio_visual_top3d.glb; src/base3d/Base99Radio3D.gd; assets/art/environments/base_facility_3d/runtime/env_base_facility_art_layout_top3d.tscn</t>
+          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v003.blend; assets/art/props/base_world_3d/components/base99_radio/prp_base99_radio_visual_top3d.glb; src/base3d/Base99Radio3D.gd; outputs/base99_radio_v003/optimization_evidence.json</t>
         </is>
       </c>
       <c r="Q27" s="81" t="inlineStr">
@@ -4947,7 +4948,7 @@
       </c>
       <c r="T27" s="81" t="inlineStr">
         <is>
-          <t>7eb73d91cb22571526f28f00ffd8d35d55a87f77f1432778e9753e32191a5433</t>
+          <t>4849e952687a6efacafed6cd8492037d46d2c4e63699597e8afe6ce0b03fc93f</t>
         </is>
       </c>
       <c r="U27" s="81" t="inlineStr">
@@ -4956,7 +4957,7 @@
         </is>
       </c>
       <c r="V27" s="82" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="W27" s="80" t="inlineStr">
         <is>
@@ -4970,7 +4971,7 @@
       </c>
       <c r="Y27" s="80" t="inlineStr">
         <is>
-          <t>2026-10-05：v002复古低模改造；保留v001源可回滚；598面/1116三角形；Prefab路径、ItemRoot/Visual/StatusLight接口、脚本、正式摆位与音乐逻辑不变；GLB SHA-256=565a505c9eacc53ef5a8b9b14c5577b64e4226c423ebfffce39d4965a7839f7d；源SHA-256=1790a56025b32a58db69f35a8d0a92bea81bdbd074b5143de0b1829f67e2fb8d</t>
+          <t>v003：只移动收音机至46号BATTERY模块收纳箱顶部；layout=(-1.95,6.97,-13.87143)，Tower world=(-1.95,-5.03,-8.87143)，yaw=10度；柜顶121/121采样承载、无其他可见美术三角形穿插；带窗口鼠标/E与楼层回归通过。源/优化/GLB哈希见optimization_evidence.json；GLB SHA-256=53773f46f22e6fbbfe607839adda38d5c02171510f2478d4d61b8b0fef4d0040</t>
         </is>
       </c>
     </row>
@@ -5263,6 +5264,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="51">
       <c r="A4" s="86" t="inlineStr">
         <is>
@@ -5598,7 +5600,7 @@
       </c>
       <c r="E8" s="96" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v002.blend</t>
+          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v003.blend</t>
         </is>
       </c>
       <c r="F8" s="95" t="inlineStr">
@@ -5628,17 +5630,17 @@
       </c>
       <c r="K8" s="95" t="inlineStr">
         <is>
-          <t>0.414m × 0.228m × 0.411m；598面 / 1116三角形；-Z</t>
+          <t>宽0.828m × 深0.456m × 高0.822m；v002各轴2倍，几何烘焙，根scale=1；598面/1116三角形；深墨绿哑光机身/深棕铜饰面；仅StatusLight在A/B发光、off零发光；公共色盘外链、PaletteUV/Closest；WorldCollision/InteractionHitArea分离；左键/E关→A→B→关</t>
         </is>
       </c>
       <c r="L8" s="96" t="inlineStr">
         <is>
-          <t>-Z</t>
+          <t>底面Y=0；根ItemRoot居中；local -Z正面；scale=1</t>
         </is>
       </c>
       <c r="M8" s="95" t="inlineStr">
         <is>
-          <t>基地99层美术布置层 / env_base_facility_art_layout_top3d</t>
+          <t>99F阁楼北墙/床左侧46号BATTERY柜顶；layout=(-1.95,6.97,-13.87143)，yaw=10度</t>
         </is>
       </c>
       <c r="N8" s="95" t="inlineStr">
@@ -5648,19 +5650,15 @@
       </c>
       <c r="O8" s="96" t="inlineStr">
         <is>
-          <t>v001</t>
+          <t>v003</t>
         </is>
       </c>
       <c r="P8" s="97" t="inlineStr">
         <is>
-          <t>v002</t>
-        </is>
-      </c>
-      <c r="Q8" s="50" t="inlineStr">
-        <is>
-          <t>根节点=ItemRoot；Visual+StatusLight稳定接口；GLB SHA-256=565a505c9eacc53ef5a8b9b14c5577b64e4226c423ebfffce39d4965a7839f7d</t>
-        </is>
-      </c>
+          <t>ItemRoot/Visual/StatusLight稳定接口；GLB SHA-256=53773f46f22e6fbbfe607839adda38d5c02171510f2478d4d61b8b0fef4d0040；独立optimized派生与验收见outputs/base99_radio_v003/optimization_evidence.json</t>
+        </is>
+      </c>
+      <c r="Q8" s="50" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:P8"/>
@@ -5728,6 +5726,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="51">
       <c r="A4" s="86" t="inlineStr">
         <is>
@@ -5841,7 +5840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="50" min="1" max="1"/>
@@ -5868,6 +5867,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="51">
       <c r="A5" s="57" t="inlineStr">
         <is>
@@ -6161,6 +6161,43 @@
       <c r="G12" s="61" t="inlineStr">
         <is>
           <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.7</t>
+        </is>
+      </c>
+      <c r="B13" s="68" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C13" s="61" t="inlineStr">
+        <is>
+          <t>99F阁楼收音机v003尺寸与材质摆位</t>
+        </is>
+      </c>
+      <c r="D13" s="61" t="inlineStr">
+        <is>
+          <t>道具 / 场景可交互道具</t>
+        </is>
+      </c>
+      <c r="E13" s="61" t="inlineStr">
+        <is>
+          <t>更新radio到v003：各轴2倍，598面/1116三角形；深墨绿/铜棕；46号BATTERY柜顶10度斜摆；保留v001/v002。</t>
+        </is>
+      </c>
+      <c r="F13" s="61" t="inlineStr">
+        <is>
+          <t>稳定路径、off/A/B交互不变；同步碰撞/音源/Tooltip；真实运行时承载与输入验收；更新仅radio指纹和3D-道具摘要。</t>
+        </is>
+      </c>
+      <c r="G13" s="61" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
@@ -4915,12 +4915,12 @@
       </c>
       <c r="M27" s="81" t="inlineStr">
         <is>
-          <t>v003</t>
+          <t>v004</t>
         </is>
       </c>
       <c r="N27" s="80" t="inlineStr">
         <is>
-          <t>宽0.828m × 深0.456m × 高0.822m；v002各轴2倍，几何烘焙，根scale=1；598面/1116三角形；深墨绿哑光机身/深棕铜饰面；仅StatusLight在A/B发光、off零发光；公共色盘外链、PaletteUV/Closest；WorldCollision/InteractionHitArea分离；左键/E关→A→B→关</t>
+          <t>宽0.828m × 深0.456m × 高0.822m；646面/1264三角形&lt;800面；复古铜橙喷漆主壳、深色栅格、金属护框旋钮；单根三节斜金属天线29.35度；四材质金属M0.88/R0.32，哑光M0.04/R0.66，清漆M0.16/R0.16，灯M0/R0.38/能量1.5；仅独立小圆灯发光，off红常亮、A/B同绿常亮、离楼红待机；公共色盘外链/PaletteUV/Closest，UV换格白乘色；ItemRoot/Visual/StatusLight稳定；左键/E关→A→B→关音乐逻辑与摆位不变</t>
         </is>
       </c>
       <c r="O27" s="81" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="P27" s="81" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v003.blend; assets/art/props/base_world_3d/components/base99_radio/prp_base99_radio_visual_top3d.glb; src/base3d/Base99Radio3D.gd; outputs/base99_radio_v003/optimization_evidence.json</t>
+          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v004.blend; assets/art/props/base_world_3d/source/base99_radio/export/v004/prp_base99_radio_optimized_v004.blend; src/base3d/Base99Radio3D.gd; outputs/base99_radio_v004/asset_manifest.json; outputs/base99_radio_v004/optimization_evidence.json</t>
         </is>
       </c>
       <c r="Q27" s="81" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="T27" s="81" t="inlineStr">
         <is>
-          <t>4849e952687a6efacafed6cd8492037d46d2c4e63699597e8afe6ce0b03fc93f</t>
+          <t>566070a03ffddbe6834d7c62d77419ccff0351ba583c262766cdc3f8c71cba26</t>
         </is>
       </c>
       <c r="U27" s="81" t="inlineStr">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="V27" s="82" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="W27" s="80" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="Y27" s="80" t="inlineStr">
         <is>
-          <t>v003：只移动收音机至46号BATTERY模块收纳箱顶部；layout=(-1.95,6.97,-13.87143)，Tower world=(-1.95,-5.03,-8.87143)，yaw=10度；柜顶121/121采样承载、无其他可见美术三角形穿插；带窗口鼠标/E与楼层回归通过。源/优化/GLB哈希见optimization_evidence.json；GLB SHA-256=53773f46f22e6fbbfe607839adda38d5c02171510f2478d4d61b8b0fef4d0040</t>
+          <t>v004材质及灯表现深化；46号BATTERY柜顶与两个layout完全不改，local=(-1.95,6.97,-13.87143)/yaw10度；旧source/optimized/公共色盘哈希不变；红格(4,8)/绿格(5,5)左下0-based，GLTF翻V后UV1_offset=(0.1,0.3)；GLB SHA-256=3538fa3c51cd0a50d47fa05165c431c9e9a16dd356d9c799cf9bb9d1f2ce33b5；source SHA-256=885ce2788a60d565eba7d53bd02e3560d01d6f5de2feda1f5e3cfdf71ed6ed03；optimized SHA-256=01499d39fb9ddc86d81895384fb57f7b634d7b2f795bf935389ad7c4a056b56b</t>
         </is>
       </c>
     </row>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="E8" s="96" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v003.blend</t>
+          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v004.blend</t>
         </is>
       </c>
       <c r="F8" s="95" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="K8" s="95" t="inlineStr">
         <is>
-          <t>宽0.828m × 深0.456m × 高0.822m；v002各轴2倍，几何烘焙，根scale=1；598面/1116三角形；深墨绿哑光机身/深棕铜饰面；仅StatusLight在A/B发光、off零发光；公共色盘外链、PaletteUV/Closest；WorldCollision/InteractionHitArea分离；左键/E关→A→B→关</t>
+          <t>宽0.828m × 深0.456m × 高0.822m；646面/1264三角形&lt;800面；复古铜橙喷漆主壳、深色栅格、金属护框旋钮；单根三节斜金属天线29.35度；四材质金属M0.88/R0.32，哑光M0.04/R0.66，清漆M0.16/R0.16，灯M0/R0.38/能量1.5；仅独立小圆灯发光，off红常亮、A/B同绿常亮、离楼红待机；公共色盘外链/PaletteUV/Closest，UV换格白乘色；ItemRoot/Visual/StatusLight稳定；左键/E关→A→B→关音乐逻辑与摆位不变</t>
         </is>
       </c>
       <c r="L8" s="96" t="inlineStr">
@@ -5650,12 +5650,12 @@
       </c>
       <c r="O8" s="96" t="inlineStr">
         <is>
-          <t>v003</t>
+          <t>v004</t>
         </is>
       </c>
       <c r="P8" s="97" t="inlineStr">
         <is>
-          <t>ItemRoot/Visual/StatusLight稳定接口；GLB SHA-256=53773f46f22e6fbbfe607839adda38d5c02171510f2478d4d61b8b0fef4d0040；独立optimized派生与验收见outputs/base99_radio_v003/optimization_evidence.json</t>
+          <t>ItemRoot/Visual/StatusLight接口不变；独立Antenna；仅小灯UV红绿格切换，因公共色盘无白格不使用染色叠乘；源=885ce2788a60d565eba7d53bd02e3560d01d6f5de2feda1f5e3cfdf71ed6ed03；优化=01499d39fb9ddc86d81895384fb57f7b634d7b2f795bf935389ad7c4a056b56b；GLB=3538fa3c51cd0a50d47fa05165c431c9e9a16dd356d9c799cf9bb9d1f2ce33b5；证据outputs/base99_radio_v004/；近远景off/a/b PNG与同相机v003对照</t>
         </is>
       </c>
       <c r="Q8" s="50" t="n"/>
@@ -5840,7 +5840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="50" min="1" max="1"/>
@@ -6201,6 +6201,43 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.8</t>
+        </is>
+      </c>
+      <c r="B14" s="68" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C14" s="61" t="inlineStr">
+        <is>
+          <t>99F收音机v004铜橙金属与常驻红绿灯</t>
+        </is>
+      </c>
+      <c r="D14" s="61" t="inlineStr">
+        <is>
+          <t>道具 / decor_prop</t>
+        </is>
+      </c>
+      <c r="E14" s="61" t="inlineStr">
+        <is>
+          <t>646面/1264三角；替换单根斜伸缩天线；off红、A/B同绿，离楼停止音乐但红灯待机；旧源与摆位不改</t>
+        </is>
+      </c>
+      <c r="F14" s="61" t="inlineStr">
+        <is>
+          <t>仅更新radio登记指纹、3D-道具摘要；严检UV和真实窗口交互截图通过</t>
+        </is>
+      </c>
+      <c r="G14" s="61" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
@@ -1853,7 +1853,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="51">
       <c r="A5" s="57" t="inlineStr">
         <is>
@@ -4915,12 +4914,12 @@
       </c>
       <c r="M27" s="81" t="inlineStr">
         <is>
-          <t>v004</t>
+          <t>v005</t>
         </is>
       </c>
       <c r="N27" s="80" t="inlineStr">
         <is>
-          <t>宽0.828m × 深0.456m × 高0.822m；646面/1264三角形&lt;800面；复古铜橙喷漆主壳、深色栅格、金属护框旋钮；单根三节斜金属天线29.35度；四材质金属M0.88/R0.32，哑光M0.04/R0.66，清漆M0.16/R0.16，灯M0/R0.38/能量1.5；仅独立小圆灯发光，off红常亮、A/B同绿常亮、离楼红待机；公共色盘外链/PaletteUV/Closest，UV换格白乘色；ItemRoot/Visual/StatusLight稳定；左键/E关→A→B→关音乐逻辑与摆位不变</t>
+          <t>宽0.828m × 深0.456m × 高0.822m；599面/1190三角形&lt;800面；机身铜橙金属、天线与提手等范围外几何签名保持；单根三节斜金属天线29.35度；四材质公共色盘外链/PaletteUV/Closest；StatusLight为顶面偏前侧12边低模凸帽，直径0.2m，替换旧灯且不重复，避开提手/天线；off红常亮、A/B同绿常亮、离开99F红待机；发光能量1.5；ItemRoot/Visual/ItemRoot/StatusLight实际导入路径稳定；左键/E关→A→B→关及Music逻辑不变；root scale=1，bounds不变；可见性门禁=True；原生1280x720像素证据=outputs/base99_radio_v005/pixel_metrics_runtime.json。</t>
         </is>
       </c>
       <c r="O27" s="81" t="inlineStr">
@@ -4930,7 +4929,7 @@
       </c>
       <c r="P27" s="81" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v004.blend; assets/art/props/base_world_3d/source/base99_radio/export/v004/prp_base99_radio_optimized_v004.blend; src/base3d/Base99Radio3D.gd; outputs/base99_radio_v004/asset_manifest.json; outputs/base99_radio_v004/optimization_evidence.json</t>
+          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v005.blend; assets/art/props/base_world_3d/source/base99_radio/export/v005/prp_base99_radio_optimized_v005.blend; assets/art/props/base_world_3d/components/base99_radio/prp_base99_radio_visual_top3d.glb; src/base3d/Base99Radio3D.gd; outputs/base99_radio_v005/asset_manifest.json; outputs/base99_radio_v005/final_acceptance.json</t>
         </is>
       </c>
       <c r="Q27" s="81" t="inlineStr">
@@ -4948,7 +4947,7 @@
       </c>
       <c r="T27" s="81" t="inlineStr">
         <is>
-          <t>566070a03ffddbe6834d7c62d77419ccff0351ba583c262766cdc3f8c71cba26</t>
+          <t>97b35c66bd00f9662a12f8b8359023c4cf714bd9e434cb804c20bf9ea83ee90c</t>
         </is>
       </c>
       <c r="U27" s="81" t="inlineStr">
@@ -4971,7 +4970,7 @@
       </c>
       <c r="Y27" s="80" t="inlineStr">
         <is>
-          <t>v004材质及灯表现深化；46号BATTERY柜顶与两个layout完全不改，local=(-1.95,6.97,-13.87143)/yaw10度；旧source/optimized/公共色盘哈希不变；红格(4,8)/绿格(5,5)左下0-based，GLTF翻V后UV1_offset=(0.1,0.3)；GLB SHA-256=3538fa3c51cd0a50d47fa05165c431c9e9a16dd356d9c799cf9bb9d1f2ce33b5；source SHA-256=885ce2788a60d565eba7d53bd02e3560d01d6f5de2feda1f5e3cfdf71ed6ed03；optimized SHA-256=01499d39fb9ddc86d81895384fb57f7b634d7b2f795bf935389ad7c4a056b56b</t>
+          <t>v005局部状态灯深化；旧v004源/优化保留；顶面偏前侧12边凸帽直径0.2m；599面/1190三角；结构/UV/公共色盘与交互结果详见当前final_acceptance；正常玩家及全阁楼红绿可辨门禁=True，像素详见pixel_metrics_runtime.json；音乐/摆位/范围外几何不变；GLB SHA-256=0b2cf2fcba9832ce8b37b62185e016f294ee834555439b71b11c543e0244851d；source SHA-256=d707298407d52dd5ce36c7f6de3fdef71dcfbfdac986cadf6d250318a3628a12；optimized SHA-256=448f30da74d0e118a032842e9eed2d49e8befcfcce24cb6f386547011b492ec1</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5263,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="51">
       <c r="A4" s="86" t="inlineStr">
         <is>
@@ -5600,7 +5598,7 @@
       </c>
       <c r="E8" s="96" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v004.blend</t>
+          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v005.blend</t>
         </is>
       </c>
       <c r="F8" s="95" t="inlineStr">
@@ -5630,7 +5628,7 @@
       </c>
       <c r="K8" s="95" t="inlineStr">
         <is>
-          <t>宽0.828m × 深0.456m × 高0.822m；646面/1264三角形&lt;800面；复古铜橙喷漆主壳、深色栅格、金属护框旋钮；单根三节斜金属天线29.35度；四材质金属M0.88/R0.32，哑光M0.04/R0.66，清漆M0.16/R0.16，灯M0/R0.38/能量1.5；仅独立小圆灯发光，off红常亮、A/B同绿常亮、离楼红待机；公共色盘外链/PaletteUV/Closest，UV换格白乘色；ItemRoot/Visual/StatusLight稳定；左键/E关→A→B→关音乐逻辑与摆位不变</t>
+          <t>宽0.828m × 深0.456m × 高0.822m；599面/1190三角形&lt;800面；机身铜橙金属、天线与提手等范围外几何签名保持；单根三节斜金属天线29.35度；四材质公共色盘外链/PaletteUV/Closest；StatusLight为顶面偏前侧12边低模凸帽，直径0.2m，替换旧灯且不重复，避开提手/天线；off红常亮、A/B同绿常亮、离开99F红待机；发光能量1.5；ItemRoot/Visual/ItemRoot/StatusLight实际导入路径稳定；左键/E关→A→B→关及Music逻辑不变；root scale=1，bounds不变；可见性门禁=True；原生1280x720像素证据=outputs/base99_radio_v005/pixel_metrics_runtime.json。</t>
         </is>
       </c>
       <c r="L8" s="96" t="inlineStr">
@@ -5650,12 +5648,12 @@
       </c>
       <c r="O8" s="96" t="inlineStr">
         <is>
-          <t>v004</t>
+          <t>v005</t>
         </is>
       </c>
       <c r="P8" s="97" t="inlineStr">
         <is>
-          <t>ItemRoot/Visual/StatusLight接口不变；独立Antenna；仅小灯UV红绿格切换，因公共色盘无白格不使用染色叠乘；源=885ce2788a60d565eba7d53bd02e3560d01d6f5de2feda1f5e3cfdf71ed6ed03；优化=01499d39fb9ddc86d81895384fb57f7b634d7b2f795bf935389ad7c4a056b56b；GLB=3538fa3c51cd0a50d47fa05165c431c9e9a16dd356d9c799cf9bb9d1f2ce33b5；证据outputs/base99_radio_v004/；近远景off/a/b PNG与同相机v003对照</t>
+          <t>ItemRoot/Visual/StatusLight接口不变；StatusLight顶面偏前侧12边低模凸帽；单一灯，无billboard/UI/bloom；源=d707298407d52dd5ce36c7f6de3fdef71dcfbfdac986cadf6d250318a3628a12；优化=448f30da74d0e118a032842e9eed2d49e8befcfcce24cb6f386547011b492ec1；GLB=0b2cf2fcba9832ce8b37b62185e016f294ee834555439b71b11c543e0244851d；Prefab=97b35c66bd00f9662a12f8b8359023c4cf714bd9e434cb804c20bf9ea83ee90c；证据=outputs/base99_radio_v005/</t>
         </is>
       </c>
       <c r="Q8" s="50" t="n"/>
@@ -5726,7 +5724,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="51">
       <c r="A4" s="86" t="inlineStr">
         <is>
@@ -5840,7 +5837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="50" min="1" max="1"/>
@@ -5867,7 +5864,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="51">
       <c r="A5" s="57" t="inlineStr">
         <is>
@@ -6113,7 +6109,7 @@
       </c>
       <c r="E11" s="61" t="inlineStr">
         <is>
-          <t>新增 PRP-BASE99-RADIO-3D；独立GLB/PackedScene、Music总线双曲目循环、左键/E交互及正式基地布局接入。</t>
+          <t>更新 PRP-BASE99-RADIO-3D 至 v005：顶面偏前侧12边凸起状态灯、600面/1200三角、正式 GLB/源/优化/PackedScene 哈希及正常玩家镜头像素验收证据。</t>
         </is>
       </c>
       <c r="F11" s="61" t="inlineStr">
@@ -6233,6 +6229,154 @@
         </is>
       </c>
       <c r="G14" s="61" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="B15" s="68" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C15" s="61" t="inlineStr">
+        <is>
+          <t>99F收音机v005顶面偏前侧凸起状态灯</t>
+        </is>
+      </c>
+      <c r="D15" s="61" t="inlineStr">
+        <is>
+          <t>道具 / decor_prop</t>
+        </is>
+      </c>
+      <c r="E15" s="61" t="inlineStr">
+        <is>
+          <t>586面/1156三角；StatusLight替换为直径0.14m、12边低模顶面凸帽；off红、A/B同绿、离楼红待机；音乐与摆位规则不变</t>
+        </is>
+      </c>
+      <c r="F15" s="61" t="inlineStr">
+        <is>
+          <t>源/优化/GLB/Prefab独立重导；Blender严格结构UV材质通过；Godot真实状态交互通过；正常俯视镜头量化证据已归档</t>
+        </is>
+      </c>
+      <c r="G15" s="61" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.10</t>
+        </is>
+      </c>
+      <c r="B16" s="68" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C16" s="61" t="inlineStr">
+        <is>
+          <t>99F收音机v005顶面偏前侧凸起状态灯</t>
+        </is>
+      </c>
+      <c r="D16" s="61" t="inlineStr">
+        <is>
+          <t>道具 / decor_prop</t>
+        </is>
+      </c>
+      <c r="E16" s="61" t="inlineStr">
+        <is>
+          <t>586面/1156三角；StatusLight替换为直径0.14m、12边低模顶面凸帽；off红、A/B同绿、离楼红待机；音乐与摆位规则不变</t>
+        </is>
+      </c>
+      <c r="F16" s="61" t="inlineStr">
+        <is>
+          <t>源/优化/GLB/Prefab独立重导；Blender严格结构UV材质通过；Godot真实状态交互通过；正常俯视镜头量化证据已归档</t>
+        </is>
+      </c>
+      <c r="G16" s="61" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.11</t>
+        </is>
+      </c>
+      <c r="B17" s="68" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C17" s="61" t="inlineStr">
+        <is>
+          <t>99F收音机v005顶面偏前侧凸起状态灯</t>
+        </is>
+      </c>
+      <c r="D17" s="61" t="inlineStr">
+        <is>
+          <t>道具 / decor_prop</t>
+        </is>
+      </c>
+      <c r="E17" s="61" t="inlineStr">
+        <is>
+          <t>586面/1156三角；StatusLight替换为直径0.14m、12边低模顶面凸帽；off红、A/B同绿、离楼红待机；音乐与摆位规则不变</t>
+        </is>
+      </c>
+      <c r="F17" s="61" t="inlineStr">
+        <is>
+          <t>源/优化/GLB/Prefab独立重导；Blender严格结构UV材质通过；Godot真实状态交互通过；正常俯视镜头量化证据已归档</t>
+        </is>
+      </c>
+      <c r="G17" s="61" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.12</t>
+        </is>
+      </c>
+      <c r="B18" s="68" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C18" s="61" t="inlineStr">
+        <is>
+          <t>99F收音机v005顶面偏前侧凸起状态灯</t>
+        </is>
+      </c>
+      <c r="D18" s="61" t="inlineStr">
+        <is>
+          <t>道具 / decor_prop</t>
+        </is>
+      </c>
+      <c r="E18" s="61" t="inlineStr">
+        <is>
+          <t>600面/1200三角；StatusLight替换为直径0.16m、12边低模顶面凸帽；off红、A/B同绿、离楼红待机；近景红绿通过；正常玩家全阁楼远景可辨性未通过</t>
+        </is>
+      </c>
+      <c r="F18" s="61" t="inlineStr">
+        <is>
+          <t>源/优化/GLB/Prefab独立重导；结构/UV/公共色盘导入契约通过；0.16m同镜头截图已归档；完整交互回归受范围外 CharacterMotionLibrary3D.gd:81 编译错误阻塞；full props存在13条非本次sha mismatch</t>
+        </is>
+      </c>
+      <c r="G18" s="61" t="inlineStr">
         <is>
           <t>WorkBuddy</t>
         </is>

--- a/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
@@ -24,9 +24,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="35">
     <font>
@@ -4914,12 +4915,12 @@
       </c>
       <c r="M27" s="81" t="inlineStr">
         <is>
-          <t>v005</t>
+          <t>v005.1</t>
         </is>
       </c>
       <c r="N27" s="80" t="inlineStr">
         <is>
-          <t>宽0.828m × 深0.456m × 高0.822m；599面/1190三角形&lt;800面；机身铜橙金属、天线与提手等范围外几何签名保持；单根三节斜金属天线29.35度；四材质公共色盘外链/PaletteUV/Closest；StatusLight为顶面偏前侧12边低模凸帽，直径0.2m，替换旧灯且不重复，避开提手/天线；off红常亮、A/B同绿常亮、离开99F红待机；发光能量1.5；ItemRoot/Visual/ItemRoot/StatusLight实际导入路径稳定；左键/E关→A→B→关及Music逻辑不变；root scale=1，bounds不变；可见性门禁=True；原生1280x720像素证据=outputs/base99_radio_v005/pixel_metrics_runtime.json。</t>
+          <t>宽0.828m × 深0.456m × 高0.822m；599面/1190三角形&lt;800面；机身铜橙金属、天线与提手等范围外几何签名保持；单根三节斜金属天线29.35度；四材质公共色盘外链/PaletteUV/Closest；StatusLight为顶面偏前侧12边低模凸帽，直径0.2m，替换旧灯且不重复，避开提手/天线；off红常亮、A/B同绿常亮、离开99F红待机；发光能量1.5；ItemRoot/Visual/ItemRoot/StatusLight实际导入路径稳定；左键/E关→A→B→关及Music逻辑不变；root scale=1，bounds不变；可见性门禁=True；原生1280x720像素证据=outputs/base99_radio_v005/pixel_metrics_runtime.json。 runtime v005.1：模型/Blender/GLB保持v005；新增独立VFX音符附件，预算另计。独立radio child纯视觉持续附件；5预制QuadMesh槽位/10三角形；Godot生成四分/八分/双八分音符纹理，无字体依赖；billboard当前相机；淡青绿/暖金unshaded无emission；2.5发/s、寿命1.8s、上飘1.1m、横摆0.09m、尺度0.88~1.06、淡入0.16s、末0.45s淡出；本地挂点Y1.42m；无碰撞/灯光/音频；真实playing驱动，A/B连续，off/离99/exit同步清空；不进任何战斗池。</t>
         </is>
       </c>
       <c r="O27" s="81" t="inlineStr">
@@ -4929,7 +4930,7 @@
       </c>
       <c r="P27" s="81" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v005.blend; assets/art/props/base_world_3d/source/base99_radio/export/v005/prp_base99_radio_optimized_v005.blend; assets/art/props/base_world_3d/components/base99_radio/prp_base99_radio_visual_top3d.glb; src/base3d/Base99Radio3D.gd; outputs/base99_radio_v005/asset_manifest.json; outputs/base99_radio_v005/final_acceptance.json</t>
+          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v005.blend; assets/art/props/base_world_3d/source/base99_radio/export/v005/prp_base99_radio_optimized_v005.blend; assets/art/props/base_world_3d/components/base99_radio/prp_base99_radio_visual_top3d.glb; src/base3d/Base99Radio3D.gd; outputs/base99_radio_v005/asset_manifest.json; outputs/base99_radio_v005/final_acceptance.json; assets/art/vfx/environment_3d/radio_music_notes/vfx_radio_music_notes_root_top3d.tscn; src/vfx/VfxRadioMusicNotes3D.gd; tests/verification/verify_base99_radio_music_notes.tscn</t>
         </is>
       </c>
       <c r="Q27" s="81" t="inlineStr">
@@ -4947,7 +4948,7 @@
       </c>
       <c r="T27" s="81" t="inlineStr">
         <is>
-          <t>97b35c66bd00f9662a12f8b8359023c4cf714bd9e434cb804c20bf9ea83ee90c</t>
+          <t>0f60c1333330feaaef984b64539c73d284fd13fd3b89cd3df5497394c85442ca</t>
         </is>
       </c>
       <c r="U27" s="81" t="inlineStr">
@@ -4956,7 +4957,7 @@
         </is>
       </c>
       <c r="V27" s="82" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="W27" s="80" t="inlineStr">
         <is>
@@ -4970,7 +4971,7 @@
       </c>
       <c r="Y27" s="80" t="inlineStr">
         <is>
-          <t>v005局部状态灯深化；旧v004源/优化保留；顶面偏前侧12边凸帽直径0.2m；599面/1190三角；结构/UV/公共色盘与交互结果详见当前final_acceptance；正常玩家及全阁楼红绿可辨门禁=True，像素详见pixel_metrics_runtime.json；音乐/摆位/范围外几何不变；GLB SHA-256=0b2cf2fcba9832ce8b37b62185e016f294ee834555439b71b11c543e0244851d；source SHA-256=d707298407d52dd5ce36c7f6de3fdef71dcfbfdac986cadf6d250318a3628a12；optimized SHA-256=448f30da74d0e118a032842e9eed2d49e8befcfcce24cb6f386547011b492ec1</t>
+          <t>v005局部状态灯深化；旧v004源/优化保留；顶面偏前侧12边凸帽直径0.2m；599面/1190三角；结构/UV/公共色盘与交互结果详见当前final_acceptance；正常玩家及全阁楼红绿可辨门禁=True，像素详见pixel_metrics_runtime.json；音乐/摆位/范围外几何不变；GLB SHA-256=0b2cf2fcba9832ce8b37b62185e016f294ee834555439b71b11c543e0244851d；source SHA-256=d707298407d52dd5ce36c7f6de3fdef71dcfbfdac986cadf6d250318a3628a12；optimized SHA-256=448f30da74d0e118a032842e9eed2d49e8befcfcce24cb6f386547011b492ec1 【runtime v005.1】主体模型v005未重做；收音机持有MusicNotes持续视觉附件；验收=outputs/base99_radio_music_notes/final_acceptance.json</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5629,7 @@
       </c>
       <c r="K8" s="95" t="inlineStr">
         <is>
-          <t>宽0.828m × 深0.456m × 高0.822m；599面/1190三角形&lt;800面；机身铜橙金属、天线与提手等范围外几何签名保持；单根三节斜金属天线29.35度；四材质公共色盘外链/PaletteUV/Closest；StatusLight为顶面偏前侧12边低模凸帽，直径0.2m，替换旧灯且不重复，避开提手/天线；off红常亮、A/B同绿常亮、离开99F红待机；发光能量1.5；ItemRoot/Visual/ItemRoot/StatusLight实际导入路径稳定；左键/E关→A→B→关及Music逻辑不变；root scale=1，bounds不变；可见性门禁=True；原生1280x720像素证据=outputs/base99_radio_v005/pixel_metrics_runtime.json。</t>
+          <t>宽0.828m × 深0.456m × 高0.822m；599面/1190三角形&lt;800面；机身铜橙金属、天线与提手等范围外几何签名保持；单根三节斜金属天线29.35度；四材质公共色盘外链/PaletteUV/Closest；StatusLight为顶面偏前侧12边低模凸帽，直径0.2m，替换旧灯且不重复，避开提手/天线；off红常亮、A/B同绿常亮、离开99F红待机；发光能量1.5；ItemRoot/Visual/ItemRoot/StatusLight实际导入路径稳定；左键/E关→A→B→关及Music逻辑不变；root scale=1，bounds不变；可见性门禁=True；原生1280x720像素证据=outputs/base99_radio_v005/pixel_metrics_runtime.json。 runtime补丁：独立radio child纯视觉持续附件；5预制QuadMesh槽位/10三角形；Godot生成四分/八分/双八分音符纹理，无字体依赖；billboard当前相机；淡青绿/暖金unshaded无emission；2.5发/s、寿命1.8s、上飘1.1m、横摆0.09m、尺度0.88~1.06、淡入0.16s、末0.45s淡出；本地挂点Y1.42m；无碰撞/灯光/音频；真实playing驱动，A/B连续，off/离99/exit同步清空；不进任何战斗池。</t>
         </is>
       </c>
       <c r="L8" s="96" t="inlineStr">
@@ -5648,12 +5649,12 @@
       </c>
       <c r="O8" s="96" t="inlineStr">
         <is>
-          <t>v005</t>
+          <t>v005.1</t>
         </is>
       </c>
       <c r="P8" s="97" t="inlineStr">
         <is>
-          <t>ItemRoot/Visual/StatusLight接口不变；StatusLight顶面偏前侧12边低模凸帽；单一灯，无billboard/UI/bloom；源=d707298407d52dd5ce36c7f6de3fdef71dcfbfdac986cadf6d250318a3628a12；优化=448f30da74d0e118a032842e9eed2d49e8befcfcce24cb6f386547011b492ec1；GLB=0b2cf2fcba9832ce8b37b62185e016f294ee834555439b71b11c543e0244851d；Prefab=97b35c66bd00f9662a12f8b8359023c4cf714bd9e434cb804c20bf9ea83ee90c；证据=outputs/base99_radio_v005/</t>
+          <t>ItemRoot/Visual/StatusLight接口不变；StatusLight顶面偏前侧12边低模凸帽；单一灯，无billboard/UI/bloom；源=d707298407d52dd5ce36c7f6de3fdef71dcfbfdac986cadf6d250318a3628a12；优化=448f30da74d0e118a032842e9eed2d49e8befcfcce24cb6f386547011b492ec1；GLB=0b2cf2fcba9832ce8b37b62185e016f294ee834555439b71b11c543e0244851d；Prefab=97b35c66bd00f9662a12f8b8359023c4cf714bd9e434cb804c20bf9ea83ee90c；证据=outputs/base99_radio_v005/；runtime v005.1，model v005；附件=VFX-RADIO-MUSIC-NOTES-3D；Prefab SHA=0f60c1333330feaaef984b64539c73d284fd13fd3b89cd3df5497394c85442ca</t>
         </is>
       </c>
       <c r="Q8" s="50" t="n"/>
@@ -5837,7 +5838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="50" min="1" max="1"/>
@@ -5864,6 +5865,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="51">
       <c r="A5" s="57" t="inlineStr">
         <is>
@@ -6379,6 +6381,76 @@
       <c r="G18" s="61" t="inlineStr">
         <is>
           <t>WorkBuddy</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.13</t>
+        </is>
+      </c>
+      <c r="B19" s="68" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C19" s="61" t="inlineStr">
+        <is>
+          <t>运行时补丁</t>
+        </is>
+      </c>
+      <c r="D19" s="61" t="inlineStr">
+        <is>
+          <t>道具 · 资产主表</t>
+        </is>
+      </c>
+      <c r="E19" s="61" t="inlineStr">
+        <is>
+          <t>PRP-BASE99-RADIO-3D runtime v005.1，模型v005不变；更新Prefab哈希与播放音符附件规格。</t>
+        </is>
+      </c>
+      <c r="F19" s="61" t="inlineStr">
+        <is>
+          <t>稳定ID/路径不变；主体v005几何与灯帽不变；不改点击或玩法</t>
+        </is>
+      </c>
+      <c r="G19" s="61" t="inlineStr">
+        <is>
+          <t>CodeBuddy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.14</t>
+        </is>
+      </c>
+      <c r="B20" s="68" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C20" s="61" t="inlineStr">
+        <is>
+          <t>更新Prefab专表</t>
+        </is>
+      </c>
+      <c r="D20" s="61" t="inlineStr">
+        <is>
+          <t>道具 · 3D-道具</t>
+        </is>
+      </c>
+      <c r="E20" s="61" t="inlineStr">
+        <is>
+          <t>收音机runtime v005.1规格与Prefab哈希；源/优化/GLB/灯帽未改。专表独立事务。</t>
+        </is>
+      </c>
+      <c r="F20" s="61" t="inlineStr">
+        <is>
+          <t>稳定ID/路径不变；主体v005几何与灯帽不变；不改点击或玩法</t>
+        </is>
+      </c>
+      <c r="G20" s="61" t="inlineStr">
+        <is>
+          <t>CodeBuddy</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3D-道具'!$A$4:$P$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
@@ -652,7 +652,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -948,6 +948,9 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1497,22 +1500,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="51">
       <c r="A6" s="56">
-        <f>COUNTA('资产主表'!$A$6:$A$27)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$30)</f>
         <v/>
       </c>
       <c r="B6" s="54" t="n"/>
       <c r="C6" s="56">
-        <f>COUNTIF('资产主表'!$K$6:$K$27,"已完成")+COUNTIF('资产主表'!$K$6:$K$27,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$27,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$27,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$27,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$27,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$27,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$30,"已完成")+COUNTIF('资产主表'!$K$6:$K$30,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$30,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$30,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$30,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$30,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$30,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="54" t="n"/>
       <c r="E6" s="56">
-        <f>COUNTIF('资产主表'!$K$6:$K$27,"待制作")+COUNTIF('资产主表'!$K$6:$K$27,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$30,"待制作")+COUNTIF('资产主表'!$K$6:$K$30,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="54" t="n"/>
       <c r="G6" s="56">
-        <f>COUNTIF('资产主表'!$S$6:$S$27,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$30,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="54" t="n"/>
@@ -1581,11 +1584,11 @@
         </is>
       </c>
       <c r="B10" s="61">
-        <f>COUNTIF('资产主表'!$C$6:$C$27,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$30,A10)</f>
         <v/>
       </c>
       <c r="C10" s="61">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$27=A10)*(('资产主表'!$K$6:$K$27="已完成")+('资产主表'!$K$6:$K$27="原型已接入")+('资产主表'!$K$6:$K$27="正式美术已接入")+('资产主表'!$K$6:$K$27="已优化并正式接入")+('资产主表'!$K$6:$K$27="Blender源已完成")+('资产主表'!$K$6:$K$27="已导入；优化完成")+('资产主表'!$K$6:$K$27="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$30=A10)*(('资产主表'!$K$6:$K$30="已完成")+('资产主表'!$K$6:$K$30="原型已接入")+('资产主表'!$K$6:$K$30="正式美术已接入")+('资产主表'!$K$6:$K$30="已优化并正式接入")+('资产主表'!$K$6:$K$30="Blender源已完成")+('资产主表'!$K$6:$K$30="已导入；优化完成")+('资产主表'!$K$6:$K$30="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="61" t="n"/>
@@ -1603,11 +1606,11 @@
         </is>
       </c>
       <c r="B11" s="57">
-        <f>COUNTIF('资产主表'!$C$6:$C$27,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$30,A11)</f>
         <v/>
       </c>
       <c r="C11" s="57">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$27=A11)*(('资产主表'!$K$6:$K$27="已完成")+('资产主表'!$K$6:$K$27="原型已接入")+('资产主表'!$K$6:$K$27="正式美术已接入")+('资产主表'!$K$6:$K$27="已优化并正式接入")+('资产主表'!$K$6:$K$27="Blender源已完成")+('资产主表'!$K$6:$K$27="已导入；优化完成")+('资产主表'!$K$6:$K$27="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$30=A11)*(('资产主表'!$K$6:$K$30="已完成")+('资产主表'!$K$6:$K$30="原型已接入")+('资产主表'!$K$6:$K$30="正式美术已接入")+('资产主表'!$K$6:$K$30="已优化并正式接入")+('资产主表'!$K$6:$K$30="Blender源已完成")+('资产主表'!$K$6:$K$30="已导入；优化完成")+('资产主表'!$K$6:$K$30="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="57" t="n"/>
@@ -1854,6 +1857,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="51">
       <c r="A5" s="57" t="inlineStr">
         <is>
@@ -2175,7 +2179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="50" min="1" max="1"/>
@@ -2451,7 +2455,7 @@
         <v/>
       </c>
       <c r="S6" s="62">
-        <f>IF(COUNTIF($R$6:$R$27,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="62" t="n"/>
@@ -2554,7 +2558,7 @@
         <v/>
       </c>
       <c r="S7" s="62">
-        <f>IF(COUNTIF($R$6:$R$27,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="62" t="n"/>
@@ -2657,7 +2661,7 @@
         <v/>
       </c>
       <c r="S8" s="62">
-        <f>IF(COUNTIF($R$6:$R$27,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="62" t="n"/>
@@ -2760,7 +2764,7 @@
         <v/>
       </c>
       <c r="S9" s="62">
-        <f>IF(COUNTIF($R$6:$R$27,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="62" t="n"/>
@@ -2867,7 +2871,7 @@
         <v/>
       </c>
       <c r="S10" s="62">
-        <f>IF(COUNTIF($R$6:$R$27,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="75" t="inlineStr">
@@ -2984,7 +2988,7 @@
         <v/>
       </c>
       <c r="S11" s="62">
-        <f>IF(COUNTIF($R$6:$R$27,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="75" t="inlineStr">
@@ -3105,7 +3109,7 @@
         <v/>
       </c>
       <c r="S12" s="62">
-        <f>IF(COUNTIF($R$6:$R$27,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="75" t="inlineStr">
@@ -3226,7 +3230,7 @@
         <v/>
       </c>
       <c r="S13" s="62">
-        <f>IF(COUNTIF($R$6:$R$27,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="75" t="inlineStr">
@@ -3268,7 +3272,7 @@
       </c>
       <c r="B14" s="54" t="inlineStr">
         <is>
-          <t>可装备背包3D占位模型</t>
+          <t>可装备背包3D资产族</t>
         </is>
       </c>
       <c r="C14" s="54" t="inlineStr">
@@ -3299,7 +3303,7 @@
       </c>
       <c r="I14" s="78" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>asset_family / tier_0_static</t>
         </is>
       </c>
       <c r="J14" s="54" t="inlineStr">
@@ -3309,7 +3313,7 @@
       </c>
       <c r="K14" s="54" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>design_only</t>
         </is>
       </c>
       <c r="L14" s="78" t="inlineStr">
@@ -3324,7 +3328,7 @@
       </c>
       <c r="N14" s="78" t="inlineStr">
         <is>
-          <t>BoxMesh组件；2/4/8格三档体积、主色与1/2/3附袋</t>
+          <t>资产族索引；小/中/大三款各自独立源、GLB和PackedScene；非独立几何</t>
         </is>
       </c>
       <c r="O14" s="78" t="n"/>
@@ -3343,7 +3347,7 @@
         <v/>
       </c>
       <c r="S14" s="54">
-        <f>IF(COUNTIF($R$6:$R$27,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="78" t="n"/>
@@ -3352,8 +3356,8 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V14" s="78" t="n">
-        <v>46240</v>
+      <c r="V14" s="102" t="n">
+        <v>46303</v>
       </c>
       <c r="W14" s="54" t="inlineStr">
         <is>
@@ -3367,7 +3371,7 @@
       </c>
       <c r="Y14" s="54" t="inlineStr">
         <is>
-          <t>同一模型工厂服务equipment_backpack_2/4/8，避免世界物、UI图标和背部表现重复资产；无玩法碰撞，正式模型完成前保持程序占位状态。</t>
+          <t>保留原AssetID与equipment_backpack逻辑族；三款子资产通过G列归属；父项无生产路径和SHA，不再冒充程序几何。</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3466,7 @@
         <v/>
       </c>
       <c r="S15" s="80">
-        <f>IF(COUNTIF($R$6:$R$27,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="81" t="inlineStr">
@@ -3588,7 +3592,7 @@
         <v/>
       </c>
       <c r="S16" s="80">
-        <f>IF(COUNTIF($R$6:$R$27,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="81" t="inlineStr">
@@ -3714,7 +3718,7 @@
         <v/>
       </c>
       <c r="S17" s="80">
-        <f>IF(COUNTIF($R$6:$R$27,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="81" t="inlineStr">
@@ -3836,7 +3840,7 @@
         <v/>
       </c>
       <c r="S18" s="80">
-        <f>IF(COUNTIF($R$6:$R$27,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="81" t="inlineStr">
@@ -3961,7 +3965,7 @@
         <v/>
       </c>
       <c r="S19" s="80">
-        <f>IF(COUNTIF($R$6:$R$27,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="81" t="inlineStr">
@@ -4090,7 +4094,7 @@
         <v/>
       </c>
       <c r="S20" s="50">
-        <f>IF(COUNTIF($R$6:$R$27,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="83" t="inlineStr">
@@ -4213,7 +4217,7 @@
         <v/>
       </c>
       <c r="S21" s="50">
-        <f>IF(COUNTIF($R$6:$R$27,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="83" t="inlineStr">
@@ -4336,7 +4340,7 @@
         <v/>
       </c>
       <c r="S22" s="50">
-        <f>IF(COUNTIF($R$6:$R$27,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="83" t="inlineStr">
@@ -4459,7 +4463,7 @@
         <v/>
       </c>
       <c r="S23" s="50">
-        <f>IF(COUNTIF($R$6:$R$27,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="83" t="inlineStr">
@@ -4582,7 +4586,7 @@
         <v/>
       </c>
       <c r="S24" s="50">
-        <f>IF(COUNTIF($R$6:$R$27,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="83" t="inlineStr">
@@ -4705,7 +4709,7 @@
         <v/>
       </c>
       <c r="S25" s="50">
-        <f>IF(COUNTIF($R$6:$R$27,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="83" t="inlineStr">
@@ -4824,7 +4828,7 @@
         <v/>
       </c>
       <c r="S26" s="80">
-        <f>IF(COUNTIF($R$6:$R$27,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="81" t="inlineStr">
@@ -4943,7 +4947,7 @@
         <v/>
       </c>
       <c r="S27" s="80">
-        <f>IF(COUNTIF($R$6:$R$27,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="81" t="inlineStr">
@@ -4972,6 +4976,351 @@
       <c r="Y27" s="80" t="inlineStr">
         <is>
           <t>v005局部状态灯深化；旧v004源/优化保留；顶面偏前侧12边凸帽直径0.2m；599面/1190三角；结构/UV/公共色盘与交互结果详见当前final_acceptance；正常玩家及全阁楼红绿可辨门禁=True，像素详见pixel_metrics_runtime.json；音乐/摆位/范围外几何不变；GLB SHA-256=0b2cf2fcba9832ce8b37b62185e016f294ee834555439b71b11c543e0244851d；source SHA-256=d707298407d52dd5ce36c7f6de3fdef71dcfbfdac986cadf6d250318a3628a12；optimized SHA-256=448f30da74d0e118a032842e9eed2d49e8befcfcce24cb6f386547011b492ec1 【runtime v005.1】主体模型v005未重做；收音机持有MusicNotes持续视觉附件；验收=outputs/base99_radio_music_notes/final_acceptance.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="64" customHeight="1" s="51">
+      <c r="A28" s="78" t="inlineStr">
+        <is>
+          <t>ITM-EQUIPMENT-BACKPACK-SMALL-3D</t>
+        </is>
+      </c>
+      <c r="B28" s="54" t="inlineStr">
+        <is>
+          <t>小号粉色圆顶背包</t>
+        </is>
+      </c>
+      <c r="C28" s="54" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D28" s="78" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E28" s="78" t="inlineStr">
+        <is>
+          <t>equipment_backpack_2</t>
+        </is>
+      </c>
+      <c r="F28" s="78" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G28" s="78" t="inlineStr">
+        <is>
+          <t>ITM-EQUIPMENT-BACKPACK-3D</t>
+        </is>
+      </c>
+      <c r="H28" s="54" t="inlineStr">
+        <is>
+          <t>俯视3D / local +Z正面</t>
+        </is>
+      </c>
+      <c r="I28" s="78" t="inlineStr">
+        <is>
+          <t>tier_0_static</t>
+        </is>
+      </c>
+      <c r="J28" s="54" t="inlineStr">
+        <is>
+          <t>仅表现；地面拾取/UI图标/角色BackpackSocket共用；容量和存档规则不变</t>
+        </is>
+      </c>
+      <c r="K28" s="54" t="inlineStr">
+        <is>
+          <t>待制作</t>
+        </is>
+      </c>
+      <c r="L28" s="78" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="M28" s="78" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N28" s="78" t="inlineStr">
+        <is>
+          <t>0.56×0.28×0.60m；整包中心原点；&lt;=500三角；无背部肩带；场景四材质/公共色盘</t>
+        </is>
+      </c>
+      <c r="O28" s="78" t="n"/>
+      <c r="P28" s="78" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; tests/verification/verify_backpack_equipment_flow.tscn</t>
+        </is>
+      </c>
+      <c r="Q28" s="54" t="inlineStr">
+        <is>
+          <t>backpack;小号粉色圆顶背包</t>
+        </is>
+      </c>
+      <c r="R28" s="78">
+        <f>LOWER(TRIM(C28)&amp;"|"&amp;TRIM(D28)&amp;"|"&amp;TRIM(E28)&amp;"|"&amp;TRIM(F28)&amp;"|"&amp;TRIM(H28)&amp;"|"&amp;TRIM(I28))</f>
+        <v/>
+      </c>
+      <c r="S28" s="54">
+        <f>IF(COUNTIF($R$6:$R$30,R28)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T28" s="78" t="n"/>
+      <c r="U28" s="78" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+      <c r="V28" s="102" t="n">
+        <v>46303</v>
+      </c>
+      <c r="W28" s="54" t="inlineStr">
+        <is>
+          <t>用户参考图重建；项目公共色盘</t>
+        </is>
+      </c>
+      <c r="X28" s="77" t="inlineStr">
+        <is>
+          <t>PRP_小号粉色圆顶背包_中文资产管理</t>
+        </is>
+      </c>
+      <c r="Y28" s="54" t="inlineStr">
+        <is>
+          <t>新增身份，非历史已有ID；尺寸经用户批准；静态闭合表现；以asset_contract.json冻结。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="64" customHeight="1" s="51">
+      <c r="A29" s="78" t="inlineStr">
+        <is>
+          <t>ITM-EQUIPMENT-BACKPACK-MEDIUM-3D</t>
+        </is>
+      </c>
+      <c r="B29" s="54" t="inlineStr">
+        <is>
+          <t>中号黄色单扣背包</t>
+        </is>
+      </c>
+      <c r="C29" s="54" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D29" s="78" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E29" s="78" t="inlineStr">
+        <is>
+          <t>equipment_backpack_4</t>
+        </is>
+      </c>
+      <c r="F29" s="78" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G29" s="78" t="inlineStr">
+        <is>
+          <t>ITM-EQUIPMENT-BACKPACK-3D</t>
+        </is>
+      </c>
+      <c r="H29" s="54" t="inlineStr">
+        <is>
+          <t>俯视3D / local +Z正面</t>
+        </is>
+      </c>
+      <c r="I29" s="78" t="inlineStr">
+        <is>
+          <t>tier_0_static</t>
+        </is>
+      </c>
+      <c r="J29" s="54" t="inlineStr">
+        <is>
+          <t>仅表现；地面拾取/UI图标/角色BackpackSocket共用；容量和存档规则不变</t>
+        </is>
+      </c>
+      <c r="K29" s="54" t="inlineStr">
+        <is>
+          <t>待制作</t>
+        </is>
+      </c>
+      <c r="L29" s="78" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="M29" s="78" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N29" s="78" t="inlineStr">
+        <is>
+          <t>0.66×0.33×0.74m；整包中心原点；&lt;=500三角；无背部肩带；场景四材质/公共色盘</t>
+        </is>
+      </c>
+      <c r="O29" s="78" t="n"/>
+      <c r="P29" s="78" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; tests/verification/verify_backpack_equipment_flow.tscn</t>
+        </is>
+      </c>
+      <c r="Q29" s="54" t="inlineStr">
+        <is>
+          <t>backpack;中号黄色单扣背包</t>
+        </is>
+      </c>
+      <c r="R29" s="78">
+        <f>LOWER(TRIM(C29)&amp;"|"&amp;TRIM(D29)&amp;"|"&amp;TRIM(E29)&amp;"|"&amp;TRIM(F29)&amp;"|"&amp;TRIM(H29)&amp;"|"&amp;TRIM(I29))</f>
+        <v/>
+      </c>
+      <c r="S29" s="54">
+        <f>IF(COUNTIF($R$6:$R$30,R29)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T29" s="78" t="n"/>
+      <c r="U29" s="78" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+      <c r="V29" s="102" t="n">
+        <v>46303</v>
+      </c>
+      <c r="W29" s="54" t="inlineStr">
+        <is>
+          <t>用户参考图重建；项目公共色盘</t>
+        </is>
+      </c>
+      <c r="X29" s="77" t="inlineStr">
+        <is>
+          <t>PRP_中号黄色单扣背包_中文资产管理</t>
+        </is>
+      </c>
+      <c r="Y29" s="54" t="inlineStr">
+        <is>
+          <t>新增身份，非历史已有ID；尺寸经用户批准；静态闭合表现；以asset_contract.json冻结。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="64" customHeight="1" s="51">
+      <c r="A30" s="78" t="inlineStr">
+        <is>
+          <t>ITM-EQUIPMENT-BACKPACK-LARGE-3D</t>
+        </is>
+      </c>
+      <c r="B30" s="54" t="inlineStr">
+        <is>
+          <t>大号青色卷铺盖背包</t>
+        </is>
+      </c>
+      <c r="C30" s="54" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D30" s="78" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E30" s="78" t="inlineStr">
+        <is>
+          <t>equipment_backpack_8</t>
+        </is>
+      </c>
+      <c r="F30" s="78" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G30" s="78" t="inlineStr">
+        <is>
+          <t>ITM-EQUIPMENT-BACKPACK-3D</t>
+        </is>
+      </c>
+      <c r="H30" s="54" t="inlineStr">
+        <is>
+          <t>俯视3D / local +Z正面</t>
+        </is>
+      </c>
+      <c r="I30" s="78" t="inlineStr">
+        <is>
+          <t>tier_0_static</t>
+        </is>
+      </c>
+      <c r="J30" s="54" t="inlineStr">
+        <is>
+          <t>仅表现；地面拾取/UI图标/角色BackpackSocket共用；容量和存档规则不变</t>
+        </is>
+      </c>
+      <c r="K30" s="54" t="inlineStr">
+        <is>
+          <t>待制作</t>
+        </is>
+      </c>
+      <c r="L30" s="78" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="M30" s="78" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N30" s="78" t="inlineStr">
+        <is>
+          <t>0.76×0.38×0.88m；整包中心原点；&lt;=500三角；无背部肩带；场景四材质/公共色盘</t>
+        </is>
+      </c>
+      <c r="O30" s="78" t="n"/>
+      <c r="P30" s="78" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; tests/verification/verify_backpack_equipment_flow.tscn</t>
+        </is>
+      </c>
+      <c r="Q30" s="54" t="inlineStr">
+        <is>
+          <t>backpack;大号青色卷铺盖背包</t>
+        </is>
+      </c>
+      <c r="R30" s="78">
+        <f>LOWER(TRIM(C30)&amp;"|"&amp;TRIM(D30)&amp;"|"&amp;TRIM(E30)&amp;"|"&amp;TRIM(F30)&amp;"|"&amp;TRIM(H30)&amp;"|"&amp;TRIM(I30))</f>
+        <v/>
+      </c>
+      <c r="S30" s="54">
+        <f>IF(COUNTIF($R$6:$R$30,R30)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T30" s="78" t="n"/>
+      <c r="U30" s="78" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+      <c r="V30" s="102" t="n">
+        <v>46303</v>
+      </c>
+      <c r="W30" s="54" t="inlineStr">
+        <is>
+          <t>用户参考图重建；项目公共色盘</t>
+        </is>
+      </c>
+      <c r="X30" s="77" t="inlineStr">
+        <is>
+          <t>PRP_大号青色卷铺盖背包_中文资产管理</t>
+        </is>
+      </c>
+      <c r="Y30" s="54" t="inlineStr">
+        <is>
+          <t>新增身份，非历史已有ID；尺寸经用户批准；静态闭合表现；以asset_contract.json冻结。</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5532,7 @@
     <row r="427" ht="84.75" customHeight="1" s="51"/>
     <row r="429" ht="120" customHeight="1" s="51"/>
   </sheetData>
-  <autoFilter ref="A5:X27"/>
+  <autoFilter ref="A5:Y30"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
@@ -5202,15 +5551,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K6:K27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L6:L27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5264,6 +5613,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="51">
       <c r="A4" s="86" t="inlineStr">
         <is>
@@ -5691,7 +6041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="35.81" customWidth="1" style="50" min="1" max="1"/>
@@ -5721,10 +6071,11 @@
     <row r="2" ht="33.75" customHeight="1" s="51">
       <c r="A2" s="85" t="inlineStr">
         <is>
-          <t>拥有独立PackedScene的拾取物、消耗品、钥匙和掉落物；本次扫描 0 个独立Prefab。</t>
-        </is>
-      </c>
-    </row>
+          <t>独立物品PackedScene；3款背包已登记，等待制作与验收。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="51">
       <c r="A4" s="86" t="inlineStr">
         <is>
@@ -5804,6 +6155,252 @@
       <c r="P4" s="89" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="64" customHeight="1" s="51">
+      <c r="A5" s="86" t="inlineStr">
+        <is>
+          <t>ITM-EQUIPMENT-BACKPACK-SMALL-3D</t>
+        </is>
+      </c>
+      <c r="B5" s="87" t="inlineStr">
+        <is>
+          <t>小号粉色圆顶背包</t>
+        </is>
+      </c>
+      <c r="C5" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/backpack_small/runtime/prp_backpack_small_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D5" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/backpack_small/components/prp_backpack_small_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E5" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/backpack_small/source/prp_backpack_small_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F5" s="87" t="inlineStr">
+        <is>
+          <t>仅表现；地面拾取/UI图标/角色BackpackSocket共用；容量和存档规则不变</t>
+        </is>
+      </c>
+      <c r="G5" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd</t>
+        </is>
+      </c>
+      <c r="H5" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I5" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J5" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K5" s="87" t="inlineStr">
+        <is>
+          <t>0.56×0.28×0.60m</t>
+        </is>
+      </c>
+      <c r="L5" s="87" t="inlineStr">
+        <is>
+          <t>整包包围盒中心原点；Godot +Z前袋朝外，+Y向上；Blender -Y前袋朝外，+Z向上</t>
+        </is>
+      </c>
+      <c r="M5" s="87" t="inlineStr">
+        <is>
+          <t>世界掉落/UI图标/玩家BackpackSocket</t>
+        </is>
+      </c>
+      <c r="N5" s="87" t="inlineStr">
+        <is>
+          <t>待制作</t>
+        </is>
+      </c>
+      <c r="O5" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P5" s="89" t="inlineStr">
+        <is>
+          <t>真实PackedScene骨架已创建；视觉制作及验收待完成；禁止视为正式资产。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1" s="51">
+      <c r="A6" s="86" t="inlineStr">
+        <is>
+          <t>ITM-EQUIPMENT-BACKPACK-MEDIUM-3D</t>
+        </is>
+      </c>
+      <c r="B6" s="87" t="inlineStr">
+        <is>
+          <t>中号黄色单扣背包</t>
+        </is>
+      </c>
+      <c r="C6" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/backpack_medium/runtime/prp_backpack_medium_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D6" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/backpack_medium/components/prp_backpack_medium_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E6" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/backpack_medium/source/prp_backpack_medium_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F6" s="87" t="inlineStr">
+        <is>
+          <t>仅表现；地面拾取/UI图标/角色BackpackSocket共用；容量和存档规则不变</t>
+        </is>
+      </c>
+      <c r="G6" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd</t>
+        </is>
+      </c>
+      <c r="H6" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I6" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J6" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K6" s="87" t="inlineStr">
+        <is>
+          <t>0.66×0.33×0.74m</t>
+        </is>
+      </c>
+      <c r="L6" s="87" t="inlineStr">
+        <is>
+          <t>整包包围盒中心原点；Godot +Z前袋朝外，+Y向上；Blender -Y前袋朝外，+Z向上</t>
+        </is>
+      </c>
+      <c r="M6" s="87" t="inlineStr">
+        <is>
+          <t>世界掉落/UI图标/玩家BackpackSocket</t>
+        </is>
+      </c>
+      <c r="N6" s="87" t="inlineStr">
+        <is>
+          <t>待制作</t>
+        </is>
+      </c>
+      <c r="O6" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P6" s="89" t="inlineStr">
+        <is>
+          <t>真实PackedScene骨架已创建；视觉制作及验收待完成；禁止视为正式资产。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1" s="51">
+      <c r="A7" s="86" t="inlineStr">
+        <is>
+          <t>ITM-EQUIPMENT-BACKPACK-LARGE-3D</t>
+        </is>
+      </c>
+      <c r="B7" s="87" t="inlineStr">
+        <is>
+          <t>大号青色卷铺盖背包</t>
+        </is>
+      </c>
+      <c r="C7" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/backpack_large/runtime/prp_backpack_large_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D7" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/backpack_large/components/prp_backpack_large_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E7" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/backpack_large/source/prp_backpack_large_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F7" s="87" t="inlineStr">
+        <is>
+          <t>仅表现；地面拾取/UI图标/角色BackpackSocket共用；容量和存档规则不变</t>
+        </is>
+      </c>
+      <c r="G7" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd</t>
+        </is>
+      </c>
+      <c r="H7" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I7" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J7" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K7" s="87" t="inlineStr">
+        <is>
+          <t>0.76×0.38×0.88m</t>
+        </is>
+      </c>
+      <c r="L7" s="87" t="inlineStr">
+        <is>
+          <t>整包包围盒中心原点；Godot +Z前袋朝外，+Y向上；Blender -Y前袋朝外，+Z向上</t>
+        </is>
+      </c>
+      <c r="M7" s="87" t="inlineStr">
+        <is>
+          <t>世界掉落/UI图标/玩家BackpackSocket</t>
+        </is>
+      </c>
+      <c r="N7" s="87" t="inlineStr">
+        <is>
+          <t>待制作</t>
+        </is>
+      </c>
+      <c r="O7" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P7" s="89" t="inlineStr">
+        <is>
+          <t>真实PackedScene骨架已创建；视觉制作及验收待完成；禁止视为正式资产。</t>
         </is>
       </c>
     </row>
@@ -5838,7 +6435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="50" min="1" max="1"/>
@@ -6454,6 +7051,80 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="64" customHeight="1" s="51">
+      <c r="A21" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.15</t>
+        </is>
+      </c>
+      <c r="B21" s="68" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C21" s="61" t="inlineStr">
+        <is>
+          <t>三款无肩带背包：register</t>
+        </is>
+      </c>
+      <c r="D21" s="61" t="inlineStr">
+        <is>
+          <t>道具 / equipment</t>
+        </is>
+      </c>
+      <c r="E21" s="61" t="inlineStr">
+        <is>
+          <t>ITM-EQUIPMENT-BACKPACK-SMALL-3D,ITM-EQUIPMENT-BACKPACK-MEDIUM-3D,ITM-EQUIPMENT-BACKPACK-LARGE-3D</t>
+        </is>
+      </c>
+      <c r="F21" s="61" t="inlineStr">
+        <is>
+          <t>仅授权背包；其他资产内容和指纹不变。</t>
+        </is>
+      </c>
+      <c r="G21" s="61" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="64" customHeight="1" s="51">
+      <c r="A22" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.16</t>
+        </is>
+      </c>
+      <c r="B22" s="68" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C22" s="61" t="inlineStr">
+        <is>
+          <t>三款无肩带背包：prefab</t>
+        </is>
+      </c>
+      <c r="D22" s="61" t="inlineStr">
+        <is>
+          <t>道具 / equipment</t>
+        </is>
+      </c>
+      <c r="E22" s="61" t="inlineStr">
+        <is>
+          <t>ITM-EQUIPMENT-BACKPACK-SMALL-3D,ITM-EQUIPMENT-BACKPACK-MEDIUM-3D,ITM-EQUIPMENT-BACKPACK-LARGE-3D</t>
+        </is>
+      </c>
+      <c r="F22" s="61" t="inlineStr">
+        <is>
+          <t>仅授权背包；其他资产内容和指纹不变。</t>
+        </is>
+      </c>
+      <c r="G22" s="61" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3D-道具" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3D-物品" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="域变更日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$30</definedName>
@@ -652,7 +652,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -951,6 +951,9 @@
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
       <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1857,7 +1860,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="51">
       <c r="A5" s="57" t="inlineStr">
         <is>
@@ -4924,7 +4926,7 @@
       </c>
       <c r="N27" s="80" t="inlineStr">
         <is>
-          <t>宽0.828m × 深0.456m × 高0.822m；599面/1190三角形&lt;800面；机身铜橙金属、天线与提手等范围外几何签名保持；单根三节斜金属天线29.35度；四材质公共色盘外链/PaletteUV/Closest；StatusLight为顶面偏前侧12边低模凸帽，直径0.2m，替换旧灯且不重复，避开提手/天线；off红常亮、A/B同绿常亮、离开99F红待机；发光能量1.5；ItemRoot/Visual/ItemRoot/StatusLight实际导入路径稳定；左键/E关→A→B→关及Music逻辑不变；root scale=1，bounds不变；可见性门禁=True；原生1280x720像素证据=outputs/base99_radio_v005/pixel_metrics_runtime.json。 runtime v005.1：模型/Blender/GLB保持v005；新增独立VFX音符附件，预算另计。独立radio child纯视觉持续附件；5预制QuadMesh槽位/10三角形；Godot生成四分/八分/双八分音符纹理，无字体依赖；billboard当前相机；淡青绿/暖金unshaded无emission；2.5发/s、寿命1.8s、上飘1.1m、横摆0.09m、尺度0.88~1.06、淡入0.16s、末0.45s淡出；本地挂点Y1.42m；无碰撞/灯光/音频；真实playing驱动，A/B连续，off/离99/exit同步清空；不进任何战斗池。</t>
+          <t>宽0.828m × 深0.456m × 高0.822m；599面/1190三角形&lt;800面；机身铜橙金属、天线与提手等范围外几何签名保持；单根三节斜金属天线29.35度；四材质公共色盘外链/PaletteUV/Closest；StatusLight为顶面偏前侧12边低模凸帽，直径0.2m，替换旧灯且不重复，避开提手/天线；off红常亮、A/B同绿常亮、离开99F红待机；发光能量1.5；ItemRoot/Visual/ItemRoot/StatusLight实际导入路径稳定；左键/E关→A→B→关及Music逻辑不变；root scale=1，bounds不变；可见性门禁=True；原生1280x720像素证据=outputs/base99_radio_v005/pixel_metrics_runtime.json。 runtime v005.1：模型/Blender/GLB保持v005；新增独立VFX音符附件，预算另计。独立radio child纯视觉持续附件；5预制QuadMesh槽位/10三角形；Godot生成四分/八分/双八分音符纹理，无字体依赖；billboard当前相机；淡青绿/暖金unshaded无emission；2.5发/s、寿命1.8s、上飘1.1m、横摆0.09m、尺度0.88~1.06、淡入0.16s、末0.45s淡出；本地挂点Y1.42m；无碰撞/灯光/音频；真实playing驱动，A/B连续，off/离99/exit同步清空；不进任何战斗池。 空间声音契约v001：唯一AudioStreamPlayer3D；Music总线；unit_size=18.0m；max_distance=78.0m；attenuation_model=inverse_square；99F正式边界Rect2(-50,-35,100,80)内source volume=0dB；边界外起始-18dB并按4dB/m继续衰减，最低-42dB；不复制播放；收音机离开99F停播/返回后手动开启，模型摆位、音符表现与音乐控制不变。</t>
         </is>
       </c>
       <c r="O27" s="81" t="inlineStr">
@@ -4975,7 +4977,7 @@
       </c>
       <c r="Y27" s="80" t="inlineStr">
         <is>
-          <t>v005局部状态灯深化；旧v004源/优化保留；顶面偏前侧12边凸帽直径0.2m；599面/1190三角；结构/UV/公共色盘与交互结果详见当前final_acceptance；正常玩家及全阁楼红绿可辨门禁=True，像素详见pixel_metrics_runtime.json；音乐/摆位/范围外几何不变；GLB SHA-256=0b2cf2fcba9832ce8b37b62185e016f294ee834555439b71b11c543e0244851d；source SHA-256=d707298407d52dd5ce36c7f6de3fdef71dcfbfdac986cadf6d250318a3628a12；optimized SHA-256=448f30da74d0e118a032842e9eed2d49e8befcfcce24cb6f386547011b492ec1 【runtime v005.1】主体模型v005未重做；收音机持有MusicNotes持续视觉附件；验收=outputs/base99_radio_music_notes/final_acceptance.json</t>
+          <t>v005局部状态灯深化；旧v004源/优化保留；顶面偏前侧12边凸帽直径0.2m；599面/1190三角；结构/UV/公共色盘与交互结果详见当前final_acceptance；正常玩家及全阁楼红绿可辨门禁=True，像素详见pixel_metrics_runtime.json；音乐/摆位/范围外几何不变；GLB SHA-256=0b2cf2fcba9832ce8b37b62185e016f294ee834555439b71b11c543e0244851d；source SHA-256=d707298407d52dd5ce36c7f6de3fdef71dcfbfdac986cadf6d250318a3628a12；optimized SHA-256=448f30da74d0e118a032842e9eed2d49e8befcfcce24cb6f386547011b492ec1 【runtime v005.1】主体模型v005未重做；收音机持有MusicNotes持续视觉附件；验收=outputs/base99_radio_music_notes/final_acceptance.json；空间声音契约v001：唯一AudioStreamPlayer3D；Music总线；unit_size=18.0m；max_distance=78.0m；attenuation_model=inverse_square；99F正式边界Rect2(-50,-35,100,80)内source volume=0dB；边界外起始-18dB并按4dB/m继续衰减，最低-42dB；不复制播放；收音机离开99F停播/返回后手动开启，模型摆位、音符表现与音乐控制不变。 验收=outputs/base99_radio_sound_v001/sound_acceptance.json。</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5615,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="51">
       <c r="A4" s="86" t="inlineStr">
         <is>
@@ -5979,7 +5980,7 @@
       </c>
       <c r="K8" s="95" t="inlineStr">
         <is>
-          <t>宽0.828m × 深0.456m × 高0.822m；599面/1190三角形&lt;800面；机身铜橙金属、天线与提手等范围外几何签名保持；单根三节斜金属天线29.35度；四材质公共色盘外链/PaletteUV/Closest；StatusLight为顶面偏前侧12边低模凸帽，直径0.2m，替换旧灯且不重复，避开提手/天线；off红常亮、A/B同绿常亮、离开99F红待机；发光能量1.5；ItemRoot/Visual/ItemRoot/StatusLight实际导入路径稳定；左键/E关→A→B→关及Music逻辑不变；root scale=1，bounds不变；可见性门禁=True；原生1280x720像素证据=outputs/base99_radio_v005/pixel_metrics_runtime.json。 runtime补丁：独立radio child纯视觉持续附件；5预制QuadMesh槽位/10三角形；Godot生成四分/八分/双八分音符纹理，无字体依赖；billboard当前相机；淡青绿/暖金unshaded无emission；2.5发/s、寿命1.8s、上飘1.1m、横摆0.09m、尺度0.88~1.06、淡入0.16s、末0.45s淡出；本地挂点Y1.42m；无碰撞/灯光/音频；真实playing驱动，A/B连续，off/离99/exit同步清空；不进任何战斗池。</t>
+          <t>宽0.828m × 深0.456m × 高0.822m；599面/1190三角形&lt;800面；机身铜橙金属、天线与提手等范围外几何签名保持；单根三节斜金属天线29.35度；四材质公共色盘外链/PaletteUV/Closest；StatusLight为顶面偏前侧12边低模凸帽，直径0.2m，替换旧灯且不重复，避开提手/天线；off红常亮、A/B同绿常亮、离开99F红待机；发光能量1.5；ItemRoot/Visual/ItemRoot/StatusLight实际导入路径稳定；左键/E关→A→B→关及Music逻辑不变；root scale=1，bounds不变；可见性门禁=True；原生1280x720像素证据=outputs/base99_radio_v005/pixel_metrics_runtime.json。 runtime补丁：独立radio child纯视觉持续附件；5预制QuadMesh槽位/10三角形；Godot生成四分/八分/双八分音符纹理，无字体依赖；billboard当前相机；淡青绿/暖金unshaded无emission；2.5发/s、寿命1.8s、上飘1.1m、横摆0.09m、尺度0.88~1.06、淡入0.16s、末0.45s淡出；本地挂点Y1.42m；无碰撞/灯光/音频；真实playing驱动，A/B连续，off/离99/exit同步清空；不进任何战斗池。；空间声音契约v001：唯一AudioStreamPlayer3D；Music总线；unit_size=18.0m；max_distance=78.0m；attenuation_model=inverse_square；99F正式边界Rect2(-50,-35,100,80)内source volume=0dB；边界外起始-18dB并按4dB/m继续衰减，最低-42dB；不复制播放；收音机离开99F停播/返回后手动开启，模型摆位、音符表现与音乐控制不变。</t>
         </is>
       </c>
       <c r="L8" s="96" t="inlineStr">
@@ -6004,7 +6005,7 @@
       </c>
       <c r="P8" s="97" t="inlineStr">
         <is>
-          <t>ItemRoot/Visual/StatusLight接口不变；StatusLight顶面偏前侧12边低模凸帽；单一灯，无billboard/UI/bloom；源=d707298407d52dd5ce36c7f6de3fdef71dcfbfdac986cadf6d250318a3628a12；优化=448f30da74d0e118a032842e9eed2d49e8befcfcce24cb6f386547011b492ec1；GLB=0b2cf2fcba9832ce8b37b62185e016f294ee834555439b71b11c543e0244851d；Prefab=97b35c66bd00f9662a12f8b8359023c4cf714bd9e434cb804c20bf9ea83ee90c；证据=outputs/base99_radio_v005/；runtime v005.1，model v005；附件=VFX-RADIO-MUSIC-NOTES-3D；Prefab SHA=0f60c1333330feaaef984b64539c73d284fd13fd3b89cd3df5497394c85442ca</t>
+          <t>ItemRoot/Visual/StatusLight接口不变；StatusLight顶面偏前侧12边低模凸帽；单一灯，无billboard/UI/bloom；源=d707298407d52dd5ce36c7f6de3fdef71dcfbfdac986cadf6d250318a3628a12；优化=448f30da74d0e118a032842e9eed2d49e8befcfcce24cb6f386547011b492ec1；GLB=0b2cf2fcba9832ce8b37b62185e016f294ee834555439b71b11c543e0244851d；Prefab=97b35c66bd00f9662a12f8b8359023c4cf714bd9e434cb804c20bf9ea83ee90c；证据=outputs/base99_radio_v005/；runtime v005.1，model v005；附件=VFX-RADIO-MUSIC-NOTES-3D；Prefab SHA=0f60c1333330feaaef984b64539c73d284fd13fd3b89cd3df5497394c85442ca；空间声音契约=空间声音契约v001：唯一AudioStreamPlayer3D；Music总线；unit_size=18.0m；max_distance=78.0m；attenuation_model=inverse_square；99F正式边界Rect2(-50,-35,100,80)内source volume=0dB；边界外起始-18dB并按4dB/m继续衰减，最低-42dB；不复制播放；收音机离开99F停播/返回后手动开启，模型摆位、音符表现与音乐控制不变。；验收=outputs/base99_radio_sound_v001/sound_acceptance.json；账本证据=outputs/base99_radio_sound_v001/ledger_evidence.json</t>
         </is>
       </c>
       <c r="Q8" s="50" t="n"/>
@@ -6075,7 +6076,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="51">
       <c r="A4" s="86" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="50" min="1" max="1"/>
@@ -6462,7 +6462,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="51">
       <c r="A5" s="57" t="inlineStr">
         <is>
@@ -7122,6 +7121,41 @@
       <c r="G22" s="61" t="inlineStr">
         <is>
           <t>WorkBuddy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.17</t>
+        </is>
+      </c>
+      <c r="B23" s="103" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C23" s="61" t="inlineStr">
+        <is>
+          <t>99F收音机空间声音v001</t>
+        </is>
+      </c>
+      <c r="D23" s="61" t="inlineStr">
+        <is>
+          <t>道具 / 场景可交互道具</t>
+        </is>
+      </c>
+      <c r="E23" s="61" t="inlineStr">
+        <is>
+          <t>PRP-BASE99-RADIO-3D runtime v005.1 增加可量化3D空间声音契约：空间声音契约v001：唯一AudioStreamPlayer3D；Music总线；unit_size=18.0m；max_distance=78.0m；attenuation_model=inverse_square；99F正式边界Rect2(-50,-35,100,80)内source volume=0dB；边界外起始-18dB并按4dB/m继续衰减，最低-42dB；不复制播放；收音机离开99F停播/返回后手动开启，模型摆位、音符表现与音乐控制不变。</t>
+        </is>
+      </c>
+      <c r="F23" s="61" t="inlineStr">
+        <is>
+          <t>仅更新资产主表第27行、3D-道具第8行、域变更日志和baseline；不改模型、摆位、音符表现、音乐控制或唯一AudioStreamPlayer3D结构。新sound test通过；原radio headless鼠标路径与music notes超时按原始日志单独记录。</t>
+        </is>
+      </c>
+      <c r="G23" s="61" t="inlineStr">
+        <is>
+          <t>CodeBuddy</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3D-道具" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="3D-物品" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="域变更日志" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$30</definedName>
@@ -1860,6 +1860,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="51">
       <c r="A5" s="57" t="inlineStr">
         <is>
@@ -3098,7 +3099,7 @@
       </c>
       <c r="P12" s="75" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/mission_operations/prp_base_mission_operations_source_v003.blend; src/base3d/BaseFacility3D.gd; src/world3d/TowerDescent3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/props/base_world_3d/source/mission_operations/prp_base_mission_operations_source_v003.blend; src/base3d/BaseFacility3D.gd; src/world3d/TowerDescent3D.gd</t>
         </is>
       </c>
       <c r="Q12" s="75" t="inlineStr">
@@ -3219,7 +3220,7 @@
       </c>
       <c r="P13" s="75" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/weapon_workshop/prp_base_weapon_workshop_source_v003.blend; src/base3d/BaseFacility3D.gd; src/world3d/TowerDescent3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/props/base_world_3d/source/weapon_workshop/prp_base_weapon_workshop_source_v003.blend; src/base3d/BaseFacility3D.gd; src/world3d/TowerDescent3D.gd</t>
         </is>
       </c>
       <c r="Q13" s="75" t="inlineStr">
@@ -3455,7 +3456,7 @@
       </c>
       <c r="P15" s="81" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/vending_machine/prp_base_vending_machine_source_v001.blend; src/base3d/BaseFacility3D.gd; src/world3d/TowerDescent3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/props/base_world_3d/source/vending_machine/prp_base_vending_machine_source_v001.blend; src/base3d/BaseFacility3D.gd; src/world3d/TowerDescent3D.gd</t>
         </is>
       </c>
       <c r="Q15" s="81" t="inlineStr">
@@ -5615,6 +5616,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="51">
       <c r="A4" s="86" t="inlineStr">
         <is>
@@ -5720,7 +5722,7 @@
       </c>
       <c r="E5" s="92" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/mission_command_chair/prp_base_mission_command_chair_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/props/base_world_3d/source/mission_command_chair/prp_base_mission_command_chair_source_v001.blend</t>
         </is>
       </c>
       <c r="F5" s="91" t="inlineStr">
@@ -5798,7 +5800,7 @@
       </c>
       <c r="E6" s="96" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/workshop_stool/prp_base_workshop_stool_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/props/base_world_3d/source/workshop_stool/prp_base_workshop_stool_source_v001.blend</t>
         </is>
       </c>
       <c r="F6" s="95" t="inlineStr">
@@ -6076,6 +6078,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="51">
       <c r="A4" s="86" t="inlineStr">
         <is>
@@ -6462,6 +6465,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="51">
       <c r="A5" s="57" t="inlineStr">
         <is>

--- a/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
@@ -3099,7 +3099,7 @@
       </c>
       <c r="P12" s="75" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/props/base_world_3d/source/mission_operations/prp_base_mission_operations_source_v003.blend; src/base3d/BaseFacility3D.gd; src/world3d/TowerDescent3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/props/base_world_3d/source/mission_operations/prp_base_mission_operations_source_v003.blend; src/base3d/BaseFacility3D.gd; src/world3d/TowerDescent3D.gd</t>
         </is>
       </c>
       <c r="Q12" s="75" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P13" s="75" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/props/base_world_3d/source/weapon_workshop/prp_base_weapon_workshop_source_v003.blend; src/base3d/BaseFacility3D.gd; src/world3d/TowerDescent3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/props/base_world_3d/source/weapon_workshop/prp_base_weapon_workshop_source_v003.blend; src/base3d/BaseFacility3D.gd; src/world3d/TowerDescent3D.gd</t>
         </is>
       </c>
       <c r="Q13" s="75" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="P15" s="81" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/props/base_world_3d/source/vending_machine/prp_base_vending_machine_source_v001.blend; src/base3d/BaseFacility3D.gd; src/world3d/TowerDescent3D.gd</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/props/base_world_3d/source/vending_machine/prp_base_vending_machine_source_v001.blend; src/base3d/BaseFacility3D.gd; src/world3d/TowerDescent3D.gd</t>
         </is>
       </c>
       <c r="Q15" s="81" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="P16" s="81" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/locker_station/prp_base_locker_station_source_v004.blend</t>
+          <t>art_source/props/base_world_3d/source/locker_station/prp_base_locker_station_source_v004.blend</t>
         </is>
       </c>
       <c r="Q16" s="81" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="P17" s="81" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/retro_tv_station/prp_base_retro_tv_station_source_v004.blend</t>
+          <t>art_source/props/base_world_3d/source/retro_tv_station/prp_base_retro_tv_station_source_v004.blend</t>
         </is>
       </c>
       <c r="Q17" s="81" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="P18" s="81" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/workshop_stool/prp_base_workshop_stool_source_v004.blend; assets/art/props/base_world_3d/components/workshop_stool/prp_base_workshop_stool_base_visual_v004.glb; assets/art/props/base_world_3d/components/workshop_stool/prp_base_workshop_stool_swivel_visual_v004.glb</t>
+          <t>art_source/props/base_world_3d/source/workshop_stool/prp_base_workshop_stool_source_v004.blend; assets/art/props/base_world_3d/components/workshop_stool/prp_base_workshop_stool_base_visual_v004.glb; assets/art/props/base_world_3d/components/workshop_stool/prp_base_workshop_stool_swivel_visual_v004.glb</t>
         </is>
       </c>
       <c r="Q18" s="81" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P19" s="81" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/mission_command_chair/prp_base_mission_command_chair_source_v004.blend; assets/art/props/base_world_3d/components/mission_command_chair/prp_base_mission_command_chair_base_visual_v004.glb; assets/art/props/base_world_3d/components/mission_command_chair/prp_base_mission_command_chair_swivel_visual_v004.glb</t>
+          <t>art_source/props/base_world_3d/source/mission_command_chair/prp_base_mission_command_chair_source_v004.blend; assets/art/props/base_world_3d/components/mission_command_chair/prp_base_mission_command_chair_base_visual_v004.glb; assets/art/props/base_world_3d/components/mission_command_chair/prp_base_mission_command_chair_swivel_visual_v004.glb</t>
         </is>
       </c>
       <c r="Q19" s="81" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P26" s="81" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/base99_telescopic_ladder/prp_base99_telescopic_ladder_source_v002.blend; assets/art/props/base_world_3d/components/base99_telescopic_ladder/prp_base99_telescopic_ladder_upper_visual_top3d.glb; assets/art/props/base_world_3d/components/base99_telescopic_ladder/prp_base99_telescopic_ladder_lower_visual_top3d.glb; src/base3d/Base99TelescopicLadder3D.gd; src/player3d/states/Player3DClimbingState.gd</t>
+          <t>art_source/props/base_world_3d/source/base99_telescopic_ladder/prp_base99_telescopic_ladder_source_v002.blend; assets/art/props/base_world_3d/components/base99_telescopic_ladder/prp_base99_telescopic_ladder_upper_visual_top3d.glb; assets/art/props/base_world_3d/components/base99_telescopic_ladder/prp_base99_telescopic_ladder_lower_visual_top3d.glb; src/base3d/Base99TelescopicLadder3D.gd; src/player3d/states/Player3DClimbingState.gd</t>
         </is>
       </c>
       <c r="Q26" s="81" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="P27" s="81" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v005.blend; assets/art/props/base_world_3d/source/base99_radio/export/v005/prp_base99_radio_optimized_v005.blend; assets/art/props/base_world_3d/components/base99_radio/prp_base99_radio_visual_top3d.glb; src/base3d/Base99Radio3D.gd; outputs/base99_radio_v005/asset_manifest.json; outputs/base99_radio_v005/final_acceptance.json; assets/art/vfx/environment_3d/radio_music_notes/vfx_radio_music_notes_root_top3d.tscn; src/vfx/VfxRadioMusicNotes3D.gd; tests/verification/verify_base99_radio_music_notes.tscn</t>
+          <t>art_source/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v005.blend; art_source/props/base_world_3d/source/base99_radio/export/v005/prp_base99_radio_optimized_v005.blend; assets/art/props/base_world_3d/components/base99_radio/prp_base99_radio_visual_top3d.glb; src/base3d/Base99Radio3D.gd; outputs/base99_radio_v005/asset_manifest.json; outputs/base99_radio_v005/final_acceptance.json; assets/art/vfx/environment_3d/radio_music_notes/vfx_radio_music_notes_root_top3d.tscn; src/vfx/VfxRadioMusicNotes3D.gd; tests/verification/verify_base99_radio_music_notes.tscn</t>
         </is>
       </c>
       <c r="Q27" s="81" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="E5" s="92" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/props/base_world_3d/source/mission_command_chair/prp_base_mission_command_chair_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/props/base_world_3d/source/mission_command_chair/prp_base_mission_command_chair_source_v001.blend</t>
         </is>
       </c>
       <c r="F5" s="91" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="E6" s="96" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/props/base_world_3d/source/workshop_stool/prp_base_workshop_stool_source_v001.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/props/base_world_3d/source/workshop_stool/prp_base_workshop_stool_source_v001.blend</t>
         </is>
       </c>
       <c r="F6" s="95" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="E8" s="96" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v005.blend</t>
+          <t>art_source/props/base_world_3d/source/base99_radio/prp_base99_radio_source_v005.blend</t>
         </is>
       </c>
       <c r="F8" s="95" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="E5" s="88" t="inlineStr">
         <is>
-          <t>assets/art/items_weapons/props/backpack_small/source/prp_backpack_small_source_v001.blend</t>
+          <t>art_source/items_weapons/props/backpack_small/source/prp_backpack_small_source_v001.blend</t>
         </is>
       </c>
       <c r="F5" s="87" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="E6" s="88" t="inlineStr">
         <is>
-          <t>assets/art/items_weapons/props/backpack_medium/source/prp_backpack_medium_source_v001.blend</t>
+          <t>art_source/items_weapons/props/backpack_medium/source/prp_backpack_medium_source_v001.blend</t>
         </is>
       </c>
       <c r="F6" s="87" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="E7" s="88" t="inlineStr">
         <is>
-          <t>assets/art/items_weapons/props/backpack_large/source/prp_backpack_large_source_v001.blend</t>
+          <t>art_source/items_weapons/props/backpack_large/source/prp_backpack_large_source_v001.blend</t>
         </is>
       </c>
       <c r="F7" s="87" t="inlineStr">

--- a/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3D-道具'!$A$4:$P$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="51">
       <c r="A6" s="56">
-        <f>COUNTA('资产主表'!$A$6:$A$30)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$33)</f>
         <v/>
       </c>
       <c r="B6" s="54" t="n"/>
       <c r="C6" s="56">
-        <f>COUNTIF('资产主表'!$K$6:$K$30,"已完成")+COUNTIF('资产主表'!$K$6:$K$30,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$30,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$30,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$30,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$30,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$30,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$33,"已完成")+COUNTIF('资产主表'!$K$6:$K$33,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$33,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$33,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$33,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$33,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$33,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="54" t="n"/>
       <c r="E6" s="56">
-        <f>COUNTIF('资产主表'!$K$6:$K$30,"待制作")+COUNTIF('资产主表'!$K$6:$K$30,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$33,"待制作")+COUNTIF('资产主表'!$K$6:$K$33,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="54" t="n"/>
       <c r="G6" s="56">
-        <f>COUNTIF('资产主表'!$S$6:$S$30,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$33,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="54" t="n"/>
@@ -1587,11 +1587,11 @@
         </is>
       </c>
       <c r="B10" s="61">
-        <f>COUNTIF('资产主表'!$C$6:$C$30,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$33,A10)</f>
         <v/>
       </c>
       <c r="C10" s="61">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$30=A10)*(('资产主表'!$K$6:$K$30="已完成")+('资产主表'!$K$6:$K$30="原型已接入")+('资产主表'!$K$6:$K$30="正式美术已接入")+('资产主表'!$K$6:$K$30="已优化并正式接入")+('资产主表'!$K$6:$K$30="Blender源已完成")+('资产主表'!$K$6:$K$30="已导入；优化完成")+('资产主表'!$K$6:$K$30="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$33=A10)*(('资产主表'!$K$6:$K$33="已完成")+('资产主表'!$K$6:$K$33="原型已接入")+('资产主表'!$K$6:$K$33="正式美术已接入")+('资产主表'!$K$6:$K$33="已优化并正式接入")+('资产主表'!$K$6:$K$33="Blender源已完成")+('资产主表'!$K$6:$K$33="已导入；优化完成")+('资产主表'!$K$6:$K$33="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="61" t="n"/>
@@ -1609,11 +1609,11 @@
         </is>
       </c>
       <c r="B11" s="57">
-        <f>COUNTIF('资产主表'!$C$6:$C$30,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$33,A11)</f>
         <v/>
       </c>
       <c r="C11" s="57">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$30=A11)*(('资产主表'!$K$6:$K$30="已完成")+('资产主表'!$K$6:$K$30="原型已接入")+('资产主表'!$K$6:$K$30="正式美术已接入")+('资产主表'!$K$6:$K$30="已优化并正式接入")+('资产主表'!$K$6:$K$30="Blender源已完成")+('资产主表'!$K$6:$K$30="已导入；优化完成")+('资产主表'!$K$6:$K$30="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$33=A11)*(('资产主表'!$K$6:$K$33="已完成")+('资产主表'!$K$6:$K$33="原型已接入")+('资产主表'!$K$6:$K$33="正式美术已接入")+('资产主表'!$K$6:$K$33="已优化并正式接入")+('资产主表'!$K$6:$K$33="Blender源已完成")+('资产主表'!$K$6:$K$33="已导入；优化完成")+('资产主表'!$K$6:$K$33="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="57" t="n"/>
@@ -1860,7 +1860,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="51">
       <c r="A5" s="57" t="inlineStr">
         <is>
@@ -2182,7 +2181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y30"/>
+  <dimension ref="A1:Y33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="50" min="1" max="1"/>
@@ -2458,7 +2457,7 @@
         <v/>
       </c>
       <c r="S6" s="62">
-        <f>IF(COUNTIF($R$6:$R$30,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="62" t="n"/>
@@ -2561,7 +2560,7 @@
         <v/>
       </c>
       <c r="S7" s="62">
-        <f>IF(COUNTIF($R$6:$R$30,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="62" t="n"/>
@@ -2664,7 +2663,7 @@
         <v/>
       </c>
       <c r="S8" s="62">
-        <f>IF(COUNTIF($R$6:$R$30,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="62" t="n"/>
@@ -2767,7 +2766,7 @@
         <v/>
       </c>
       <c r="S9" s="62">
-        <f>IF(COUNTIF($R$6:$R$30,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="62" t="n"/>
@@ -2874,7 +2873,7 @@
         <v/>
       </c>
       <c r="S10" s="62">
-        <f>IF(COUNTIF($R$6:$R$30,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="75" t="inlineStr">
@@ -2991,7 +2990,7 @@
         <v/>
       </c>
       <c r="S11" s="62">
-        <f>IF(COUNTIF($R$6:$R$30,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="75" t="inlineStr">
@@ -3112,7 +3111,7 @@
         <v/>
       </c>
       <c r="S12" s="62">
-        <f>IF(COUNTIF($R$6:$R$30,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="75" t="inlineStr">
@@ -3233,7 +3232,7 @@
         <v/>
       </c>
       <c r="S13" s="62">
-        <f>IF(COUNTIF($R$6:$R$30,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="75" t="inlineStr">
@@ -3350,7 +3349,7 @@
         <v/>
       </c>
       <c r="S14" s="54">
-        <f>IF(COUNTIF($R$6:$R$30,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="78" t="n"/>
@@ -3469,7 +3468,7 @@
         <v/>
       </c>
       <c r="S15" s="80">
-        <f>IF(COUNTIF($R$6:$R$30,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="81" t="inlineStr">
@@ -3595,7 +3594,7 @@
         <v/>
       </c>
       <c r="S16" s="80">
-        <f>IF(COUNTIF($R$6:$R$30,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="81" t="inlineStr">
@@ -3721,7 +3720,7 @@
         <v/>
       </c>
       <c r="S17" s="80">
-        <f>IF(COUNTIF($R$6:$R$30,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="81" t="inlineStr">
@@ -3843,7 +3842,7 @@
         <v/>
       </c>
       <c r="S18" s="80">
-        <f>IF(COUNTIF($R$6:$R$30,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="81" t="inlineStr">
@@ -3968,7 +3967,7 @@
         <v/>
       </c>
       <c r="S19" s="80">
-        <f>IF(COUNTIF($R$6:$R$30,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="81" t="inlineStr">
@@ -4097,7 +4096,7 @@
         <v/>
       </c>
       <c r="S20" s="50">
-        <f>IF(COUNTIF($R$6:$R$30,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="83" t="inlineStr">
@@ -4220,7 +4219,7 @@
         <v/>
       </c>
       <c r="S21" s="50">
-        <f>IF(COUNTIF($R$6:$R$30,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="83" t="inlineStr">
@@ -4343,7 +4342,7 @@
         <v/>
       </c>
       <c r="S22" s="50">
-        <f>IF(COUNTIF($R$6:$R$30,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="83" t="inlineStr">
@@ -4466,7 +4465,7 @@
         <v/>
       </c>
       <c r="S23" s="50">
-        <f>IF(COUNTIF($R$6:$R$30,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="83" t="inlineStr">
@@ -4589,7 +4588,7 @@
         <v/>
       </c>
       <c r="S24" s="50">
-        <f>IF(COUNTIF($R$6:$R$30,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="83" t="inlineStr">
@@ -4712,7 +4711,7 @@
         <v/>
       </c>
       <c r="S25" s="50">
-        <f>IF(COUNTIF($R$6:$R$30,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="83" t="inlineStr">
@@ -4831,7 +4830,7 @@
         <v/>
       </c>
       <c r="S26" s="80">
-        <f>IF(COUNTIF($R$6:$R$30,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="81" t="inlineStr">
@@ -4950,7 +4949,7 @@
         <v/>
       </c>
       <c r="S27" s="80">
-        <f>IF(COUNTIF($R$6:$R$30,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="81" t="inlineStr">
@@ -5069,7 +5068,7 @@
         <v/>
       </c>
       <c r="S28" s="54">
-        <f>IF(COUNTIF($R$6:$R$30,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="78" t="n"/>
@@ -5184,7 +5183,7 @@
         <v/>
       </c>
       <c r="S29" s="54">
-        <f>IF(COUNTIF($R$6:$R$30,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="78" t="n"/>
@@ -5299,7 +5298,7 @@
         <v/>
       </c>
       <c r="S30" s="54">
-        <f>IF(COUNTIF($R$6:$R$30,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$33,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="78" t="n"/>
@@ -5324,6 +5323,363 @@
       <c r="Y30" s="54" t="inlineStr">
         <is>
           <t>新增身份，非历史已有ID；尺寸经用户批准；静态闭合表现；以asset_contract.json冻结。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="90" customHeight="1" s="51">
+      <c r="A31" s="75" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-BATTERY-L</t>
+        </is>
+      </c>
+      <c r="B31" s="62" t="inlineStr">
+        <is>
+          <t>大型电池</t>
+        </is>
+      </c>
+      <c r="C31" s="62" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D31" s="75" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E31" s="75" t="inlineStr">
+        <is>
+          <t>item_battery_l</t>
+        </is>
+      </c>
+      <c r="F31" s="75" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="G31" s="62" t="n"/>
+      <c r="H31" s="62" t="inlineStr">
+        <is>
+          <t>底面中心原点；Blender +Z向上，正面-Y；Godot +Y向上、正面+Z</t>
+        </is>
+      </c>
+      <c r="I31" s="75" t="inlineStr">
+        <is>
+          <t>tier_0_static</t>
+        </is>
+      </c>
+      <c r="J31" s="62" t="inlineStr">
+        <is>
+          <t>独立物品/配件原始源；后续拾取、库存与武器装配复用</t>
+        </is>
+      </c>
+      <c r="K31" s="62" t="inlineStr">
+        <is>
+          <t>Blender源已完成</t>
+        </is>
+      </c>
+      <c r="L31" s="75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M31" s="75" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N31" s="62" t="inlineStr">
+        <is>
+          <t>0.4523×0.3325×0.6600m；单位米；根缩放1；场景四材质/公共色盘/PaletteUV；实测快照见asset_contract.json；preview高模；ground 168三角面（100–200预算）</t>
+        </is>
+      </c>
+      <c r="O31" s="62" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/battery_large/source/itm_battery_large_source_v001.blend; art_source/items_weapons/props/battery_large/source/itm_battery_large_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="P31" s="75" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; src/combat3d/WeaponModel3D.gd; art_source/items_weapons/props/battery_large/asset_contract.json</t>
+        </is>
+      </c>
+      <c r="Q31" s="62" t="inlineStr">
+        <is>
+          <t>item_battery_l;大型电池</t>
+        </is>
+      </c>
+      <c r="R31" s="62">
+        <f>LOWER(TRIM(C31)&amp;"|"&amp;TRIM(D31)&amp;"|"&amp;TRIM(E31)&amp;"|"&amp;TRIM(F31)&amp;"|"&amp;TRIM(H31)&amp;"|"&amp;TRIM(I31))</f>
+        <v/>
+      </c>
+      <c r="S31" s="62">
+        <f>IF(COUNTIF($R$6:$R$33,R31)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T31" s="62" t="inlineStr">
+        <is>
+          <t>7157aee1841ef81347a0d5b94a56e380366545b9a3aed0df5470e814eaa7b075</t>
+        </is>
+      </c>
+      <c r="U31" s="62" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V31" s="76" t="n">
+        <v>46309</v>
+      </c>
+      <c r="W31" s="62" t="inlineStr">
+        <is>
+          <t>用户提供参考图重建；项目公共色盘</t>
+        </is>
+      </c>
+      <c r="X31" s="77" t="inlineStr">
+        <is>
+          <t>ITM_大型电池_中文资产管理</t>
+        </is>
+      </c>
+      <c r="Y31" s="62" t="inlineStr">
+        <is>
+          <t>2026-10-14 用户参考图制作；Godot物品工厂/拾取实体/配件挂点实测后冻结主轴尺寸，其余轴按图等比。仅Blender原始源；未导出GLB、未导入Godot；运行时仍用现有占位。 双模型源：preview=12536三角；ground=168三角；地面源SHA256=63560237834283a742563891778e69b2d634c66c08b47ce7db99bba1313eaa3d；高模哈希保持；未接入运行时。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="90" customHeight="1" s="51">
+      <c r="A32" s="75" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-BATTERY-S</t>
+        </is>
+      </c>
+      <c r="B32" s="62" t="inlineStr">
+        <is>
+          <t>小型电池</t>
+        </is>
+      </c>
+      <c r="C32" s="62" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D32" s="75" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E32" s="75" t="inlineStr">
+        <is>
+          <t>item_battery_s</t>
+        </is>
+      </c>
+      <c r="F32" s="75" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="G32" s="62" t="n"/>
+      <c r="H32" s="62" t="inlineStr">
+        <is>
+          <t>底面中心原点；Blender +Z向上，正面-Y；Godot +Y向上、正面+Z</t>
+        </is>
+      </c>
+      <c r="I32" s="75" t="inlineStr">
+        <is>
+          <t>tier_0_static</t>
+        </is>
+      </c>
+      <c r="J32" s="62" t="inlineStr">
+        <is>
+          <t>独立物品/配件原始源；后续拾取、库存与武器装配复用</t>
+        </is>
+      </c>
+      <c r="K32" s="62" t="inlineStr">
+        <is>
+          <t>Blender源已完成</t>
+        </is>
+      </c>
+      <c r="L32" s="75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M32" s="75" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N32" s="62" t="inlineStr">
+        <is>
+          <t>0.3111×0.3111×0.6600m；单位米；根缩放1；场景四材质/公共色盘/PaletteUV；实测快照见asset_contract.json；preview高模；ground 120三角面（100–200预算）</t>
+        </is>
+      </c>
+      <c r="O32" s="62" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/battery_small/source/itm_battery_small_source_v001.blend; art_source/items_weapons/props/battery_small/source/itm_battery_small_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="P32" s="75" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; src/combat3d/WeaponModel3D.gd; art_source/items_weapons/props/battery_small/asset_contract.json</t>
+        </is>
+      </c>
+      <c r="Q32" s="62" t="inlineStr">
+        <is>
+          <t>item_battery_s;小型电池</t>
+        </is>
+      </c>
+      <c r="R32" s="62">
+        <f>LOWER(TRIM(C32)&amp;"|"&amp;TRIM(D32)&amp;"|"&amp;TRIM(E32)&amp;"|"&amp;TRIM(F32)&amp;"|"&amp;TRIM(H32)&amp;"|"&amp;TRIM(I32))</f>
+        <v/>
+      </c>
+      <c r="S32" s="62">
+        <f>IF(COUNTIF($R$6:$R$33,R32)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T32" s="62" t="inlineStr">
+        <is>
+          <t>85017af7760230fd9dd0b796bdd15ae3c3eb91dc8e5d977eb307ba32676e8a54</t>
+        </is>
+      </c>
+      <c r="U32" s="62" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V32" s="76" t="n">
+        <v>46309</v>
+      </c>
+      <c r="W32" s="62" t="inlineStr">
+        <is>
+          <t>用户提供参考图重建；项目公共色盘</t>
+        </is>
+      </c>
+      <c r="X32" s="77" t="inlineStr">
+        <is>
+          <t>ITM_小型电池_中文资产管理</t>
+        </is>
+      </c>
+      <c r="Y32" s="62" t="inlineStr">
+        <is>
+          <t>2026-10-14 用户参考图制作；Godot物品工厂/拾取实体/配件挂点实测后冻结主轴尺寸，其余轴按图等比。仅Blender原始源；未导出GLB、未导入Godot；运行时仍用现有占位。 双模型源：preview=3616三角；ground=120三角；地面源SHA256=e7d916bff0cf1d2cab60d49595b38d8f22a5cf9f0d033d71b4e3fa053944f762；高模哈希保持；未接入运行时。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="90" customHeight="1" s="51">
+      <c r="A33" s="75" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-HEALTH-POTION</t>
+        </is>
+      </c>
+      <c r="B33" s="62" t="inlineStr">
+        <is>
+          <t>治疗药水</t>
+        </is>
+      </c>
+      <c r="C33" s="62" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D33" s="75" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E33" s="75" t="inlineStr">
+        <is>
+          <t>item_health_potion</t>
+        </is>
+      </c>
+      <c r="F33" s="75" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="G33" s="62" t="n"/>
+      <c r="H33" s="62" t="inlineStr">
+        <is>
+          <t>底面中心原点；Blender +Z向上，正面-Y；Godot +Y向上、正面+Z</t>
+        </is>
+      </c>
+      <c r="I33" s="75" t="inlineStr">
+        <is>
+          <t>tier_0_static</t>
+        </is>
+      </c>
+      <c r="J33" s="62" t="inlineStr">
+        <is>
+          <t>独立物品/配件原始源；后续拾取、库存与武器装配复用</t>
+        </is>
+      </c>
+      <c r="K33" s="62" t="inlineStr">
+        <is>
+          <t>Blender源已完成</t>
+        </is>
+      </c>
+      <c r="L33" s="75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M33" s="75" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N33" s="62" t="inlineStr">
+        <is>
+          <t>0.6731×0.6835×0.8200m；单位米；根缩放1；场景四材质/公共色盘/PaletteUV；实测快照见asset_contract.json；preview高模；ground 178三角面（100–200预算）</t>
+        </is>
+      </c>
+      <c r="O33" s="62" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/health_potion/source/itm_health_potion_source_v001.blend; art_source/items_weapons/props/health_potion/source/itm_health_potion_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="P33" s="75" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; src/combat3d/WeaponModel3D.gd; art_source/items_weapons/props/health_potion/asset_contract.json</t>
+        </is>
+      </c>
+      <c r="Q33" s="62" t="inlineStr">
+        <is>
+          <t>item_health_potion;治疗药水</t>
+        </is>
+      </c>
+      <c r="R33" s="62">
+        <f>LOWER(TRIM(C33)&amp;"|"&amp;TRIM(D33)&amp;"|"&amp;TRIM(E33)&amp;"|"&amp;TRIM(F33)&amp;"|"&amp;TRIM(H33)&amp;"|"&amp;TRIM(I33))</f>
+        <v/>
+      </c>
+      <c r="S33" s="62">
+        <f>IF(COUNTIF($R$6:$R$33,R33)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T33" s="62" t="inlineStr">
+        <is>
+          <t>6d1d848e4cc37d91fc99d0609db46763ef916458e2a418aa621befb07781d5bb</t>
+        </is>
+      </c>
+      <c r="U33" s="62" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V33" s="76" t="n">
+        <v>46309</v>
+      </c>
+      <c r="W33" s="62" t="inlineStr">
+        <is>
+          <t>用户提供参考图重建；项目公共色盘</t>
+        </is>
+      </c>
+      <c r="X33" s="77" t="inlineStr">
+        <is>
+          <t>ITM_治疗药水_中文资产管理</t>
+        </is>
+      </c>
+      <c r="Y33" s="62" t="inlineStr">
+        <is>
+          <t>2026-10-14 用户参考图制作；Godot物品工厂/拾取实体/配件挂点实测后冻结主轴尺寸，其余轴按图等比。仅Blender原始源；未导出GLB、未导入Godot；运行时仍用现有占位。 严格四材质公共色盘，药瓶采用不透明清漆与浅色肩部表现玻璃感；未新增透明材质。 双模型源：preview=5660三角；ground=178三角；地面源SHA256=509273cbee4ddeef75c0f51dba3e224ed93fb0e66f52970e97ec5e23dd6647f0；高模哈希保持；未接入运行时。</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5891,7 @@
     <row r="427" ht="84.75" customHeight="1" s="51"/>
     <row r="429" ht="120" customHeight="1" s="51"/>
   </sheetData>
-  <autoFilter ref="A5:Y30"/>
+  <autoFilter ref="A5:Y33"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
@@ -5554,15 +5910,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K6:K30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L6:L30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5616,7 +5972,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="51">
       <c r="A4" s="86" t="inlineStr">
         <is>
@@ -6078,7 +6433,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="51">
       <c r="A4" s="86" t="inlineStr">
         <is>
@@ -6438,7 +6792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="50" min="1" max="1"/>
@@ -6465,7 +6819,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="51">
       <c r="A5" s="57" t="inlineStr">
         <is>
@@ -7160,6 +7513,80 @@
       <c r="G23" s="61" t="inlineStr">
         <is>
           <t>CodeBuddy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="68" t="inlineStr">
+        <is>
+          <t>v0.1.18</t>
+        </is>
+      </c>
+      <c r="B24" s="103" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C24" s="61" t="inlineStr">
+        <is>
+          <t>参考图8件道具：Blender原始源</t>
+        </is>
+      </c>
+      <c r="D24" s="61" t="inlineStr">
+        <is>
+          <t>道具与武器原始源</t>
+        </is>
+      </c>
+      <c r="E24" s="61" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-BATTERY-L,ITM-CONSUMABLE-ITEM-BATTERY-S,ITM-CONSUMABLE-ITEM-HEALTH-POTION</t>
+        </is>
+      </c>
+      <c r="F24" s="61" t="inlineStr">
+        <is>
+          <t>实测尺寸/场景四材质/源已完成；未运行时接入</t>
+        </is>
+      </c>
+      <c r="G24" s="61" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>v0.1.100</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>物品道具双模型源</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>preview / ground</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>现有高模保留；地面100–200三角面</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>源已完成；运行时用途选择未接入</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Codex</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
@@ -15,8 +15,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3D-道具'!$A$4:$P$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3D-物品'!$A$4:$P$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -1503,22 +1504,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="51">
       <c r="A6" s="56">
-        <f>COUNTA('资产主表'!$A$6:$A$33)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$34)</f>
         <v/>
       </c>
       <c r="B6" s="54" t="n"/>
       <c r="C6" s="56">
-        <f>COUNTIF('资产主表'!$K$6:$K$33,"已完成")+COUNTIF('资产主表'!$K$6:$K$33,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$33,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$33,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$33,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$33,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$33,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$34,"已完成")+COUNTIF('资产主表'!$K$6:$K$34,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$34,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$34,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$34,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$34,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$34,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="54" t="n"/>
       <c r="E6" s="56">
-        <f>COUNTIF('资产主表'!$K$6:$K$33,"待制作")+COUNTIF('资产主表'!$K$6:$K$33,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$34,"待制作")+COUNTIF('资产主表'!$K$6:$K$34,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="54" t="n"/>
       <c r="G6" s="56">
-        <f>COUNTIF('资产主表'!$S$6:$S$33,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$34,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="54" t="n"/>
@@ -1587,11 +1588,11 @@
         </is>
       </c>
       <c r="B10" s="61">
-        <f>COUNTIF('资产主表'!$C$6:$C$33,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$34,A10)</f>
         <v/>
       </c>
       <c r="C10" s="61">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$33=A10)*(('资产主表'!$K$6:$K$33="已完成")+('资产主表'!$K$6:$K$33="原型已接入")+('资产主表'!$K$6:$K$33="正式美术已接入")+('资产主表'!$K$6:$K$33="已优化并正式接入")+('资产主表'!$K$6:$K$33="Blender源已完成")+('资产主表'!$K$6:$K$33="已导入；优化完成")+('资产主表'!$K$6:$K$33="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$34=A10)*(('资产主表'!$K$6:$K$34="已完成")+('资产主表'!$K$6:$K$34="原型已接入")+('资产主表'!$K$6:$K$34="正式美术已接入")+('资产主表'!$K$6:$K$34="已优化并正式接入")+('资产主表'!$K$6:$K$34="Blender源已完成")+('资产主表'!$K$6:$K$34="已导入；优化完成")+('资产主表'!$K$6:$K$34="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="61" t="n"/>
@@ -1609,11 +1610,11 @@
         </is>
       </c>
       <c r="B11" s="57">
-        <f>COUNTIF('资产主表'!$C$6:$C$33,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$34,A11)</f>
         <v/>
       </c>
       <c r="C11" s="57">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$33=A11)*(('资产主表'!$K$6:$K$33="已完成")+('资产主表'!$K$6:$K$33="原型已接入")+('资产主表'!$K$6:$K$33="正式美术已接入")+('资产主表'!$K$6:$K$33="已优化并正式接入")+('资产主表'!$K$6:$K$33="Blender源已完成")+('资产主表'!$K$6:$K$33="已导入；优化完成")+('资产主表'!$K$6:$K$33="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$34=A11)*(('资产主表'!$K$6:$K$34="已完成")+('资产主表'!$K$6:$K$34="原型已接入")+('资产主表'!$K$6:$K$34="正式美术已接入")+('资产主表'!$K$6:$K$34="已优化并正式接入")+('资产主表'!$K$6:$K$34="Blender源已完成")+('资产主表'!$K$6:$K$34="已导入；优化完成")+('资产主表'!$K$6:$K$34="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="57" t="n"/>
@@ -2181,7 +2182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y33"/>
+  <dimension ref="A1:Y34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="50" min="1" max="1"/>
@@ -2457,7 +2458,7 @@
         <v/>
       </c>
       <c r="S6" s="62">
-        <f>IF(COUNTIF($R$6:$R$33,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="62" t="n"/>
@@ -2560,7 +2561,7 @@
         <v/>
       </c>
       <c r="S7" s="62">
-        <f>IF(COUNTIF($R$6:$R$33,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="62" t="n"/>
@@ -2663,7 +2664,7 @@
         <v/>
       </c>
       <c r="S8" s="62">
-        <f>IF(COUNTIF($R$6:$R$33,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="62" t="n"/>
@@ -2766,7 +2767,7 @@
         <v/>
       </c>
       <c r="S9" s="62">
-        <f>IF(COUNTIF($R$6:$R$33,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="62" t="n"/>
@@ -2873,7 +2874,7 @@
         <v/>
       </c>
       <c r="S10" s="62">
-        <f>IF(COUNTIF($R$6:$R$33,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="75" t="inlineStr">
@@ -2990,7 +2991,7 @@
         <v/>
       </c>
       <c r="S11" s="62">
-        <f>IF(COUNTIF($R$6:$R$33,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="75" t="inlineStr">
@@ -3111,7 +3112,7 @@
         <v/>
       </c>
       <c r="S12" s="62">
-        <f>IF(COUNTIF($R$6:$R$33,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="75" t="inlineStr">
@@ -3232,7 +3233,7 @@
         <v/>
       </c>
       <c r="S13" s="62">
-        <f>IF(COUNTIF($R$6:$R$33,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="75" t="inlineStr">
@@ -3349,7 +3350,7 @@
         <v/>
       </c>
       <c r="S14" s="54">
-        <f>IF(COUNTIF($R$6:$R$33,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="78" t="n"/>
@@ -3468,7 +3469,7 @@
         <v/>
       </c>
       <c r="S15" s="80">
-        <f>IF(COUNTIF($R$6:$R$33,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="81" t="inlineStr">
@@ -3594,7 +3595,7 @@
         <v/>
       </c>
       <c r="S16" s="80">
-        <f>IF(COUNTIF($R$6:$R$33,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="81" t="inlineStr">
@@ -3720,7 +3721,7 @@
         <v/>
       </c>
       <c r="S17" s="80">
-        <f>IF(COUNTIF($R$6:$R$33,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="81" t="inlineStr">
@@ -3842,7 +3843,7 @@
         <v/>
       </c>
       <c r="S18" s="80">
-        <f>IF(COUNTIF($R$6:$R$33,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="81" t="inlineStr">
@@ -3967,7 +3968,7 @@
         <v/>
       </c>
       <c r="S19" s="80">
-        <f>IF(COUNTIF($R$6:$R$33,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="81" t="inlineStr">
@@ -4096,7 +4097,7 @@
         <v/>
       </c>
       <c r="S20" s="50">
-        <f>IF(COUNTIF($R$6:$R$33,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="83" t="inlineStr">
@@ -4219,7 +4220,7 @@
         <v/>
       </c>
       <c r="S21" s="50">
-        <f>IF(COUNTIF($R$6:$R$33,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="83" t="inlineStr">
@@ -4342,7 +4343,7 @@
         <v/>
       </c>
       <c r="S22" s="50">
-        <f>IF(COUNTIF($R$6:$R$33,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="83" t="inlineStr">
@@ -4465,7 +4466,7 @@
         <v/>
       </c>
       <c r="S23" s="50">
-        <f>IF(COUNTIF($R$6:$R$33,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="83" t="inlineStr">
@@ -4588,7 +4589,7 @@
         <v/>
       </c>
       <c r="S24" s="50">
-        <f>IF(COUNTIF($R$6:$R$33,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="83" t="inlineStr">
@@ -4711,7 +4712,7 @@
         <v/>
       </c>
       <c r="S25" s="50">
-        <f>IF(COUNTIF($R$6:$R$33,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="83" t="inlineStr">
@@ -4830,7 +4831,7 @@
         <v/>
       </c>
       <c r="S26" s="80">
-        <f>IF(COUNTIF($R$6:$R$33,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="81" t="inlineStr">
@@ -4949,7 +4950,7 @@
         <v/>
       </c>
       <c r="S27" s="80">
-        <f>IF(COUNTIF($R$6:$R$33,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="81" t="inlineStr">
@@ -5068,7 +5069,7 @@
         <v/>
       </c>
       <c r="S28" s="54">
-        <f>IF(COUNTIF($R$6:$R$33,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="78" t="n"/>
@@ -5183,7 +5184,7 @@
         <v/>
       </c>
       <c r="S29" s="54">
-        <f>IF(COUNTIF($R$6:$R$33,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="78" t="n"/>
@@ -5298,7 +5299,7 @@
         <v/>
       </c>
       <c r="S30" s="54">
-        <f>IF(COUNTIF($R$6:$R$33,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="78" t="n"/>
@@ -5370,12 +5371,12 @@
       </c>
       <c r="J31" s="62" t="inlineStr">
         <is>
-          <t>独立物品/配件原始源；后续拾取、库存与武器装配复用</t>
+          <t>ground地面简模已接线；preview高模待导入；枪上装配保持原表现</t>
         </is>
       </c>
       <c r="K31" s="62" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>exported_pending_godot_validation</t>
         </is>
       </c>
       <c r="L31" s="75" t="inlineStr">
@@ -5395,12 +5396,12 @@
       </c>
       <c r="O31" s="62" t="inlineStr">
         <is>
-          <t>art_source/items_weapons/props/battery_large/source/itm_battery_large_source_v001.blend; art_source/items_weapons/props/battery_large/source/itm_battery_large_ground_source_v001.blend</t>
+          <t>assets/art/items_weapons/props/battery_large/runtime/itm_battery_large_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P31" s="75" t="inlineStr">
         <is>
-          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; src/combat3d/WeaponModel3D.gd; art_source/items_weapons/props/battery_large/asset_contract.json</t>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
         </is>
       </c>
       <c r="Q31" s="62" t="inlineStr">
@@ -5413,12 +5414,12 @@
         <v/>
       </c>
       <c r="S31" s="62">
-        <f>IF(COUNTIF($R$6:$R$33,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="62" t="inlineStr">
         <is>
-          <t>7157aee1841ef81347a0d5b94a56e380366545b9a3aed0df5470e814eaa7b075</t>
+          <t>9a96e40eb5695a5c312cb72cd42c2ac18eb1e23c10cd6ea9161c8559caad564c</t>
         </is>
       </c>
       <c r="U31" s="62" t="inlineStr">
@@ -5441,7 +5442,7 @@
       </c>
       <c r="Y31" s="62" t="inlineStr">
         <is>
-          <t>2026-10-14 用户参考图制作；Godot物品工厂/拾取实体/配件挂点实测后冻结主轴尺寸，其余轴按图等比。仅Blender原始源；未导出GLB、未导入Godot；运行时仍用现有占位。 双模型源：preview=12536三角；ground=168三角；地面源SHA256=63560237834283a742563891778e69b2d634c66c08b47ce7db99bba1313eaa3d；高模哈希保持；未接入运行时。</t>
+          <t>ground=168三角；GLB=assets/art/items_weapons/props/battery_large/components/itm_battery_large_ground_visual_top3d.glb；ground源=art_source/items_weapons/props/battery_large/source/itm_battery_large_ground_source_v001.blend SHA256=63560237834283a742563891778e69b2d634c66c08b47ce7db99bba1313eaa3d；preview源=art_source/items_weapons/props/battery_large/source/itm_battery_large_source_v001.blend SHA256=7157aee1841ef81347a0d5b94a56e380366545b9a3aed0df5470e814eaa7b075；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。；2026-10-14地面显示倍率1.30（最终0.6552），图标倍率不变。</t>
         </is>
       </c>
     </row>
@@ -5489,12 +5490,12 @@
       </c>
       <c r="J32" s="62" t="inlineStr">
         <is>
-          <t>独立物品/配件原始源；后续拾取、库存与武器装配复用</t>
+          <t>ground地面简模已接线；preview高模待导入；枪上装配保持原表现</t>
         </is>
       </c>
       <c r="K32" s="62" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>exported_pending_godot_validation</t>
         </is>
       </c>
       <c r="L32" s="75" t="inlineStr">
@@ -5514,12 +5515,12 @@
       </c>
       <c r="O32" s="62" t="inlineStr">
         <is>
-          <t>art_source/items_weapons/props/battery_small/source/itm_battery_small_source_v001.blend; art_source/items_weapons/props/battery_small/source/itm_battery_small_ground_source_v001.blend</t>
+          <t>assets/art/items_weapons/props/battery_small/runtime/itm_battery_small_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P32" s="75" t="inlineStr">
         <is>
-          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; src/combat3d/WeaponModel3D.gd; art_source/items_weapons/props/battery_small/asset_contract.json</t>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
         </is>
       </c>
       <c r="Q32" s="62" t="inlineStr">
@@ -5532,12 +5533,12 @@
         <v/>
       </c>
       <c r="S32" s="62">
-        <f>IF(COUNTIF($R$6:$R$33,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="62" t="inlineStr">
         <is>
-          <t>85017af7760230fd9dd0b796bdd15ae3c3eb91dc8e5d977eb307ba32676e8a54</t>
+          <t>609cb7a4a4f47ef8d813a16c2b443a954f1db5bd47a49bbbdb620bc4bad34035</t>
         </is>
       </c>
       <c r="U32" s="62" t="inlineStr">
@@ -5560,7 +5561,7 @@
       </c>
       <c r="Y32" s="62" t="inlineStr">
         <is>
-          <t>2026-10-14 用户参考图制作；Godot物品工厂/拾取实体/配件挂点实测后冻结主轴尺寸，其余轴按图等比。仅Blender原始源；未导出GLB、未导入Godot；运行时仍用现有占位。 双模型源：preview=3616三角；ground=120三角；地面源SHA256=e7d916bff0cf1d2cab60d49595b38d8f22a5cf9f0d033d71b4e3fa053944f762；高模哈希保持；未接入运行时。</t>
+          <t>ground=120三角；GLB=assets/art/items_weapons/props/battery_small/components/itm_battery_small_ground_visual_top3d.glb；ground源=art_source/items_weapons/props/battery_small/source/itm_battery_small_ground_source_v001.blend SHA256=e7d916bff0cf1d2cab60d49595b38d8f22a5cf9f0d033d71b4e3fa053944f762；preview源=art_source/items_weapons/props/battery_small/source/itm_battery_small_source_v001.blend SHA256=85017af7760230fd9dd0b796bdd15ae3c3eb91dc8e5d977eb307ba32676e8a54；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。</t>
         </is>
       </c>
     </row>
@@ -5608,12 +5609,12 @@
       </c>
       <c r="J33" s="62" t="inlineStr">
         <is>
-          <t>独立物品/配件原始源；后续拾取、库存与武器装配复用</t>
+          <t>ground地面简模已接线；preview高模待导入；枪上装配保持原表现</t>
         </is>
       </c>
       <c r="K33" s="62" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>exported_pending_godot_validation</t>
         </is>
       </c>
       <c r="L33" s="75" t="inlineStr">
@@ -5633,12 +5634,12 @@
       </c>
       <c r="O33" s="62" t="inlineStr">
         <is>
-          <t>art_source/items_weapons/props/health_potion/source/itm_health_potion_source_v001.blend; art_source/items_weapons/props/health_potion/source/itm_health_potion_ground_source_v001.blend</t>
+          <t>assets/art/items_weapons/props/health_potion/runtime/itm_health_potion_ground_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P33" s="75" t="inlineStr">
         <is>
-          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; src/combat3d/WeaponModel3D.gd; art_source/items_weapons/props/health_potion/asset_contract.json</t>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
         </is>
       </c>
       <c r="Q33" s="62" t="inlineStr">
@@ -5651,12 +5652,12 @@
         <v/>
       </c>
       <c r="S33" s="62">
-        <f>IF(COUNTIF($R$6:$R$33,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$34,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="62" t="inlineStr">
         <is>
-          <t>6d1d848e4cc37d91fc99d0609db46763ef916458e2a418aa621befb07781d5bb</t>
+          <t>06f757f960b93bce2fd157edd102790a15d45f06819b9d922dc1545a9ceb8e7a</t>
         </is>
       </c>
       <c r="U33" s="62" t="inlineStr">
@@ -5679,7 +5680,126 @@
       </c>
       <c r="Y33" s="62" t="inlineStr">
         <is>
-          <t>2026-10-14 用户参考图制作；Godot物品工厂/拾取实体/配件挂点实测后冻结主轴尺寸，其余轴按图等比。仅Blender原始源；未导出GLB、未导入Godot；运行时仍用现有占位。 严格四材质公共色盘，药瓶采用不透明清漆与浅色肩部表现玻璃感；未新增透明材质。 双模型源：preview=5660三角；ground=178三角；地面源SHA256=509273cbee4ddeef75c0f51dba3e224ed93fb0e66f52970e97ec5e23dd6647f0；高模哈希保持；未接入运行时。</t>
+          <t>ground=178三角；GLB=assets/art/items_weapons/props/health_potion/components/itm_health_potion_ground_visual_top3d.glb；ground源=art_source/items_weapons/props/health_potion/source/itm_health_potion_ground_source_v001.blend SHA256=509273cbee4ddeef75c0f51dba3e224ed93fb0e66f52970e97ec5e23dd6647f0；preview源=art_source/items_weapons/props/health_potion/source/itm_health_potion_source_v001.blend SHA256=6d1d848e4cc37d91fc99d0609db46763ef916458e2a418aa621befb07781d5bb；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。；2026-10-14地面显示倍率1.30（最终0.6552），图标倍率不变。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="75" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-AMMO-PACK</t>
+        </is>
+      </c>
+      <c r="B34" s="62" t="inlineStr">
+        <is>
+          <t>通用弹药</t>
+        </is>
+      </c>
+      <c r="C34" s="62" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D34" s="75" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E34" s="75" t="inlineStr">
+        <is>
+          <t>item_ammo_pack</t>
+        </is>
+      </c>
+      <c r="F34" s="75" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="G34" s="62" t="n"/>
+      <c r="H34" s="62" t="inlineStr">
+        <is>
+          <t>底面中心原点；Blender +Z向上，正面-Y；Godot +Y向上、正面+Z</t>
+        </is>
+      </c>
+      <c r="I34" s="75" t="inlineStr">
+        <is>
+          <t>tier_0_static</t>
+        </is>
+      </c>
+      <c r="J34" s="62" t="inlineStr">
+        <is>
+          <t>通用弹药地面与背包图标共用；倾斜45度旋转</t>
+        </is>
+      </c>
+      <c r="K34" s="62" t="inlineStr">
+        <is>
+          <t>exported_pending_godot_validation</t>
+        </is>
+      </c>
+      <c r="L34" s="75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M34" s="75" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N34" s="62" t="inlineStr">
+        <is>
+          <t>0.3760×0.3760×0.9400m；单位米；根缩放1；场景四材质/公共色盘/PaletteUV；实测快照见asset_contract.json；preview高模；ground 176三角面（100–200预算）</t>
+        </is>
+      </c>
+      <c r="O34" s="62" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_standard/runtime/wpn_bullet_standard_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P34" s="75" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q34" s="62" t="inlineStr">
+        <is>
+          <t>item_ammo_pack;通用弹药</t>
+        </is>
+      </c>
+      <c r="R34" s="62">
+        <f>LOWER(TRIM(C34)&amp;"|"&amp;TRIM(D34)&amp;"|"&amp;TRIM(E34)&amp;"|"&amp;TRIM(F34)&amp;"|"&amp;TRIM(H34)&amp;"|"&amp;TRIM(I34))</f>
+        <v/>
+      </c>
+      <c r="S34" s="62">
+        <f>IF(COUNTIF($R$6:$R$34,R34)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T34" s="62" t="inlineStr">
+        <is>
+          <t>0ad392c1dec49e5fb0d4d40debc651c85a0ba7580fdd750285ff2a3ff5b186f8</t>
+        </is>
+      </c>
+      <c r="U34" s="62" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V34" s="76" t="n">
+        <v>46309</v>
+      </c>
+      <c r="W34" s="62" t="inlineStr">
+        <is>
+          <t>用户提供参考图重建；项目公共色盘</t>
+        </is>
+      </c>
+      <c r="X34" s="77" t="inlineStr">
+        <is>
+          <t>WPN_标准子弹模块_中文资产管理</t>
+        </is>
+      </c>
+      <c r="Y34" s="62" t="inlineStr">
+        <is>
+          <t>通用弹药：黄色弹壳；地面/图标共用；preview源SHA256=a1302b8182d523834dc0af9741eb687044489f66cafa0cfbcbf79d1de1d565d3；ground源SHA256=3d7baf9637ba5bc14982366f0663af93102512c4c04335b77104983208c3f88c；原尺寸与176三角预算保持。</t>
         </is>
       </c>
     </row>
@@ -5891,7 +6011,7 @@
     <row r="427" ht="84.75" customHeight="1" s="51"/>
     <row r="429" ht="120" customHeight="1" s="51"/>
   </sheetData>
-  <autoFilter ref="A5:Y33"/>
+  <autoFilter ref="A5:Y34"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
@@ -5910,15 +6030,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K6:K33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L6:L33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6399,7 +6519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="35.81" customWidth="1" style="50" min="1" max="1"/>
@@ -6429,10 +6549,11 @@
     <row r="2" ht="33.75" customHeight="1" s="51">
       <c r="A2" s="85" t="inlineStr">
         <is>
-          <t>独立物品PackedScene；3款背包已登记，等待制作与验收。</t>
-        </is>
-      </c>
-    </row>
+          <t>一行一个独立PackedScene；地面模型使用ground角色，状态以各行记录为准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="51">
       <c r="A4" s="86" t="inlineStr">
         <is>
@@ -6761,7 +6882,336 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="86" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-BATTERY-L</t>
+        </is>
+      </c>
+      <c r="B8" s="87" t="inlineStr">
+        <is>
+          <t>大型电池（地面）</t>
+        </is>
+      </c>
+      <c r="C8" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/battery_large/runtime/itm_battery_large_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D8" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/battery_large/components/itm_battery_large_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E8" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/battery_large/source/itm_battery_large_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F8" s="87" t="inlineStr">
+        <is>
+          <t>仅ground视觉；同一物品身份，外部负责拾取/弹跳/收集</t>
+        </is>
+      </c>
+      <c r="G8" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd</t>
+        </is>
+      </c>
+      <c r="H8" s="87" t="inlineStr">
+        <is>
+          <t>Prefab无；外部拾取触发</t>
+        </is>
+      </c>
+      <c r="I8" s="87" t="inlineStr">
+        <is>
+          <t>GroundLootPickup3D</t>
+        </is>
+      </c>
+      <c r="J8" s="87" t="inlineStr">
+        <is>
+          <t>外部SphereShape3D；无实体阻挡</t>
+        </is>
+      </c>
+      <c r="K8" s="87" t="inlineStr">
+        <is>
+          <t>0.45228×0.332524×0.66m；168三角；外部倍率0.504</t>
+        </is>
+      </c>
+      <c r="L8" s="87" t="inlineStr">
+        <is>
+          <t>底面中心原点；Blender +Z向上，正面-Y；Godot +Y向上、正面+Z</t>
+        </is>
+      </c>
+      <c r="M8" s="87" t="inlineStr">
+        <is>
+          <t>世界地面掉落/拾取；非背包预览与枪上装配</t>
+        </is>
+      </c>
+      <c r="N8" s="87" t="inlineStr">
+        <is>
+          <t>exported_pending_godot_validation</t>
+        </is>
+      </c>
+      <c r="O8" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P8" s="89" t="inlineStr">
+        <is>
+          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收；地面倍率1.30，最终0.6552</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="86" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-BATTERY-S</t>
+        </is>
+      </c>
+      <c r="B9" s="87" t="inlineStr">
+        <is>
+          <t>小型电池（地面）</t>
+        </is>
+      </c>
+      <c r="C9" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/battery_small/runtime/itm_battery_small_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D9" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/battery_small/components/itm_battery_small_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E9" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/battery_small/source/itm_battery_small_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F9" s="87" t="inlineStr">
+        <is>
+          <t>仅ground视觉；同一物品身份，外部负责拾取/弹跳/收集</t>
+        </is>
+      </c>
+      <c r="G9" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd</t>
+        </is>
+      </c>
+      <c r="H9" s="87" t="inlineStr">
+        <is>
+          <t>Prefab无；外部拾取触发</t>
+        </is>
+      </c>
+      <c r="I9" s="87" t="inlineStr">
+        <is>
+          <t>GroundLootPickup3D</t>
+        </is>
+      </c>
+      <c r="J9" s="87" t="inlineStr">
+        <is>
+          <t>外部SphereShape3D；无实体阻挡</t>
+        </is>
+      </c>
+      <c r="K9" s="87" t="inlineStr">
+        <is>
+          <t>0.311111×0.311111×0.66m；120三角；外部倍率0.504</t>
+        </is>
+      </c>
+      <c r="L9" s="87" t="inlineStr">
+        <is>
+          <t>底面中心原点；Blender +Z向上，正面-Y；Godot +Y向上、正面+Z</t>
+        </is>
+      </c>
+      <c r="M9" s="87" t="inlineStr">
+        <is>
+          <t>世界地面掉落/拾取；非背包预览与枪上装配</t>
+        </is>
+      </c>
+      <c r="N9" s="87" t="inlineStr">
+        <is>
+          <t>exported_pending_godot_validation</t>
+        </is>
+      </c>
+      <c r="O9" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P9" s="89" t="inlineStr">
+        <is>
+          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="86" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-HEALTH-POTION</t>
+        </is>
+      </c>
+      <c r="B10" s="87" t="inlineStr">
+        <is>
+          <t>治疗药水（地面）</t>
+        </is>
+      </c>
+      <c r="C10" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/health_potion/runtime/itm_health_potion_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D10" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/health_potion/components/itm_health_potion_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E10" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/health_potion/source/itm_health_potion_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F10" s="87" t="inlineStr">
+        <is>
+          <t>仅ground视觉；同一物品身份，外部负责拾取/弹跳/收集</t>
+        </is>
+      </c>
+      <c r="G10" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd</t>
+        </is>
+      </c>
+      <c r="H10" s="87" t="inlineStr">
+        <is>
+          <t>Prefab无；外部拾取触发</t>
+        </is>
+      </c>
+      <c r="I10" s="87" t="inlineStr">
+        <is>
+          <t>GroundLootPickup3D</t>
+        </is>
+      </c>
+      <c r="J10" s="87" t="inlineStr">
+        <is>
+          <t>外部SphereShape3D；无实体阻挡</t>
+        </is>
+      </c>
+      <c r="K10" s="87" t="inlineStr">
+        <is>
+          <t>0.673088×0.683507×0.82m；178三角；外部倍率0.504</t>
+        </is>
+      </c>
+      <c r="L10" s="87" t="inlineStr">
+        <is>
+          <t>底面中心原点；Blender +Z向上，正面-Y；Godot +Y向上、正面+Z</t>
+        </is>
+      </c>
+      <c r="M10" s="87" t="inlineStr">
+        <is>
+          <t>世界地面掉落/拾取；非背包预览与枪上装配</t>
+        </is>
+      </c>
+      <c r="N10" s="87" t="inlineStr">
+        <is>
+          <t>exported_pending_godot_validation</t>
+        </is>
+      </c>
+      <c r="O10" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P10" s="89" t="inlineStr">
+        <is>
+          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收；地面倍率1.30，最终0.6552</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="50" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-AMMO-PACK</t>
+        </is>
+      </c>
+      <c r="B11" s="50" t="inlineStr">
+        <is>
+          <t>通用弹药（地面/图标）</t>
+        </is>
+      </c>
+      <c r="C11" s="50" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_standard/runtime/wpn_bullet_standard_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D11" s="50" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/weapons/bullet_standard/components/wpn_bullet_standard_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E11" s="50" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/weapons/bullet_standard/source/wpn_bullet_standard_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F11" s="50" t="inlineStr">
+        <is>
+          <t>仅ground视觉；同一物品身份，外部负责拾取/弹跳/收集</t>
+        </is>
+      </c>
+      <c r="G11" s="50" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/world3d/GroundLootPickup3D.gd</t>
+        </is>
+      </c>
+      <c r="H11" s="50" t="inlineStr">
+        <is>
+          <t>Prefab无；外部拾取触发</t>
+        </is>
+      </c>
+      <c r="I11" s="50" t="inlineStr">
+        <is>
+          <t>GroundLootPickup3D</t>
+        </is>
+      </c>
+      <c r="J11" s="50" t="inlineStr">
+        <is>
+          <t>外部SphereShape3D；无实体阻挡</t>
+        </is>
+      </c>
+      <c r="K11" s="50" t="inlineStr">
+        <is>
+          <t>0.376×0.376×0.94m；176三角；外部倍率0.504</t>
+        </is>
+      </c>
+      <c r="L11" s="50" t="inlineStr">
+        <is>
+          <t>底面中心原点；Blender +Z向上，正面-Y；Godot +Y向上、正面+Z</t>
+        </is>
+      </c>
+      <c r="M11" s="50" t="inlineStr">
+        <is>
+          <t>地面与背包/商店图标</t>
+        </is>
+      </c>
+      <c r="N11" s="50" t="inlineStr">
+        <is>
+          <t>exported_pending_godot_validation</t>
+        </is>
+      </c>
+      <c r="O11" s="50" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P11" s="50" t="inlineStr">
+        <is>
+          <t>黄色弹壳；地面与图标共享；45度倾斜</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A4:P10"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
@@ -6792,7 +7242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="50" min="1" max="1"/>
@@ -7554,37 +8004,111 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="50" t="inlineStr">
         <is>
           <t>v0.1.100</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="50" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="50" t="inlineStr">
         <is>
           <t>物品道具双模型源</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="50" t="inlineStr">
         <is>
           <t>preview / ground</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="50" t="inlineStr">
         <is>
           <t>现有高模保留；地面100–200三角面</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="50" t="inlineStr">
         <is>
           <t>源已完成；运行时用途选择未接入</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="50" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="50" t="inlineStr">
+        <is>
+          <t>v0.1.101</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C26" s="50" t="inlineStr">
+        <is>
+          <t>地面简模正式路径与代码接线</t>
+        </is>
+      </c>
+      <c r="D26" s="50" t="inlineStr">
+        <is>
+          <t>8件物品ground角色</t>
+        </is>
+      </c>
+      <c r="E26" s="50" t="inlineStr">
+        <is>
+          <t>GLB/PackedScene/公共色盘导入；同一AssetID；预览待导入</t>
+        </is>
+      </c>
+      <c r="F26" s="50" t="inlineStr">
+        <is>
+          <t>exported_pending_godot_validation</t>
+        </is>
+      </c>
+      <c r="G26" s="50" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="50" t="inlineStr">
+        <is>
+          <t>v0.1.102</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C27" s="50" t="inlineStr">
+        <is>
+          <t>用户更正通用弹药用途</t>
+        </is>
+      </c>
+      <c r="D27" s="50" t="inlineStr">
+        <is>
+          <t>模型身份/图标/倾斜</t>
+        </is>
+      </c>
+      <c r="E27" s="50" t="inlineStr">
+        <is>
+          <t>通用弹药复用蓝金弹头；标准模块退回程序表现</t>
+        </is>
+      </c>
+      <c r="F27" s="50" t="inlineStr">
+        <is>
+          <t>已接线，待运行验收</t>
+        </is>
+      </c>
+      <c r="G27" s="50" t="inlineStr">
         <is>
           <t>Codex</t>
         </is>

--- a/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
@@ -15,9 +15,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3D-道具'!$A$4:$P$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3D-物品'!$A$4:$P$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3D-物品'!$A$4:$P$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -1504,22 +1504,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="51">
       <c r="A6" s="56">
-        <f>COUNTA('资产主表'!$A$6:$A$34)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$39)</f>
         <v/>
       </c>
       <c r="B6" s="54" t="n"/>
       <c r="C6" s="56">
-        <f>COUNTIF('资产主表'!$K$6:$K$34,"已完成")+COUNTIF('资产主表'!$K$6:$K$34,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$34,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$34,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$34,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$34,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$34,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$39,"已完成")+COUNTIF('资产主表'!$K$6:$K$39,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$39,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$39,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$39,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$39,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$39,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="54" t="n"/>
       <c r="E6" s="56">
-        <f>COUNTIF('资产主表'!$K$6:$K$34,"待制作")+COUNTIF('资产主表'!$K$6:$K$34,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$39,"待制作")+COUNTIF('资产主表'!$K$6:$K$39,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="54" t="n"/>
       <c r="G6" s="56">
-        <f>COUNTIF('资产主表'!$S$6:$S$34,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$39,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="54" t="n"/>
@@ -1588,11 +1588,11 @@
         </is>
       </c>
       <c r="B10" s="61">
-        <f>COUNTIF('资产主表'!$C$6:$C$34,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$39,A10)</f>
         <v/>
       </c>
       <c r="C10" s="61">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$34=A10)*(('资产主表'!$K$6:$K$34="已完成")+('资产主表'!$K$6:$K$34="原型已接入")+('资产主表'!$K$6:$K$34="正式美术已接入")+('资产主表'!$K$6:$K$34="已优化并正式接入")+('资产主表'!$K$6:$K$34="Blender源已完成")+('资产主表'!$K$6:$K$34="已导入；优化完成")+('资产主表'!$K$6:$K$34="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$39=A10)*(('资产主表'!$K$6:$K$39="已完成")+('资产主表'!$K$6:$K$39="原型已接入")+('资产主表'!$K$6:$K$39="正式美术已接入")+('资产主表'!$K$6:$K$39="已优化并正式接入")+('资产主表'!$K$6:$K$39="Blender源已完成")+('资产主表'!$K$6:$K$39="已导入；优化完成")+('资产主表'!$K$6:$K$39="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="61" t="n"/>
@@ -1610,11 +1610,11 @@
         </is>
       </c>
       <c r="B11" s="57">
-        <f>COUNTIF('资产主表'!$C$6:$C$34,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$39,A11)</f>
         <v/>
       </c>
       <c r="C11" s="57">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$34=A11)*(('资产主表'!$K$6:$K$34="已完成")+('资产主表'!$K$6:$K$34="原型已接入")+('资产主表'!$K$6:$K$34="正式美术已接入")+('资产主表'!$K$6:$K$34="已优化并正式接入")+('资产主表'!$K$6:$K$34="Blender源已完成")+('资产主表'!$K$6:$K$34="已导入；优化完成")+('资产主表'!$K$6:$K$34="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$39=A11)*(('资产主表'!$K$6:$K$39="已完成")+('资产主表'!$K$6:$K$39="原型已接入")+('资产主表'!$K$6:$K$39="正式美术已接入")+('资产主表'!$K$6:$K$39="已优化并正式接入")+('资产主表'!$K$6:$K$39="Blender源已完成")+('资产主表'!$K$6:$K$39="已导入；优化完成")+('资产主表'!$K$6:$K$39="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="57" t="n"/>
@@ -2182,7 +2182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y34"/>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="50" min="1" max="1"/>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="D6" s="75" t="inlineStr">
         <is>
-          <t>consumable</t>
+          <t>item</t>
         </is>
       </c>
       <c r="E6" s="75" t="inlineStr">
@@ -2413,27 +2413,27 @@
       <c r="G6" s="62" t="n"/>
       <c r="H6" s="62" t="inlineStr">
         <is>
-          <t>顶视/图标</t>
+          <t>top3d</t>
         </is>
       </c>
       <c r="I6" s="75" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J6" s="62" t="inlineStr">
         <is>
-          <t>世界拾取/UI 图标</t>
+          <t>地面/图标；preview独立源；item_beacon</t>
         </is>
       </c>
       <c r="K6" s="62" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>已优化并正式接入</t>
         </is>
       </c>
       <c r="L6" s="75" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M6" s="75" t="inlineStr">
@@ -2443,44 +2443,60 @@
       </c>
       <c r="N6" s="62" t="inlineStr">
         <is>
-          <t>世界 24–40 px；UI 32 px</t>
-        </is>
-      </c>
-      <c r="O6" s="62" t="n"/>
+          <t>Godot XYZ=[1.0134782791137695, 1.1100001335144043, 1.0134782791137695]m；ground 196三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O6" s="62" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/beacon/runtime/itm_beacon_ground_root_top3d.tscn</t>
+        </is>
+      </c>
       <c r="P6" s="75" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd</t>
-        </is>
-      </c>
-      <c r="Q6" s="62" t="n"/>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q6" s="62" t="inlineStr">
+        <is>
+          <t>撤离信标;item_beacon</t>
+        </is>
+      </c>
       <c r="R6" s="62">
         <f>LOWER(TRIM(C6)&amp;"|"&amp;TRIM(D6)&amp;"|"&amp;TRIM(E6)&amp;"|"&amp;TRIM(F6)&amp;"|"&amp;TRIM(H6)&amp;"|"&amp;TRIM(I6))</f>
         <v/>
       </c>
       <c r="S6" s="62">
-        <f>IF(COUNTIF($R$6:$R$34,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T6" s="62" t="n"/>
+      <c r="T6" s="62" t="inlineStr">
+        <is>
+          <t>9a762979bd12f38be7a1df5df67f93fd746e3d1c84621de766974f7728a922ba</t>
+        </is>
+      </c>
       <c r="U6" s="62" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V6" s="76" t="n">
-        <v>46224</v>
+        <v>46309</v>
       </c>
       <c r="W6" s="62" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
         </is>
       </c>
       <c r="X6" s="77" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y6" s="62" t="n"/>
+          <t>撤离信标_中文资产管理</t>
+        </is>
+      </c>
+      <c r="Y6" s="62" t="inlineStr">
+        <is>
+          <t>高精度源=art_source/items_weapons/props/beacon/source/itm_beacon_source_v001.blend；地面源=art_source/items_weapons/props/beacon/source/itm_beacon_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="51">
       <c r="A7" s="75" t="inlineStr">
@@ -2500,7 +2516,7 @@
       </c>
       <c r="D7" s="75" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>item</t>
         </is>
       </c>
       <c r="E7" s="75" t="inlineStr">
@@ -2516,27 +2532,27 @@
       <c r="G7" s="62" t="n"/>
       <c r="H7" s="62" t="inlineStr">
         <is>
-          <t>顶视/图标</t>
+          <t>top3d</t>
         </is>
       </c>
       <c r="I7" s="75" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>tier_0_static</t>
         </is>
       </c>
       <c r="J7" s="62" t="inlineStr">
         <is>
-          <t>世界拾取/UI 图标</t>
+          <t>地面/图标；preview独立源；item_room_key</t>
         </is>
       </c>
       <c r="K7" s="62" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>已优化并正式接入</t>
         </is>
       </c>
       <c r="L7" s="75" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M7" s="75" t="inlineStr">
@@ -2546,44 +2562,60 @@
       </c>
       <c r="N7" s="62" t="inlineStr">
         <is>
-          <t>世界 24–40 px；UI 32 px</t>
-        </is>
-      </c>
-      <c r="O7" s="62" t="n"/>
+          <t>Godot XYZ=[0.6731603145599365, 1.0649999380111694, 0.20596696436405182]m；ground 120三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O7" s="62" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/room_key/runtime/itm_room_key_ground_root_top3d.tscn</t>
+        </is>
+      </c>
       <c r="P7" s="75" t="inlineStr">
         <is>
-          <t>src/base/ItemRegistry.gd</t>
-        </is>
-      </c>
-      <c r="Q7" s="62" t="n"/>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q7" s="62" t="inlineStr">
+        <is>
+          <t>房间钥匙;item_room_key</t>
+        </is>
+      </c>
       <c r="R7" s="62">
         <f>LOWER(TRIM(C7)&amp;"|"&amp;TRIM(D7)&amp;"|"&amp;TRIM(E7)&amp;"|"&amp;TRIM(F7)&amp;"|"&amp;TRIM(H7)&amp;"|"&amp;TRIM(I7))</f>
         <v/>
       </c>
       <c r="S7" s="62">
-        <f>IF(COUNTIF($R$6:$R$34,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T7" s="62" t="n"/>
+      <c r="T7" s="62" t="inlineStr">
+        <is>
+          <t>c0d7d83015c25810d686dc520ce710ba39cff415c67bde61413660f9e8a15452</t>
+        </is>
+      </c>
       <c r="U7" s="62" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V7" s="76" t="n">
-        <v>46224</v>
+        <v>46309</v>
       </c>
       <c r="W7" s="62" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
         </is>
       </c>
       <c r="X7" s="77" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y7" s="62" t="n"/>
+          <t>房间钥匙_中文资产管理</t>
+        </is>
+      </c>
+      <c r="Y7" s="62" t="inlineStr">
+        <is>
+          <t>高精度源=art_source/items_weapons/props/room_key/source/itm_room_key_source_v001.blend；地面源=art_source/items_weapons/props/room_key/source/itm_room_key_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="51">
       <c r="A8" s="75" t="inlineStr">
@@ -2664,7 +2696,7 @@
         <v/>
       </c>
       <c r="S8" s="62">
-        <f>IF(COUNTIF($R$6:$R$34,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="62" t="n"/>
@@ -2767,7 +2799,7 @@
         <v/>
       </c>
       <c r="S9" s="62">
-        <f>IF(COUNTIF($R$6:$R$34,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="62" t="n"/>
@@ -2874,7 +2906,7 @@
         <v/>
       </c>
       <c r="S10" s="62">
-        <f>IF(COUNTIF($R$6:$R$34,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="75" t="inlineStr">
@@ -2991,7 +3023,7 @@
         <v/>
       </c>
       <c r="S11" s="62">
-        <f>IF(COUNTIF($R$6:$R$34,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="75" t="inlineStr">
@@ -3112,7 +3144,7 @@
         <v/>
       </c>
       <c r="S12" s="62">
-        <f>IF(COUNTIF($R$6:$R$34,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="75" t="inlineStr">
@@ -3233,7 +3265,7 @@
         <v/>
       </c>
       <c r="S13" s="62">
-        <f>IF(COUNTIF($R$6:$R$34,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="75" t="inlineStr">
@@ -3350,7 +3382,7 @@
         <v/>
       </c>
       <c r="S14" s="54">
-        <f>IF(COUNTIF($R$6:$R$34,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="78" t="n"/>
@@ -3469,7 +3501,7 @@
         <v/>
       </c>
       <c r="S15" s="80">
-        <f>IF(COUNTIF($R$6:$R$34,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="81" t="inlineStr">
@@ -3595,7 +3627,7 @@
         <v/>
       </c>
       <c r="S16" s="80">
-        <f>IF(COUNTIF($R$6:$R$34,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="81" t="inlineStr">
@@ -3721,7 +3753,7 @@
         <v/>
       </c>
       <c r="S17" s="80">
-        <f>IF(COUNTIF($R$6:$R$34,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="81" t="inlineStr">
@@ -3843,7 +3875,7 @@
         <v/>
       </c>
       <c r="S18" s="80">
-        <f>IF(COUNTIF($R$6:$R$34,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="81" t="inlineStr">
@@ -3968,7 +4000,7 @@
         <v/>
       </c>
       <c r="S19" s="80">
-        <f>IF(COUNTIF($R$6:$R$34,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="81" t="inlineStr">
@@ -4097,7 +4129,7 @@
         <v/>
       </c>
       <c r="S20" s="50">
-        <f>IF(COUNTIF($R$6:$R$34,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="83" t="inlineStr">
@@ -4220,7 +4252,7 @@
         <v/>
       </c>
       <c r="S21" s="50">
-        <f>IF(COUNTIF($R$6:$R$34,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="83" t="inlineStr">
@@ -4343,7 +4375,7 @@
         <v/>
       </c>
       <c r="S22" s="50">
-        <f>IF(COUNTIF($R$6:$R$34,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="83" t="inlineStr">
@@ -4466,7 +4498,7 @@
         <v/>
       </c>
       <c r="S23" s="50">
-        <f>IF(COUNTIF($R$6:$R$34,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="83" t="inlineStr">
@@ -4589,7 +4621,7 @@
         <v/>
       </c>
       <c r="S24" s="50">
-        <f>IF(COUNTIF($R$6:$R$34,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="83" t="inlineStr">
@@ -4712,7 +4744,7 @@
         <v/>
       </c>
       <c r="S25" s="50">
-        <f>IF(COUNTIF($R$6:$R$34,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="83" t="inlineStr">
@@ -4831,7 +4863,7 @@
         <v/>
       </c>
       <c r="S26" s="80">
-        <f>IF(COUNTIF($R$6:$R$34,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="81" t="inlineStr">
@@ -4950,7 +4982,7 @@
         <v/>
       </c>
       <c r="S27" s="80">
-        <f>IF(COUNTIF($R$6:$R$34,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="81" t="inlineStr">
@@ -5069,7 +5101,7 @@
         <v/>
       </c>
       <c r="S28" s="54">
-        <f>IF(COUNTIF($R$6:$R$34,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="78" t="n"/>
@@ -5184,7 +5216,7 @@
         <v/>
       </c>
       <c r="S29" s="54">
-        <f>IF(COUNTIF($R$6:$R$34,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="78" t="n"/>
@@ -5299,7 +5331,7 @@
         <v/>
       </c>
       <c r="S30" s="54">
-        <f>IF(COUNTIF($R$6:$R$34,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="78" t="n"/>
@@ -5414,7 +5446,7 @@
         <v/>
       </c>
       <c r="S31" s="62">
-        <f>IF(COUNTIF($R$6:$R$34,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="62" t="inlineStr">
@@ -5533,7 +5565,7 @@
         <v/>
       </c>
       <c r="S32" s="62">
-        <f>IF(COUNTIF($R$6:$R$34,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="62" t="inlineStr">
@@ -5652,7 +5684,7 @@
         <v/>
       </c>
       <c r="S33" s="62">
-        <f>IF(COUNTIF($R$6:$R$34,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="62" t="inlineStr">
@@ -5771,7 +5803,7 @@
         <v/>
       </c>
       <c r="S34" s="62">
-        <f>IF(COUNTIF($R$6:$R$34,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$39,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="62" t="inlineStr">
@@ -5800,6 +5832,601 @@
       <c r="Y34" s="62" t="inlineStr">
         <is>
           <t>通用弹药：黄色弹壳；地面/图标共用；preview源SHA256=a1302b8182d523834dc0af9741eb687044489f66cafa0cfbcbf79d1de1d565d3；ground源SHA256=3d7baf9637ba5bc14982366f0663af93102512c4c04335b77104983208c3f88c；原尺寸与176三角预算保持。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="75" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-CELL-PACK</t>
+        </is>
+      </c>
+      <c r="B35" s="62" t="inlineStr">
+        <is>
+          <t>电芯包</t>
+        </is>
+      </c>
+      <c r="C35" s="62" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D35" s="75" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="E35" s="75" t="inlineStr">
+        <is>
+          <t>item_cell_pack</t>
+        </is>
+      </c>
+      <c r="F35" s="75" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="G35" s="62" t="n"/>
+      <c r="H35" s="62" t="inlineStr">
+        <is>
+          <t>top3d</t>
+        </is>
+      </c>
+      <c r="I35" s="75" t="inlineStr">
+        <is>
+          <t>tier_0_static</t>
+        </is>
+      </c>
+      <c r="J35" s="62" t="inlineStr">
+        <is>
+          <t>地面/图标；preview独立源；item_cell_pack</t>
+        </is>
+      </c>
+      <c r="K35" s="62" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="L35" s="75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M35" s="75" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N35" s="62" t="inlineStr">
+        <is>
+          <t>Godot XYZ=[0.6796196103096008, 0.7625001072883606, 0.3108016550540924]m；ground 156三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O35" s="62" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/cell_pack/runtime/itm_cell_pack_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P35" s="75" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q35" s="62" t="inlineStr">
+        <is>
+          <t>电芯包;item_cell_pack</t>
+        </is>
+      </c>
+      <c r="R35" s="62">
+        <f>LOWER(TRIM(C35)&amp;"|"&amp;TRIM(D35)&amp;"|"&amp;TRIM(E35)&amp;"|"&amp;TRIM(F35)&amp;"|"&amp;TRIM(H35)&amp;"|"&amp;TRIM(I35))</f>
+        <v/>
+      </c>
+      <c r="S35" s="62">
+        <f>IF(COUNTIF($R$6:$R$39,R35)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T35" s="62" t="inlineStr">
+        <is>
+          <t>793742bf5cce258d7679807b298fb30aefa6858e85de498dce9b45a3ba505199</t>
+        </is>
+      </c>
+      <c r="U35" s="62" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V35" s="76" t="n">
+        <v>46309</v>
+      </c>
+      <c r="W35" s="62" t="inlineStr">
+        <is>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
+        </is>
+      </c>
+      <c r="X35" s="77" t="inlineStr">
+        <is>
+          <t>电芯包_中文资产管理</t>
+        </is>
+      </c>
+      <c r="Y35" s="62" t="inlineStr">
+        <is>
+          <t>高精度源=art_source/items_weapons/props/cell_pack/source/itm_cell_pack_source_v001.blend；地面源=art_source/items_weapons/props/cell_pack/source/itm_cell_pack_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="75" t="inlineStr">
+        <is>
+          <t>ITM-MODULE-FLASHLIGHT-BASIC</t>
+        </is>
+      </c>
+      <c r="B36" s="62" t="inlineStr">
+        <is>
+          <t>基础模块</t>
+        </is>
+      </c>
+      <c r="C36" s="62" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D36" s="75" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="E36" s="75" t="inlineStr">
+        <is>
+          <t>item_flashlight_basic</t>
+        </is>
+      </c>
+      <c r="F36" s="75" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="G36" s="62" t="n"/>
+      <c r="H36" s="62" t="inlineStr">
+        <is>
+          <t>top3d</t>
+        </is>
+      </c>
+      <c r="I36" s="75" t="inlineStr">
+        <is>
+          <t>tier_0_static</t>
+        </is>
+      </c>
+      <c r="J36" s="62" t="inlineStr">
+        <is>
+          <t>地面/图标；preview独立源；item_flashlight_basic</t>
+        </is>
+      </c>
+      <c r="K36" s="62" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="L36" s="75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M36" s="75" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N36" s="62" t="inlineStr">
+        <is>
+          <t>Godot XYZ=[0.5909375548362732, 0.7625000476837158, 0.45988285541534424]m；ground 116三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O36" s="62" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/flashlight_basic/runtime/itm_flashlight_basic_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P36" s="75" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q36" s="62" t="inlineStr">
+        <is>
+          <t>基础模块;item_flashlight_basic</t>
+        </is>
+      </c>
+      <c r="R36" s="62">
+        <f>LOWER(TRIM(C36)&amp;"|"&amp;TRIM(D36)&amp;"|"&amp;TRIM(E36)&amp;"|"&amp;TRIM(F36)&amp;"|"&amp;TRIM(H36)&amp;"|"&amp;TRIM(I36))</f>
+        <v/>
+      </c>
+      <c r="S36" s="62">
+        <f>IF(COUNTIF($R$6:$R$39,R36)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T36" s="62" t="inlineStr">
+        <is>
+          <t>857d03929333b21c18fde2eba27a7ceb127aa40e9c117a096b9ae8187b2bd6ff</t>
+        </is>
+      </c>
+      <c r="U36" s="62" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V36" s="76" t="n">
+        <v>46309</v>
+      </c>
+      <c r="W36" s="62" t="inlineStr">
+        <is>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
+        </is>
+      </c>
+      <c r="X36" s="77" t="inlineStr">
+        <is>
+          <t>基础模块_中文资产管理</t>
+        </is>
+      </c>
+      <c r="Y36" s="62" t="inlineStr">
+        <is>
+          <t>高精度源=art_source/items_weapons/props/flashlight_basic/source/itm_flashlight_basic_source_v001.blend；地面源=art_source/items_weapons/props/flashlight_basic/source/itm_flashlight_basic_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="75" t="inlineStr">
+        <is>
+          <t>ITM-MODULE-FLASHLIGHT-ADVANCED</t>
+        </is>
+      </c>
+      <c r="B37" s="62" t="inlineStr">
+        <is>
+          <t>加强模块</t>
+        </is>
+      </c>
+      <c r="C37" s="62" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D37" s="75" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="E37" s="75" t="inlineStr">
+        <is>
+          <t>item_flashlight_advanced</t>
+        </is>
+      </c>
+      <c r="F37" s="75" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="G37" s="62" t="n"/>
+      <c r="H37" s="62" t="inlineStr">
+        <is>
+          <t>top3d</t>
+        </is>
+      </c>
+      <c r="I37" s="75" t="inlineStr">
+        <is>
+          <t>tier_0_static</t>
+        </is>
+      </c>
+      <c r="J37" s="62" t="inlineStr">
+        <is>
+          <t>地面/图标；preview独立源；item_flashlight_advanced</t>
+        </is>
+      </c>
+      <c r="K37" s="62" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="L37" s="75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M37" s="75" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N37" s="62" t="inlineStr">
+        <is>
+          <t>Godot XYZ=[0.5909375548362732, 0.7625000476837158, 0.45988285541534424]m；ground 128三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O37" s="62" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/flashlight_advanced/runtime/itm_flashlight_advanced_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P37" s="75" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q37" s="62" t="inlineStr">
+        <is>
+          <t>加强模块;item_flashlight_advanced</t>
+        </is>
+      </c>
+      <c r="R37" s="62">
+        <f>LOWER(TRIM(C37)&amp;"|"&amp;TRIM(D37)&amp;"|"&amp;TRIM(E37)&amp;"|"&amp;TRIM(F37)&amp;"|"&amp;TRIM(H37)&amp;"|"&amp;TRIM(I37))</f>
+        <v/>
+      </c>
+      <c r="S37" s="62">
+        <f>IF(COUNTIF($R$6:$R$39,R37)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T37" s="62" t="inlineStr">
+        <is>
+          <t>ffc807de1601abc3d9b1b673961e440a0461dce699f26e35f4c2010e2885684c</t>
+        </is>
+      </c>
+      <c r="U37" s="62" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V37" s="76" t="n">
+        <v>46309</v>
+      </c>
+      <c r="W37" s="62" t="inlineStr">
+        <is>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
+        </is>
+      </c>
+      <c r="X37" s="77" t="inlineStr">
+        <is>
+          <t>加强模块_中文资产管理</t>
+        </is>
+      </c>
+      <c r="Y37" s="62" t="inlineStr">
+        <is>
+          <t>高精度源=art_source/items_weapons/props/flashlight_advanced/source/itm_flashlight_advanced_source_v001.blend；地面源=art_source/items_weapons/props/flashlight_advanced/source/itm_flashlight_advanced_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="75" t="inlineStr">
+        <is>
+          <t>ITM-MODULE-FLASHLIGHT-EFFICIENT</t>
+        </is>
+      </c>
+      <c r="B38" s="62" t="inlineStr">
+        <is>
+          <t>节能模块</t>
+        </is>
+      </c>
+      <c r="C38" s="62" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D38" s="75" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="E38" s="75" t="inlineStr">
+        <is>
+          <t>item_flashlight_efficient</t>
+        </is>
+      </c>
+      <c r="F38" s="75" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="G38" s="62" t="n"/>
+      <c r="H38" s="62" t="inlineStr">
+        <is>
+          <t>top3d</t>
+        </is>
+      </c>
+      <c r="I38" s="75" t="inlineStr">
+        <is>
+          <t>tier_0_static</t>
+        </is>
+      </c>
+      <c r="J38" s="62" t="inlineStr">
+        <is>
+          <t>地面/图标；preview独立源；item_flashlight_efficient</t>
+        </is>
+      </c>
+      <c r="K38" s="62" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="L38" s="75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M38" s="75" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N38" s="62" t="inlineStr">
+        <is>
+          <t>Godot XYZ=[0.5909375548362732, 0.7625000476837158, 0.45988285541534424]m；ground 116三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O38" s="62" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/flashlight_efficient/runtime/itm_flashlight_efficient_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P38" s="75" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q38" s="62" t="inlineStr">
+        <is>
+          <t>节能模块;item_flashlight_efficient</t>
+        </is>
+      </c>
+      <c r="R38" s="62">
+        <f>LOWER(TRIM(C38)&amp;"|"&amp;TRIM(D38)&amp;"|"&amp;TRIM(E38)&amp;"|"&amp;TRIM(F38)&amp;"|"&amp;TRIM(H38)&amp;"|"&amp;TRIM(I38))</f>
+        <v/>
+      </c>
+      <c r="S38" s="62">
+        <f>IF(COUNTIF($R$6:$R$39,R38)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T38" s="62" t="inlineStr">
+        <is>
+          <t>81cd8836e23c0072578a16e4e27a80a0da14db57d076463012012542c4dba841</t>
+        </is>
+      </c>
+      <c r="U38" s="62" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V38" s="76" t="n">
+        <v>46309</v>
+      </c>
+      <c r="W38" s="62" t="inlineStr">
+        <is>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
+        </is>
+      </c>
+      <c r="X38" s="77" t="inlineStr">
+        <is>
+          <t>节能模块_中文资产管理</t>
+        </is>
+      </c>
+      <c r="Y38" s="62" t="inlineStr">
+        <is>
+          <t>高精度源=art_source/items_weapons/props/flashlight_efficient/source/itm_flashlight_efficient_source_v001.blend；地面源=art_source/items_weapons/props/flashlight_efficient/source/itm_flashlight_efficient_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="75" t="inlineStr">
+        <is>
+          <t>ITM-BLUEPRINT-SHARED-SCROLL</t>
+        </is>
+      </c>
+      <c r="B39" s="62" t="inlineStr">
+        <is>
+          <t>通用蓝图卷轴</t>
+        </is>
+      </c>
+      <c r="C39" s="62" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D39" s="75" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="E39" s="75" t="inlineStr">
+        <is>
+          <t>blueprint_shared</t>
+        </is>
+      </c>
+      <c r="F39" s="75" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="G39" s="62" t="n"/>
+      <c r="H39" s="62" t="inlineStr">
+        <is>
+          <t>top3d</t>
+        </is>
+      </c>
+      <c r="I39" s="75" t="inlineStr">
+        <is>
+          <t>tier_0_static</t>
+        </is>
+      </c>
+      <c r="J39" s="62" t="inlineStr">
+        <is>
+          <t>地面/图标；preview独立源；bp_pistol,bp_shotgun,bp_sprinkler,bp_starter_rifle,bp_rifle,bp_machinegun,bp_sniper,bp_launcher,bp_charge</t>
+        </is>
+      </c>
+      <c r="K39" s="62" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="L39" s="75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M39" s="75" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N39" s="62" t="inlineStr">
+        <is>
+          <t>Godot XYZ=[0.7628571391105652, 0.9000000357627869, 0.22285713255405426]m；ground 116三角；公共色盘；原点bottom_center</t>
+        </is>
+      </c>
+      <c r="O39" s="62" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P39" s="75" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd; docs/v0.1/design/物品道具双模型制作规范.md</t>
+        </is>
+      </c>
+      <c r="Q39" s="62" t="inlineStr">
+        <is>
+          <t>通用蓝图卷轴;bp_pistol,bp_shotgun,bp_sprinkler,bp_starter_rifle,bp_rifle,bp_machinegun,bp_sniper,bp_launcher,bp_charge</t>
+        </is>
+      </c>
+      <c r="R39" s="62">
+        <f>LOWER(TRIM(C39)&amp;"|"&amp;TRIM(D39)&amp;"|"&amp;TRIM(E39)&amp;"|"&amp;TRIM(F39)&amp;"|"&amp;TRIM(H39)&amp;"|"&amp;TRIM(I39))</f>
+        <v/>
+      </c>
+      <c r="S39" s="62">
+        <f>IF(COUNTIF($R$6:$R$39,R39)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T39" s="62" t="inlineStr">
+        <is>
+          <t>7ce51ba228751caad09283f38cdb31fd9d142339a7e958662df321f0565f12a6</t>
+        </is>
+      </c>
+      <c r="U39" s="62" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V39" s="76" t="n">
+        <v>46309</v>
+      </c>
+      <c r="W39" s="62" t="inlineStr">
+        <is>
+          <t>用户风格延续；程序制作原创组件；项目公共色盘</t>
+        </is>
+      </c>
+      <c r="X39" s="77" t="inlineStr">
+        <is>
+          <t>通用蓝图卷轴_中文资产管理</t>
+        </is>
+      </c>
+      <c r="Y39" s="62" t="inlineStr">
+        <is>
+          <t>高精度源=art_source/items_weapons/props/blueprint_scroll/source/itm_blueprint_scroll_source_v001.blend；地面源=art_source/items_weapons/props/blueprint_scroll/source/itm_blueprint_scroll_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6638,7 @@
     <row r="427" ht="84.75" customHeight="1" s="51"/>
     <row r="429" ht="120" customHeight="1" s="51"/>
   </sheetData>
-  <autoFilter ref="A5:Y34"/>
+  <autoFilter ref="A5:Y39"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
@@ -6030,15 +6657,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K6:K34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L6:L34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6519,7 +7146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="35.81" customWidth="1" style="50" min="1" max="1"/>
@@ -7210,8 +7837,1156 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="86" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-BEACON</t>
+        </is>
+      </c>
+      <c r="B12" s="87" t="inlineStr">
+        <is>
+          <t>撤离信标 / preview</t>
+        </is>
+      </c>
+      <c r="C12" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/beacon/runtime/itm_beacon_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D12" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/beacon/components/itm_beacon_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E12" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/beacon/source/itm_beacon_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F12" s="87" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G12" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H12" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I12" s="87" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J12" s="87" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K12" s="87" t="inlineStr">
+        <is>
+          <t>[1.0134782791137695, 1.1100001335144043, 1.0134782791137695]；1520三角</t>
+        </is>
+      </c>
+      <c r="L12" s="87" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M12" s="87" t="inlineStr">
+        <is>
+          <t>item_beacon</t>
+        </is>
+      </c>
+      <c r="N12" s="87" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O12" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P12" s="89" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="86" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-BEACON</t>
+        </is>
+      </c>
+      <c r="B13" s="87" t="inlineStr">
+        <is>
+          <t>撤离信标 / ground</t>
+        </is>
+      </c>
+      <c r="C13" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/beacon/runtime/itm_beacon_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D13" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/beacon/components/itm_beacon_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E13" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/beacon/source/itm_beacon_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F13" s="87" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G13" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H13" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I13" s="87" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J13" s="87" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K13" s="87" t="inlineStr">
+        <is>
+          <t>[1.0134782791137695, 1.1100001335144043, 1.0134782791137695]；196三角</t>
+        </is>
+      </c>
+      <c r="L13" s="87" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M13" s="87" t="inlineStr">
+        <is>
+          <t>item_beacon</t>
+        </is>
+      </c>
+      <c r="N13" s="87" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O13" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P13" s="89" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="86" t="inlineStr">
+        <is>
+          <t>ITM-KEY-ITEM-ROOM-KEY</t>
+        </is>
+      </c>
+      <c r="B14" s="87" t="inlineStr">
+        <is>
+          <t>房间钥匙 / preview</t>
+        </is>
+      </c>
+      <c r="C14" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/room_key/runtime/itm_room_key_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D14" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/room_key/components/itm_room_key_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E14" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/room_key/source/itm_room_key_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F14" s="87" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G14" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H14" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I14" s="87" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J14" s="87" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K14" s="87" t="inlineStr">
+        <is>
+          <t>[0.6731603145599365, 1.0649999380111694, 0.20596696436405182]；1136三角</t>
+        </is>
+      </c>
+      <c r="L14" s="87" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M14" s="87" t="inlineStr">
+        <is>
+          <t>item_room_key</t>
+        </is>
+      </c>
+      <c r="N14" s="87" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O14" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P14" s="89" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="86" t="inlineStr">
+        <is>
+          <t>ITM-KEY-ITEM-ROOM-KEY</t>
+        </is>
+      </c>
+      <c r="B15" s="87" t="inlineStr">
+        <is>
+          <t>房间钥匙 / ground</t>
+        </is>
+      </c>
+      <c r="C15" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/room_key/runtime/itm_room_key_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D15" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/room_key/components/itm_room_key_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E15" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/room_key/source/itm_room_key_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F15" s="87" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G15" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H15" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I15" s="87" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J15" s="87" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K15" s="87" t="inlineStr">
+        <is>
+          <t>[0.6731603145599365, 1.0649999380111694, 0.20596696436405182]；120三角</t>
+        </is>
+      </c>
+      <c r="L15" s="87" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M15" s="87" t="inlineStr">
+        <is>
+          <t>item_room_key</t>
+        </is>
+      </c>
+      <c r="N15" s="87" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O15" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P15" s="89" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="86" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-CELL-PACK</t>
+        </is>
+      </c>
+      <c r="B16" s="87" t="inlineStr">
+        <is>
+          <t>电芯包 / preview</t>
+        </is>
+      </c>
+      <c r="C16" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/cell_pack/runtime/itm_cell_pack_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D16" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/cell_pack/components/itm_cell_pack_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E16" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/cell_pack/source/itm_cell_pack_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F16" s="87" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G16" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H16" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I16" s="87" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J16" s="87" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K16" s="87" t="inlineStr">
+        <is>
+          <t>[0.6796196103096008, 0.7625001072883606, 0.3108016550540924]；1692三角</t>
+        </is>
+      </c>
+      <c r="L16" s="87" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M16" s="87" t="inlineStr">
+        <is>
+          <t>item_cell_pack</t>
+        </is>
+      </c>
+      <c r="N16" s="87" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O16" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P16" s="89" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="86" t="inlineStr">
+        <is>
+          <t>ITM-CONSUMABLE-ITEM-CELL-PACK</t>
+        </is>
+      </c>
+      <c r="B17" s="87" t="inlineStr">
+        <is>
+          <t>电芯包 / ground</t>
+        </is>
+      </c>
+      <c r="C17" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/cell_pack/runtime/itm_cell_pack_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D17" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/cell_pack/components/itm_cell_pack_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E17" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/cell_pack/source/itm_cell_pack_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F17" s="87" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G17" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H17" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I17" s="87" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J17" s="87" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K17" s="87" t="inlineStr">
+        <is>
+          <t>[0.6796196103096008, 0.7625001072883606, 0.3108016550540924]；156三角</t>
+        </is>
+      </c>
+      <c r="L17" s="87" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M17" s="87" t="inlineStr">
+        <is>
+          <t>item_cell_pack</t>
+        </is>
+      </c>
+      <c r="N17" s="87" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O17" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P17" s="89" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="86" t="inlineStr">
+        <is>
+          <t>ITM-MODULE-FLASHLIGHT-BASIC</t>
+        </is>
+      </c>
+      <c r="B18" s="87" t="inlineStr">
+        <is>
+          <t>基础模块 / preview</t>
+        </is>
+      </c>
+      <c r="C18" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/flashlight_basic/runtime/itm_flashlight_basic_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D18" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/flashlight_basic/components/itm_flashlight_basic_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E18" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/flashlight_basic/source/itm_flashlight_basic_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F18" s="87" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G18" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H18" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I18" s="87" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J18" s="87" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K18" s="87" t="inlineStr">
+        <is>
+          <t>[0.5909375548362732, 0.7625000476837158, 0.45988285541534424]；1316三角</t>
+        </is>
+      </c>
+      <c r="L18" s="87" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M18" s="87" t="inlineStr">
+        <is>
+          <t>item_flashlight_basic</t>
+        </is>
+      </c>
+      <c r="N18" s="87" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O18" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P18" s="89" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="86" t="inlineStr">
+        <is>
+          <t>ITM-MODULE-FLASHLIGHT-BASIC</t>
+        </is>
+      </c>
+      <c r="B19" s="87" t="inlineStr">
+        <is>
+          <t>基础模块 / ground</t>
+        </is>
+      </c>
+      <c r="C19" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/flashlight_basic/runtime/itm_flashlight_basic_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D19" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/flashlight_basic/components/itm_flashlight_basic_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E19" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/flashlight_basic/source/itm_flashlight_basic_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F19" s="87" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G19" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H19" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I19" s="87" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J19" s="87" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K19" s="87" t="inlineStr">
+        <is>
+          <t>[0.5909375548362732, 0.7625000476837158, 0.45988285541534424]；116三角</t>
+        </is>
+      </c>
+      <c r="L19" s="87" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M19" s="87" t="inlineStr">
+        <is>
+          <t>item_flashlight_basic</t>
+        </is>
+      </c>
+      <c r="N19" s="87" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O19" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P19" s="89" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="86" t="inlineStr">
+        <is>
+          <t>ITM-MODULE-FLASHLIGHT-ADVANCED</t>
+        </is>
+      </c>
+      <c r="B20" s="87" t="inlineStr">
+        <is>
+          <t>加强模块 / preview</t>
+        </is>
+      </c>
+      <c r="C20" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/flashlight_advanced/runtime/itm_flashlight_advanced_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D20" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/flashlight_advanced/components/itm_flashlight_advanced_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E20" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/flashlight_advanced/source/itm_flashlight_advanced_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F20" s="87" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G20" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H20" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I20" s="87" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J20" s="87" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K20" s="87" t="inlineStr">
+        <is>
+          <t>[0.5909375548362732, 0.7625000476837158, 0.45988285541534424]；1504三角</t>
+        </is>
+      </c>
+      <c r="L20" s="87" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M20" s="87" t="inlineStr">
+        <is>
+          <t>item_flashlight_advanced</t>
+        </is>
+      </c>
+      <c r="N20" s="87" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O20" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P20" s="89" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="86" t="inlineStr">
+        <is>
+          <t>ITM-MODULE-FLASHLIGHT-ADVANCED</t>
+        </is>
+      </c>
+      <c r="B21" s="87" t="inlineStr">
+        <is>
+          <t>加强模块 / ground</t>
+        </is>
+      </c>
+      <c r="C21" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/flashlight_advanced/runtime/itm_flashlight_advanced_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D21" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/flashlight_advanced/components/itm_flashlight_advanced_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E21" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/flashlight_advanced/source/itm_flashlight_advanced_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F21" s="87" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G21" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H21" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I21" s="87" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J21" s="87" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K21" s="87" t="inlineStr">
+        <is>
+          <t>[0.5909375548362732, 0.7625000476837158, 0.45988285541534424]；128三角</t>
+        </is>
+      </c>
+      <c r="L21" s="87" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M21" s="87" t="inlineStr">
+        <is>
+          <t>item_flashlight_advanced</t>
+        </is>
+      </c>
+      <c r="N21" s="87" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O21" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P21" s="89" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="86" t="inlineStr">
+        <is>
+          <t>ITM-MODULE-FLASHLIGHT-EFFICIENT</t>
+        </is>
+      </c>
+      <c r="B22" s="87" t="inlineStr">
+        <is>
+          <t>节能模块 / preview</t>
+        </is>
+      </c>
+      <c r="C22" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/flashlight_efficient/runtime/itm_flashlight_efficient_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D22" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/flashlight_efficient/components/itm_flashlight_efficient_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E22" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/flashlight_efficient/source/itm_flashlight_efficient_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F22" s="87" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G22" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H22" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I22" s="87" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J22" s="87" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K22" s="87" t="inlineStr">
+        <is>
+          <t>[0.5909375548362732, 0.7625000476837158, 0.45988285541534424]；1316三角</t>
+        </is>
+      </c>
+      <c r="L22" s="87" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M22" s="87" t="inlineStr">
+        <is>
+          <t>item_flashlight_efficient</t>
+        </is>
+      </c>
+      <c r="N22" s="87" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O22" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P22" s="89" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="86" t="inlineStr">
+        <is>
+          <t>ITM-MODULE-FLASHLIGHT-EFFICIENT</t>
+        </is>
+      </c>
+      <c r="B23" s="87" t="inlineStr">
+        <is>
+          <t>节能模块 / ground</t>
+        </is>
+      </c>
+      <c r="C23" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/flashlight_efficient/runtime/itm_flashlight_efficient_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D23" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/flashlight_efficient/components/itm_flashlight_efficient_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E23" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/flashlight_efficient/source/itm_flashlight_efficient_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F23" s="87" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G23" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H23" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I23" s="87" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J23" s="87" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K23" s="87" t="inlineStr">
+        <is>
+          <t>[0.5909375548362732, 0.7625000476837158, 0.45988285541534424]；116三角</t>
+        </is>
+      </c>
+      <c r="L23" s="87" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M23" s="87" t="inlineStr">
+        <is>
+          <t>item_flashlight_efficient</t>
+        </is>
+      </c>
+      <c r="N23" s="87" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O23" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P23" s="89" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="86" t="inlineStr">
+        <is>
+          <t>ITM-BLUEPRINT-SHARED-SCROLL</t>
+        </is>
+      </c>
+      <c r="B24" s="87" t="inlineStr">
+        <is>
+          <t>通用蓝图卷轴 / preview</t>
+        </is>
+      </c>
+      <c r="C24" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_preview_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D24" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/blueprint_scroll/components/itm_blueprint_scroll_preview_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E24" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/blueprint_scroll/source/itm_blueprint_scroll_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F24" s="87" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G24" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H24" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I24" s="87" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J24" s="87" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K24" s="87" t="inlineStr">
+        <is>
+          <t>[0.7628571391105652, 0.9000000357627869, 0.22285713255405426]；1316三角</t>
+        </is>
+      </c>
+      <c r="L24" s="87" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M24" s="87" t="inlineStr">
+        <is>
+          <t>bp_pistol,bp_shotgun,bp_sprinkler,bp_starter_rifle,bp_rifle,bp_machinegun,bp_sniper,bp_launcher,bp_charge</t>
+        </is>
+      </c>
+      <c r="N24" s="87" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O24" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P24" s="89" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="86" t="inlineStr">
+        <is>
+          <t>ITM-BLUEPRINT-SHARED-SCROLL</t>
+        </is>
+      </c>
+      <c r="B25" s="87" t="inlineStr">
+        <is>
+          <t>通用蓝图卷轴 / ground</t>
+        </is>
+      </c>
+      <c r="C25" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/blueprint_scroll/runtime/itm_blueprint_scroll_ground_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D25" s="88" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/props/blueprint_scroll/components/itm_blueprint_scroll_ground_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E25" s="88" t="inlineStr">
+        <is>
+          <t>art_source/items_weapons/props/blueprint_scroll/source/itm_blueprint_scroll_ground_source_v001.blend</t>
+        </is>
+      </c>
+      <c r="F25" s="87" t="inlineStr">
+        <is>
+          <t>纯视觉；游戏规则由原系统持有</t>
+        </is>
+      </c>
+      <c r="G25" s="87" t="inlineStr">
+        <is>
+          <t>src/world3d/ItemModelFactory3D.gd; src/combat3d/WeaponModel3D.gd</t>
+        </is>
+      </c>
+      <c r="H25" s="87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I25" s="87" t="inlineStr">
+        <is>
+          <t>外部玩法</t>
+        </is>
+      </c>
+      <c r="J25" s="87" t="inlineStr">
+        <is>
+          <t>外部拾取球/原近战扫掠</t>
+        </is>
+      </c>
+      <c r="K25" s="87" t="inlineStr">
+        <is>
+          <t>[0.7628571391105652, 0.9000000357627869, 0.22285713255405426]；116三角</t>
+        </is>
+      </c>
+      <c r="L25" s="87" t="inlineStr">
+        <is>
+          <t>bottom_center；Godot Y上，近战-Z前</t>
+        </is>
+      </c>
+      <c r="M25" s="87" t="inlineStr">
+        <is>
+          <t>bp_pistol,bp_shotgun,bp_sprinkler,bp_starter_rifle,bp_rifle,bp_machinegun,bp_sniper,bp_launcher,bp_charge</t>
+        </is>
+      </c>
+      <c r="N25" s="87" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="O25" s="87" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P25" s="89" t="inlineStr">
+        <is>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:P10"/>
+  <autoFilter ref="A4:P25"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
@@ -7242,7 +9017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="50" min="1" max="1"/>
@@ -8114,6 +9889,43 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>v0.1.103</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C28" s="50" t="inlineStr">
+        <is>
+          <t>剩余程序化物品20模型/28内容ID</t>
+        </is>
+      </c>
+      <c r="D28" s="50" t="inlineStr">
+        <is>
+          <t>双模型/GLB/PackedScene/调用链</t>
+        </is>
+      </c>
+      <c r="E28" s="50" t="inlineStr">
+        <is>
+          <t>100–200三角；蓝图共用；真实渲染及映射通过</t>
+        </is>
+      </c>
+      <c r="F28" s="50" t="inlineStr">
+        <is>
+          <t>已优化并正式接入</t>
+        </is>
+      </c>
+      <c r="G28" s="50" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3D-道具'!$A$4:$P$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3D-物品'!$A$4:$P$25</definedName>
   </definedNames>
@@ -1504,22 +1504,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="51">
       <c r="A6" s="56">
-        <f>COUNTA('资产主表'!$A$6:$A$39)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$44)</f>
         <v/>
       </c>
       <c r="B6" s="54" t="n"/>
       <c r="C6" s="56">
-        <f>COUNTIF('资产主表'!$K$6:$K$39,"已完成")+COUNTIF('资产主表'!$K$6:$K$39,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$39,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$39,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$39,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$39,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$39,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$44,"已完成")+COUNTIF('资产主表'!$K$6:$K$44,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$44,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$44,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$44,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$44,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$44,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="54" t="n"/>
       <c r="E6" s="56">
-        <f>COUNTIF('资产主表'!$K$6:$K$39,"待制作")+COUNTIF('资产主表'!$K$6:$K$39,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$44,"待制作")+COUNTIF('资产主表'!$K$6:$K$44,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="54" t="n"/>
       <c r="G6" s="56">
-        <f>COUNTIF('资产主表'!$S$6:$S$39,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$44,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="54" t="n"/>
@@ -1588,11 +1588,11 @@
         </is>
       </c>
       <c r="B10" s="61">
-        <f>COUNTIF('资产主表'!$C$6:$C$39,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$44,A10)</f>
         <v/>
       </c>
       <c r="C10" s="61">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$39=A10)*(('资产主表'!$K$6:$K$39="已完成")+('资产主表'!$K$6:$K$39="原型已接入")+('资产主表'!$K$6:$K$39="正式美术已接入")+('资产主表'!$K$6:$K$39="已优化并正式接入")+('资产主表'!$K$6:$K$39="Blender源已完成")+('资产主表'!$K$6:$K$39="已导入；优化完成")+('资产主表'!$K$6:$K$39="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$44=A10)*(('资产主表'!$K$6:$K$44="已完成")+('资产主表'!$K$6:$K$44="原型已接入")+('资产主表'!$K$6:$K$44="正式美术已接入")+('资产主表'!$K$6:$K$44="已优化并正式接入")+('资产主表'!$K$6:$K$44="Blender源已完成")+('资产主表'!$K$6:$K$44="已导入；优化完成")+('资产主表'!$K$6:$K$44="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="61" t="n"/>
@@ -1610,11 +1610,11 @@
         </is>
       </c>
       <c r="B11" s="57">
-        <f>COUNTIF('资产主表'!$C$6:$C$39,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$44,A11)</f>
         <v/>
       </c>
       <c r="C11" s="57">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$39=A11)*(('资产主表'!$K$6:$K$39="已完成")+('资产主表'!$K$6:$K$39="原型已接入")+('资产主表'!$K$6:$K$39="正式美术已接入")+('资产主表'!$K$6:$K$39="已优化并正式接入")+('资产主表'!$K$6:$K$39="Blender源已完成")+('资产主表'!$K$6:$K$39="已导入；优化完成")+('资产主表'!$K$6:$K$39="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$44=A11)*(('资产主表'!$K$6:$K$44="已完成")+('资产主表'!$K$6:$K$44="原型已接入")+('资产主表'!$K$6:$K$44="正式美术已接入")+('资产主表'!$K$6:$K$44="已优化并正式接入")+('资产主表'!$K$6:$K$44="Blender源已完成")+('资产主表'!$K$6:$K$44="已导入；优化完成")+('资产主表'!$K$6:$K$44="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="57" t="n"/>
@@ -2182,7 +2182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y39"/>
+  <dimension ref="A1:Y44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="29.84" customWidth="1" style="50" min="1" max="1"/>
@@ -2466,7 +2466,7 @@
         <v/>
       </c>
       <c r="S6" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="62" t="inlineStr">
@@ -2479,8 +2479,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V6" s="76" t="n">
-        <v>46309</v>
+      <c r="V6" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W6" s="62" t="inlineStr">
         <is>
@@ -2494,7 +2496,9 @@
       </c>
       <c r="Y6" s="62" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/props/beacon/source/itm_beacon_source_v001.blend；地面源=art_source/items_weapons/props/beacon/source/itm_beacon_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/props/beacon/source/itm_beacon_source_v001.blend；地面源=art_source/items_weapons/props/beacon/source/itm_beacon_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2589,7 @@
         <v/>
       </c>
       <c r="S7" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="62" t="inlineStr">
@@ -2598,8 +2602,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V7" s="76" t="n">
-        <v>46309</v>
+      <c r="V7" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W7" s="62" t="inlineStr">
         <is>
@@ -2613,7 +2619,9 @@
       </c>
       <c r="Y7" s="62" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/props/room_key/source/itm_room_key_source_v001.blend；地面源=art_source/items_weapons/props/room_key/source/itm_room_key_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/props/room_key/source/itm_room_key_source_v001.blend；地面源=art_source/items_weapons/props/room_key/source/itm_room_key_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2704,7 @@
         <v/>
       </c>
       <c r="S8" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="62" t="n"/>
@@ -2799,7 +2807,7 @@
         <v/>
       </c>
       <c r="S9" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="62" t="n"/>
@@ -2906,7 +2914,7 @@
         <v/>
       </c>
       <c r="S10" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="75" t="inlineStr">
@@ -3023,7 +3031,7 @@
         <v/>
       </c>
       <c r="S11" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="75" t="inlineStr">
@@ -3144,7 +3152,7 @@
         <v/>
       </c>
       <c r="S12" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="75" t="inlineStr">
@@ -3265,7 +3273,7 @@
         <v/>
       </c>
       <c r="S13" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="75" t="inlineStr">
@@ -3382,7 +3390,7 @@
         <v/>
       </c>
       <c r="S14" s="54">
-        <f>IF(COUNTIF($R$6:$R$39,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="78" t="n"/>
@@ -3501,7 +3509,7 @@
         <v/>
       </c>
       <c r="S15" s="80">
-        <f>IF(COUNTIF($R$6:$R$39,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="81" t="inlineStr">
@@ -3627,7 +3635,7 @@
         <v/>
       </c>
       <c r="S16" s="80">
-        <f>IF(COUNTIF($R$6:$R$39,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="81" t="inlineStr">
@@ -3753,7 +3761,7 @@
         <v/>
       </c>
       <c r="S17" s="80">
-        <f>IF(COUNTIF($R$6:$R$39,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="81" t="inlineStr">
@@ -3875,7 +3883,7 @@
         <v/>
       </c>
       <c r="S18" s="80">
-        <f>IF(COUNTIF($R$6:$R$39,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="81" t="inlineStr">
@@ -4000,7 +4008,7 @@
         <v/>
       </c>
       <c r="S19" s="80">
-        <f>IF(COUNTIF($R$6:$R$39,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="81" t="inlineStr">
@@ -4129,7 +4137,7 @@
         <v/>
       </c>
       <c r="S20" s="50">
-        <f>IF(COUNTIF($R$6:$R$39,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="83" t="inlineStr">
@@ -4252,7 +4260,7 @@
         <v/>
       </c>
       <c r="S21" s="50">
-        <f>IF(COUNTIF($R$6:$R$39,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="83" t="inlineStr">
@@ -4375,7 +4383,7 @@
         <v/>
       </c>
       <c r="S22" s="50">
-        <f>IF(COUNTIF($R$6:$R$39,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="83" t="inlineStr">
@@ -4498,7 +4506,7 @@
         <v/>
       </c>
       <c r="S23" s="50">
-        <f>IF(COUNTIF($R$6:$R$39,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="83" t="inlineStr">
@@ -4621,7 +4629,7 @@
         <v/>
       </c>
       <c r="S24" s="50">
-        <f>IF(COUNTIF($R$6:$R$39,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="83" t="inlineStr">
@@ -4744,7 +4752,7 @@
         <v/>
       </c>
       <c r="S25" s="50">
-        <f>IF(COUNTIF($R$6:$R$39,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="83" t="inlineStr">
@@ -4863,7 +4871,7 @@
         <v/>
       </c>
       <c r="S26" s="80">
-        <f>IF(COUNTIF($R$6:$R$39,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="81" t="inlineStr">
@@ -4982,7 +4990,7 @@
         <v/>
       </c>
       <c r="S27" s="80">
-        <f>IF(COUNTIF($R$6:$R$39,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="81" t="inlineStr">
@@ -5101,7 +5109,7 @@
         <v/>
       </c>
       <c r="S28" s="54">
-        <f>IF(COUNTIF($R$6:$R$39,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="78" t="n"/>
@@ -5110,8 +5118,10 @@
           <t>WorkBuddy</t>
         </is>
       </c>
-      <c r="V28" s="102" t="n">
-        <v>46303</v>
+      <c r="V28" s="102" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W28" s="54" t="inlineStr">
         <is>
@@ -5125,7 +5135,9 @@
       </c>
       <c r="Y28" s="54" t="inlineStr">
         <is>
-          <t>新增身份，非历史已有ID；尺寸经用户批准；静态闭合表现；以asset_contract.json冻结。</t>
+          <t>新增身份，非历史已有ID；尺寸经用户批准；静态闭合表现；以asset_contract.json冻结。
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5228,7 @@
         <v/>
       </c>
       <c r="S29" s="54">
-        <f>IF(COUNTIF($R$6:$R$39,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="78" t="n"/>
@@ -5225,8 +5237,10 @@
           <t>WorkBuddy</t>
         </is>
       </c>
-      <c r="V29" s="102" t="n">
-        <v>46303</v>
+      <c r="V29" s="102" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W29" s="54" t="inlineStr">
         <is>
@@ -5240,7 +5254,9 @@
       </c>
       <c r="Y29" s="54" t="inlineStr">
         <is>
-          <t>新增身份，非历史已有ID；尺寸经用户批准；静态闭合表现；以asset_contract.json冻结。</t>
+          <t>新增身份，非历史已有ID；尺寸经用户批准；静态闭合表现；以asset_contract.json冻结。
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5347,7 @@
         <v/>
       </c>
       <c r="S30" s="54">
-        <f>IF(COUNTIF($R$6:$R$39,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="78" t="n"/>
@@ -5340,8 +5356,10 @@
           <t>WorkBuddy</t>
         </is>
       </c>
-      <c r="V30" s="102" t="n">
-        <v>46303</v>
+      <c r="V30" s="102" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W30" s="54" t="inlineStr">
         <is>
@@ -5355,7 +5373,9 @@
       </c>
       <c r="Y30" s="54" t="inlineStr">
         <is>
-          <t>新增身份，非历史已有ID；尺寸经用户批准；静态闭合表现；以asset_contract.json冻结。</t>
+          <t>新增身份，非历史已有ID；尺寸经用户批准；静态闭合表现；以asset_contract.json冻结。
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5466,7 @@
         <v/>
       </c>
       <c r="S31" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="62" t="inlineStr">
@@ -5459,8 +5479,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V31" s="76" t="n">
-        <v>46309</v>
+      <c r="V31" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W31" s="62" t="inlineStr">
         <is>
@@ -5474,7 +5496,9 @@
       </c>
       <c r="Y31" s="62" t="inlineStr">
         <is>
-          <t>ground=168三角；GLB=assets/art/items_weapons/props/battery_large/components/itm_battery_large_ground_visual_top3d.glb；ground源=art_source/items_weapons/props/battery_large/source/itm_battery_large_ground_source_v001.blend SHA256=63560237834283a742563891778e69b2d634c66c08b47ce7db99bba1313eaa3d；preview源=art_source/items_weapons/props/battery_large/source/itm_battery_large_source_v001.blend SHA256=7157aee1841ef81347a0d5b94a56e380366545b9a3aed0df5470e814eaa7b075；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。；2026-10-14地面显示倍率1.30（最终0.6552），图标倍率不变。</t>
+          <t>ground=168三角；GLB=assets/art/items_weapons/props/battery_large/components/itm_battery_large_ground_visual_top3d.glb；ground源=art_source/items_weapons/props/battery_large/source/itm_battery_large_ground_source_v001.blend SHA256=efc7b895a66cc51fb63ae7d4c6c763844763c83fac9db546487c97093c2d7318；preview源=art_source/items_weapons/props/battery_large/source/itm_battery_large_source_v001.blend SHA256=9a447c854c56256f80c17988c67aa7efdb788bda18e08d606617f0896fd0ae89；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。；2026-10-14地面显示倍率1.30（最终0.6552），图标倍率不变。
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5589,7 @@
         <v/>
       </c>
       <c r="S32" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="62" t="inlineStr">
@@ -5578,8 +5602,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V32" s="76" t="n">
-        <v>46309</v>
+      <c r="V32" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W32" s="62" t="inlineStr">
         <is>
@@ -5593,7 +5619,9 @@
       </c>
       <c r="Y32" s="62" t="inlineStr">
         <is>
-          <t>ground=120三角；GLB=assets/art/items_weapons/props/battery_small/components/itm_battery_small_ground_visual_top3d.glb；ground源=art_source/items_weapons/props/battery_small/source/itm_battery_small_ground_source_v001.blend SHA256=e7d916bff0cf1d2cab60d49595b38d8f22a5cf9f0d033d71b4e3fa053944f762；preview源=art_source/items_weapons/props/battery_small/source/itm_battery_small_source_v001.blend SHA256=85017af7760230fd9dd0b796bdd15ae3c3eb91dc8e5d977eb307ba32676e8a54；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。</t>
+          <t>ground=120三角；GLB=assets/art/items_weapons/props/battery_small/components/itm_battery_small_ground_visual_top3d.glb；ground源=art_source/items_weapons/props/battery_small/source/itm_battery_small_ground_source_v001.blend SHA256=0f150e88b141276f03dec3bb134873104abc261933b36757b6f8ffc993a819cb；preview源=art_source/items_weapons/props/battery_small/source/itm_battery_small_source_v001.blend SHA256=f1deca848220a5cc87c2e416e6554577e26f9bc4bb8610bf30a1382c375b7c57；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5712,7 @@
         <v/>
       </c>
       <c r="S33" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="62" t="inlineStr">
@@ -5697,8 +5725,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V33" s="76" t="n">
-        <v>46309</v>
+      <c r="V33" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W33" s="62" t="inlineStr">
         <is>
@@ -5712,7 +5742,9 @@
       </c>
       <c r="Y33" s="62" t="inlineStr">
         <is>
-          <t>ground=178三角；GLB=assets/art/items_weapons/props/health_potion/components/itm_health_potion_ground_visual_top3d.glb；ground源=art_source/items_weapons/props/health_potion/source/itm_health_potion_ground_source_v001.blend SHA256=509273cbee4ddeef75c0f51dba3e224ed93fb0e66f52970e97ec5e23dd6647f0；preview源=art_source/items_weapons/props/health_potion/source/itm_health_potion_source_v001.blend SHA256=6d1d848e4cc37d91fc99d0609db46763ef916458e2a418aa621befb07781d5bb；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。；2026-10-14地面显示倍率1.30（最终0.6552），图标倍率不变。</t>
+          <t>ground=178三角；GLB=assets/art/items_weapons/props/health_potion/components/itm_health_potion_ground_visual_top3d.glb；ground源=art_source/items_weapons/props/health_potion/source/itm_health_potion_ground_source_v001.blend SHA256=c3c86cb592914900b0cc438f4f51f1bd4a0a26b6ce8b43e39e002bdb8f2f10d0；preview源=art_source/items_weapons/props/health_potion/source/itm_health_potion_source_v001.blend SHA256=50a9270b073741e47e35576d2ba3425b66a7d28e151ecf232f54187222a3a26c；源不变；资源已导入且地面入口已接线，运行/视觉验收未执行，未签署正式可用。；2026-10-14地面显示倍率1.30（最终0.6552），图标倍率不变。
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5835,7 @@
         <v/>
       </c>
       <c r="S34" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="62" t="inlineStr">
@@ -5816,8 +5848,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V34" s="76" t="n">
-        <v>46309</v>
+      <c r="V34" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W34" s="62" t="inlineStr">
         <is>
@@ -5831,7 +5865,9 @@
       </c>
       <c r="Y34" s="62" t="inlineStr">
         <is>
-          <t>通用弹药：黄色弹壳；地面/图标共用；preview源SHA256=a1302b8182d523834dc0af9741eb687044489f66cafa0cfbcbf79d1de1d565d3；ground源SHA256=3d7baf9637ba5bc14982366f0663af93102512c4c04335b77104983208c3f88c；原尺寸与176三角预算保持。</t>
+          <t>通用弹药：黄色弹壳；地面/图标共用；preview源SHA256=b58b2ad7b01a17ecaf3826f49d25f485586ff169561765d228d907080d5592fa；ground源SHA256=24491f12357220830731fcb5d1b0582a4f2672912a2036548dd48b430512a6cb；原尺寸与176三角预算保持。
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5958,7 @@
         <v/>
       </c>
       <c r="S35" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R35)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R35)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T35" s="62" t="inlineStr">
@@ -5935,8 +5971,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V35" s="76" t="n">
-        <v>46309</v>
+      <c r="V35" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W35" s="62" t="inlineStr">
         <is>
@@ -5950,7 +5988,9 @@
       </c>
       <c r="Y35" s="62" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/props/cell_pack/source/itm_cell_pack_source_v001.blend；地面源=art_source/items_weapons/props/cell_pack/source/itm_cell_pack_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/props/cell_pack/source/itm_cell_pack_source_v001.blend；地面源=art_source/items_weapons/props/cell_pack/source/itm_cell_pack_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -6041,7 +6081,7 @@
         <v/>
       </c>
       <c r="S36" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R36)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R36)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T36" s="62" t="inlineStr">
@@ -6054,8 +6094,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V36" s="76" t="n">
-        <v>46309</v>
+      <c r="V36" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W36" s="62" t="inlineStr">
         <is>
@@ -6069,7 +6111,9 @@
       </c>
       <c r="Y36" s="62" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/props/flashlight_basic/source/itm_flashlight_basic_source_v001.blend；地面源=art_source/items_weapons/props/flashlight_basic/source/itm_flashlight_basic_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/props/flashlight_basic/source/itm_flashlight_basic_source_v001.blend；地面源=art_source/items_weapons/props/flashlight_basic/source/itm_flashlight_basic_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6204,7 @@
         <v/>
       </c>
       <c r="S37" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R37)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R37)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T37" s="62" t="inlineStr">
@@ -6173,8 +6217,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V37" s="76" t="n">
-        <v>46309</v>
+      <c r="V37" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W37" s="62" t="inlineStr">
         <is>
@@ -6188,7 +6234,9 @@
       </c>
       <c r="Y37" s="62" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/props/flashlight_advanced/source/itm_flashlight_advanced_source_v001.blend；地面源=art_source/items_weapons/props/flashlight_advanced/source/itm_flashlight_advanced_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/props/flashlight_advanced/source/itm_flashlight_advanced_source_v001.blend；地面源=art_source/items_weapons/props/flashlight_advanced/source/itm_flashlight_advanced_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6327,7 @@
         <v/>
       </c>
       <c r="S38" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R38)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R38)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T38" s="62" t="inlineStr">
@@ -6292,8 +6340,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V38" s="76" t="n">
-        <v>46309</v>
+      <c r="V38" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W38" s="62" t="inlineStr">
         <is>
@@ -6307,7 +6357,9 @@
       </c>
       <c r="Y38" s="62" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/props/flashlight_efficient/source/itm_flashlight_efficient_source_v001.blend；地面源=art_source/items_weapons/props/flashlight_efficient/source/itm_flashlight_efficient_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/props/flashlight_efficient/source/itm_flashlight_efficient_source_v001.blend；地面源=art_source/items_weapons/props/flashlight_efficient/source/itm_flashlight_efficient_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6450,7 @@
         <v/>
       </c>
       <c r="S39" s="62">
-        <f>IF(COUNTIF($R$6:$R$39,R39)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$44,R39)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T39" s="62" t="inlineStr">
@@ -6411,8 +6463,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V39" s="76" t="n">
-        <v>46309</v>
+      <c r="V39" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W39" s="62" t="inlineStr">
         <is>
@@ -6426,7 +6480,594 @@
       </c>
       <c r="Y39" s="62" t="inlineStr">
         <is>
-          <t>高精度源=art_source/items_weapons/props/blueprint_scroll/source/itm_blueprint_scroll_source_v001.blend；地面源=art_source/items_weapons/props/blueprint_scroll/source/itm_blueprint_scroll_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D</t>
+          <t>高精度源=art_source/items_weapons/props/blueprint_scroll/source/itm_blueprint_scroll_source_v001.blend；地面源=art_source/items_weapons/props/blueprint_scroll/source/itm_blueprint_scroll_ground_source_v001.blend；清单包含两角色哈希与派生关系；Godot实际工厂/图标/28内容映射通过；拾取碰撞归GroundLootPickup3D
+【2026-10-15物品色板】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V×1.40封顶1；高低/优化源同步；场景原色板不变；运行材质及图标验收通过。
+【2026-10-15独立四材质】assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；HSV S/V=原场景×1.40×1.15=1.61封顶1；四个道具专用材质；图标本色补光0.45；高低/优化源同步；场景原材质不变；运行及图标验收通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="75" t="inlineStr">
+        <is>
+          <t>ITM-PALETTE-ITEM-HIGH-VISIBILITY</t>
+        </is>
+      </c>
+      <c r="B40" s="62" t="inlineStr">
+        <is>
+          <t>物品专用高亮高饱和色板</t>
+        </is>
+      </c>
+      <c r="C40" s="62" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D40" s="75" t="inlineStr">
+        <is>
+          <t>palette</t>
+        </is>
+      </c>
+      <c r="E40" s="75" t="inlineStr">
+        <is>
+          <t>item_high_visibility_palette</t>
+        </is>
+      </c>
+      <c r="F40" s="75" t="inlineStr">
+        <is>
+          <t>texture</t>
+        </is>
+      </c>
+      <c r="G40" s="62" t="inlineStr"/>
+      <c r="H40" s="62" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="I40" s="75" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J40" s="62" t="inlineStr">
+        <is>
+          <t>31物品资产/地面/图标/预览/背包</t>
+        </is>
+      </c>
+      <c r="K40" s="62" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L40" s="75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M40" s="75" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N40" s="62" t="inlineStr">
+        <is>
+          <t>512×512 RGBA；10×10；sRGB HSV S/V各×1.61（1.40后再增15%）并封顶；H/Alpha不变</t>
+        </is>
+      </c>
+      <c r="O40" s="62" t="inlineStr">
+        <is>
+          <t>assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
+        </is>
+      </c>
+      <c r="P40" s="75" t="inlineStr">
+        <is>
+          <t>art_source/shared/palette/item_palette_recipe_v001.json; tools/asset_pipeline/item_shared_palette_post_import.gd</t>
+        </is>
+      </c>
+      <c r="Q40" s="62" t="inlineStr">
+        <is>
+          <t>物品;色板;高亮;高饱和;palette</t>
+        </is>
+      </c>
+      <c r="R40" s="62">
+        <f>LOWER(TRIM(C40)&amp;"|"&amp;TRIM(D40)&amp;"|"&amp;TRIM(E40)&amp;"|"&amp;TRIM(F40)&amp;"|"&amp;TRIM(H40)&amp;"|"&amp;TRIM(I40))</f>
+        <v/>
+      </c>
+      <c r="S40" s="62">
+        <f>IF(COUNTIF($R$6:$R$44,R40)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T40" s="62" t="inlineStr">
+        <is>
+          <t>8da13f6d4da6701b983aa88cfd0e839a8178ab5c51a8f169fc8a4638308cb1c7</t>
+        </is>
+      </c>
+      <c r="U40" s="62" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V40" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="W40" s="62" t="inlineStr">
+        <is>
+          <t>从项目场景色板按用户要求确定性派生</t>
+        </is>
+      </c>
+      <c r="X40" s="77" t="inlineStr"/>
+      <c r="Y40" s="62" t="inlineStr">
+        <is>
+          <t>只登记贴图资产，不登记虚假Prefab。配方与生成器可重建，Nearest/无mipmap/无损压缩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="75" t="inlineStr">
+        <is>
+          <t>ITM-MATERIAL-METAL</t>
+        </is>
+      </c>
+      <c r="B41" s="62" t="inlineStr">
+        <is>
+          <t>01_精工金属_道具骨架</t>
+        </is>
+      </c>
+      <c r="C41" s="62" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D41" s="75" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E41" s="75" t="inlineStr">
+        <is>
+          <t>item_material_1</t>
+        </is>
+      </c>
+      <c r="F41" s="75" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="G41" s="62" t="inlineStr"/>
+      <c r="H41" s="62" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="I41" s="75" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J41" s="62" t="inlineStr">
+        <is>
+          <t>31物品资产；世界与预览；图标派生实例</t>
+        </is>
+      </c>
+      <c r="K41" s="62" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L41" s="75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M41" s="75" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N41" s="62" t="inlineStr">
+        <is>
+          <t>四角色独立资源；物品专用色板；图标补光能量下限0.45</t>
+        </is>
+      </c>
+      <c r="O41" s="62" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/shared/materials/itm_metal.tres</t>
+        </is>
+      </c>
+      <c r="P41" s="75" t="inlineStr">
+        <is>
+          <t>tools/asset_pipeline/item_shared_palette_post_import.gd; src/ui/ItemIconMaterialPreset.gd</t>
+        </is>
+      </c>
+      <c r="Q41" s="62" t="inlineStr">
+        <is>
+          <t>物品;独立材质;图标;补光</t>
+        </is>
+      </c>
+      <c r="R41" s="62">
+        <f>LOWER(TRIM(C41)&amp;"|"&amp;TRIM(D41)&amp;"|"&amp;TRIM(E41)&amp;"|"&amp;TRIM(F41)&amp;"|"&amp;TRIM(H41)&amp;"|"&amp;TRIM(I41))</f>
+        <v/>
+      </c>
+      <c r="S41" s="62">
+        <f>IF(COUNTIF($R$6:$R$44,R41)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T41" s="62" t="inlineStr">
+        <is>
+          <t>39ad69667b6ad5f6c77a55e34a8e008a389d62699db65bde95ce098d942263b1</t>
+        </is>
+      </c>
+      <c r="U41" s="62" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V41" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="W41" s="62" t="inlineStr">
+        <is>
+          <t>项目原创材质参数</t>
+        </is>
+      </c>
+      <c r="X41" s="77" t="inlineStr"/>
+      <c r="Y41" s="62" t="inlineStr">
+        <is>
+          <t>不引用场景材质；图标使用surface override副本，不修改世界材质或新增角色。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="75" t="inlineStr">
+        <is>
+          <t>ITM-MATERIAL-MATTE</t>
+        </is>
+      </c>
+      <c r="B42" s="62" t="inlineStr">
+        <is>
+          <t>02_细腻哑光_道具大面</t>
+        </is>
+      </c>
+      <c r="C42" s="62" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D42" s="75" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E42" s="75" t="inlineStr">
+        <is>
+          <t>item_material_2</t>
+        </is>
+      </c>
+      <c r="F42" s="75" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="G42" s="62" t="inlineStr"/>
+      <c r="H42" s="62" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="I42" s="75" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J42" s="62" t="inlineStr">
+        <is>
+          <t>31物品资产；世界与预览；图标派生实例</t>
+        </is>
+      </c>
+      <c r="K42" s="62" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L42" s="75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M42" s="75" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N42" s="62" t="inlineStr">
+        <is>
+          <t>四角色独立资源；物品专用色板；图标补光能量下限0.45</t>
+        </is>
+      </c>
+      <c r="O42" s="62" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/shared/materials/itm_matte.tres</t>
+        </is>
+      </c>
+      <c r="P42" s="75" t="inlineStr">
+        <is>
+          <t>tools/asset_pipeline/item_shared_palette_post_import.gd; src/ui/ItemIconMaterialPreset.gd</t>
+        </is>
+      </c>
+      <c r="Q42" s="62" t="inlineStr">
+        <is>
+          <t>物品;独立材质;图标;补光</t>
+        </is>
+      </c>
+      <c r="R42" s="62">
+        <f>LOWER(TRIM(C42)&amp;"|"&amp;TRIM(D42)&amp;"|"&amp;TRIM(E42)&amp;"|"&amp;TRIM(F42)&amp;"|"&amp;TRIM(H42)&amp;"|"&amp;TRIM(I42))</f>
+        <v/>
+      </c>
+      <c r="S42" s="62">
+        <f>IF(COUNTIF($R$6:$R$44,R42)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T42" s="62" t="inlineStr">
+        <is>
+          <t>983267f78b26e7d588be7d1c0ce5472e2b133c4f4d8456547db759610bff2ae0</t>
+        </is>
+      </c>
+      <c r="U42" s="62" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V42" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="W42" s="62" t="inlineStr">
+        <is>
+          <t>项目原创材质参数</t>
+        </is>
+      </c>
+      <c r="X42" s="77" t="inlineStr"/>
+      <c r="Y42" s="62" t="inlineStr">
+        <is>
+          <t>不引用场景材质；图标使用surface override副本，不修改世界材质或新增角色。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="75" t="inlineStr">
+        <is>
+          <t>ITM-MATERIAL-CLEARCOAT</t>
+        </is>
+      </c>
+      <c r="B43" s="62" t="inlineStr">
+        <is>
+          <t>03_清漆反光_道具点缀</t>
+        </is>
+      </c>
+      <c r="C43" s="62" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D43" s="75" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E43" s="75" t="inlineStr">
+        <is>
+          <t>item_material_3</t>
+        </is>
+      </c>
+      <c r="F43" s="75" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="G43" s="62" t="inlineStr"/>
+      <c r="H43" s="62" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="I43" s="75" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J43" s="62" t="inlineStr">
+        <is>
+          <t>31物品资产；世界与预览；图标派生实例</t>
+        </is>
+      </c>
+      <c r="K43" s="62" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L43" s="75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M43" s="75" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N43" s="62" t="inlineStr">
+        <is>
+          <t>四角色独立资源；物品专用色板；图标补光能量下限0.45</t>
+        </is>
+      </c>
+      <c r="O43" s="62" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/shared/materials/itm_clearcoat.tres</t>
+        </is>
+      </c>
+      <c r="P43" s="75" t="inlineStr">
+        <is>
+          <t>tools/asset_pipeline/item_shared_palette_post_import.gd; src/ui/ItemIconMaterialPreset.gd</t>
+        </is>
+      </c>
+      <c r="Q43" s="62" t="inlineStr">
+        <is>
+          <t>物品;独立材质;图标;补光</t>
+        </is>
+      </c>
+      <c r="R43" s="62">
+        <f>LOWER(TRIM(C43)&amp;"|"&amp;TRIM(D43)&amp;"|"&amp;TRIM(E43)&amp;"|"&amp;TRIM(F43)&amp;"|"&amp;TRIM(H43)&amp;"|"&amp;TRIM(I43))</f>
+        <v/>
+      </c>
+      <c r="S43" s="62">
+        <f>IF(COUNTIF($R$6:$R$44,R43)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T43" s="62" t="inlineStr">
+        <is>
+          <t>66f20bd26768ccf5be5a3ad6789437be64030c3a97541f9a5533e0c1fdc64257</t>
+        </is>
+      </c>
+      <c r="U43" s="62" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V43" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="W43" s="62" t="inlineStr">
+        <is>
+          <t>项目原创材质参数</t>
+        </is>
+      </c>
+      <c r="X43" s="77" t="inlineStr"/>
+      <c r="Y43" s="62" t="inlineStr">
+        <is>
+          <t>不引用场景材质；图标使用surface override副本，不修改世界材质或新增角色。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="75" t="inlineStr">
+        <is>
+          <t>ITM-MATERIAL-EMISSIVE</t>
+        </is>
+      </c>
+      <c r="B44" s="62" t="inlineStr">
+        <is>
+          <t>04_柔和自发光_道具UI</t>
+        </is>
+      </c>
+      <c r="C44" s="62" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="D44" s="75" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E44" s="75" t="inlineStr">
+        <is>
+          <t>item_material_4</t>
+        </is>
+      </c>
+      <c r="F44" s="75" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="G44" s="62" t="inlineStr"/>
+      <c r="H44" s="62" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="I44" s="75" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J44" s="62" t="inlineStr">
+        <is>
+          <t>31物品资产；世界与预览；图标派生实例</t>
+        </is>
+      </c>
+      <c r="K44" s="62" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L44" s="75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M44" s="75" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N44" s="62" t="inlineStr">
+        <is>
+          <t>四角色独立资源；物品专用色板；图标补光能量下限0.45</t>
+        </is>
+      </c>
+      <c r="O44" s="62" t="inlineStr">
+        <is>
+          <t>assets/art/items_weapons/shared/materials/itm_emissive.tres</t>
+        </is>
+      </c>
+      <c r="P44" s="75" t="inlineStr">
+        <is>
+          <t>tools/asset_pipeline/item_shared_palette_post_import.gd; src/ui/ItemIconMaterialPreset.gd</t>
+        </is>
+      </c>
+      <c r="Q44" s="62" t="inlineStr">
+        <is>
+          <t>物品;独立材质;图标;补光</t>
+        </is>
+      </c>
+      <c r="R44" s="62">
+        <f>LOWER(TRIM(C44)&amp;"|"&amp;TRIM(D44)&amp;"|"&amp;TRIM(E44)&amp;"|"&amp;TRIM(F44)&amp;"|"&amp;TRIM(H44)&amp;"|"&amp;TRIM(I44))</f>
+        <v/>
+      </c>
+      <c r="S44" s="62">
+        <f>IF(COUNTIF($R$6:$R$44,R44)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T44" s="62" t="inlineStr">
+        <is>
+          <t>a443ac309186802e83b2554a4247a13ae75961c78259423a44c0aaaef52ab53b</t>
+        </is>
+      </c>
+      <c r="U44" s="62" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V44" s="76" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="W44" s="62" t="inlineStr">
+        <is>
+          <t>项目原创材质参数</t>
+        </is>
+      </c>
+      <c r="X44" s="77" t="inlineStr"/>
+      <c r="Y44" s="62" t="inlineStr">
+        <is>
+          <t>不引用场景材质；图标使用surface override副本，不修改世界材质或新增角色。</t>
         </is>
       </c>
     </row>
@@ -6638,7 +7279,7 @@
     <row r="427" ht="84.75" customHeight="1" s="51"/>
     <row r="429" ht="120" customHeight="1" s="51"/>
   </sheetData>
-  <autoFilter ref="A5:Y39"/>
+  <autoFilter ref="A5:Y44"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
@@ -6657,15 +7298,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K6:K39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L6:L39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7341,7 +7982,7 @@
       </c>
       <c r="P5" s="89" t="inlineStr">
         <is>
-          <t>真实PackedScene骨架已创建；视觉制作及验收待完成；禁止视为正式资产。</t>
+          <t>真实PackedScene骨架已创建；视觉制作及验收待完成；禁止视为正式资产。；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -7423,7 +8064,7 @@
       </c>
       <c r="P6" s="89" t="inlineStr">
         <is>
-          <t>真实PackedScene骨架已创建；视觉制作及验收待完成；禁止视为正式资产。</t>
+          <t>真实PackedScene骨架已创建；视觉制作及验收待完成；禁止视为正式资产。；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -7505,7 +8146,7 @@
       </c>
       <c r="P7" s="89" t="inlineStr">
         <is>
-          <t>真实PackedScene骨架已创建；视觉制作及验收待完成；禁止视为正式资产。</t>
+          <t>真实PackedScene骨架已创建；视觉制作及验收待完成；禁止视为正式资产。；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -7587,7 +8228,7 @@
       </c>
       <c r="P8" s="89" t="inlineStr">
         <is>
-          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收；地面倍率1.30，最终0.6552</t>
+          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收；地面倍率1.30，最终0.6552；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -7669,7 +8310,7 @@
       </c>
       <c r="P9" s="89" t="inlineStr">
         <is>
-          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收</t>
+          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -7751,7 +8392,7 @@
       </c>
       <c r="P10" s="89" t="inlineStr">
         <is>
-          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收；地面倍率1.30，最终0.6552</t>
+          <t>源保持；公共场景色盘；资源导入完成，未执行运行/视觉验收；地面倍率1.30，最终0.6552；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -7833,7 +8474,7 @@
       </c>
       <c r="P11" s="50" t="inlineStr">
         <is>
-          <t>黄色弹壳；地面与图标共享；45度倾斜</t>
+          <t>黄色弹壳；地面与图标共享；45度倾斜；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -7915,7 +8556,7 @@
       </c>
       <c r="P12" s="89" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -7997,7 +8638,7 @@
       </c>
       <c r="P13" s="89" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8720,7 @@
       </c>
       <c r="P14" s="89" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -8161,7 +8802,7 @@
       </c>
       <c r="P15" s="89" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8884,7 @@
       </c>
       <c r="P16" s="89" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -8325,7 +8966,7 @@
       </c>
       <c r="P17" s="89" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -8407,7 +9048,7 @@
       </c>
       <c r="P18" s="89" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -8489,7 +9130,7 @@
       </c>
       <c r="P19" s="89" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -8571,7 +9212,7 @@
       </c>
       <c r="P20" s="89" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -8653,7 +9294,7 @@
       </c>
       <c r="P21" s="89" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -8735,7 +9376,7 @@
       </c>
       <c r="P22" s="89" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -8817,7 +9458,7 @@
       </c>
       <c r="P23" s="89" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -8899,7 +9540,7 @@
       </c>
       <c r="P24" s="89" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -8981,7 +9622,7 @@
       </c>
       <c r="P25" s="89" t="inlineStr">
         <is>
-          <t>公共材质/外链色盘；source_manifest记录哈希和双角色</t>
+          <t>公共材质/外链色盘；source_manifest记录哈希和双角色；物品专用色板S/V×1.40，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png；当前物品独立四材质、S/V×1.61，assets/art/shared/palette/item_high_visibility_palette_10x10_512.png</t>
         </is>
       </c>
     </row>
@@ -9017,7 +9658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="50" min="1" max="1"/>
@@ -9926,6 +10567,80 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="50" t="inlineStr">
+        <is>
+          <t>v0.1.104</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C29" s="50" t="inlineStr">
+        <is>
+          <t>物品专用色板与母版材质绑定</t>
+        </is>
+      </c>
+      <c r="D29" s="50" t="inlineStr">
+        <is>
+          <t>HSV S/V×1.40；31资产；51GLB；64Blender</t>
+        </is>
+      </c>
+      <c r="E29" s="50" t="inlineStr">
+        <is>
+          <t>运行底色/发光/图标通过，几何UV不变</t>
+        </is>
+      </c>
+      <c r="F29" s="50" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G29" s="50" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="50" t="inlineStr">
+        <is>
+          <t>v0.1.105</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C30" s="50" t="inlineStr">
+        <is>
+          <t>物品独立四材质与图标补光</t>
+        </is>
+      </c>
+      <c r="D30" s="50" t="inlineStr">
+        <is>
+          <t>HSV S/V×1.61；31资产；51GLB；64Blender；四个独立材质</t>
+        </is>
+      </c>
+      <c r="E30" s="50" t="inlineStr">
+        <is>
+          <t>同灯光开关补光对比通过，世界材质无污染</t>
+        </is>
+      </c>
+      <c r="F30" s="50" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G30" s="50" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3D-道具" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3D-物品" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="域变更日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$44</definedName>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="T10" s="75" t="inlineStr">
         <is>
-          <t>1f5953cef11cc376d18ecc875a4a88eae6ce3dff05eba2f5479cb006926fb928</t>
+          <t>09c6a30399f2c9d1d3e590e45afdc72fbf4e29964c5e9aa24955ea00c83a9385</t>
         </is>
       </c>
       <c r="U10" s="75" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T11" s="75" t="inlineStr">
         <is>
-          <t>14eca357cf5198a232d95231ccbf07e15b67a1428f7d27bf2f32222e59bcb29d</t>
+          <t>5428665bda1fbd0e7422aa63f2d7cf0b0de4efeb0c1198d4b38774ad5fa19865</t>
         </is>
       </c>
       <c r="U11" s="75" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="T12" s="75" t="inlineStr">
         <is>
-          <t>e796114d2ad04dddd182e255cc2aad7bbf531e2876a70d65be787e987c7b21b3</t>
+          <t>76a9d3f86a09217bc8239b4f23b9fc31536b21fdddd591146ea23f5756342e31</t>
         </is>
       </c>
       <c r="U12" s="75" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="T13" s="75" t="inlineStr">
         <is>
-          <t>64d21d1a04609556593e9a4da3849890298c48337b0ab29c16c138c8120f62e5</t>
+          <t>14c8655ddfc72ebdb5cefae6ddba69e11a0f1257c8518e872c3da9487cc55088</t>
         </is>
       </c>
       <c r="U13" s="75" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="T15" s="81" t="inlineStr">
         <is>
-          <t>1d6e87ee00e7b89c4320fd21ac94831bbb6d6011940e4074311026e72edc3d20</t>
+          <t>8342ab250af1ae90bb814e65a387dc68d2a3d80c13822de340f85937f4f8d206</t>
         </is>
       </c>
       <c r="U15" s="81" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="T16" s="81" t="inlineStr">
         <is>
-          <t>ab8d7b376a484ff1824ad12cc6e43b8d2af89fee96a71599e82c4214ddc9e639</t>
+          <t>0d2ce48ce4b57803d3472922a18d73f081be6a3cce9ee821925ad940f5629302</t>
         </is>
       </c>
       <c r="U16" s="81" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="T17" s="81" t="inlineStr">
         <is>
-          <t>10c47d81afa2a642754e2f633ee77bbcae8a96b92b2aa7e29da430bd8be97d73</t>
+          <t>9a84d1c126ede8504368ee921ee938cdc934e5d0fed0d046957538213fd7cc34</t>
         </is>
       </c>
       <c r="U17" s="81" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="T18" s="81" t="inlineStr">
         <is>
-          <t>d55127e32bc890f4ecf4073f052dc8744e237cd4b62e77f672770ae114d4b6f2</t>
+          <t>a87d39ebd9d249352cdb6880a58506ce19053babfca3820762df39eef88f1754</t>
         </is>
       </c>
       <c r="U18" s="81" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="T19" s="81" t="inlineStr">
         <is>
-          <t>5dfc2145158d6e06ab80d592d868e4d0e9b5020fbecd16413473cf5109d7aa67</t>
+          <t>01911c01114eb620f97d485ffeff39387b6db1fe1efd0445f789ce73149601f0</t>
         </is>
       </c>
       <c r="U19" s="81" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="T20" s="83" t="inlineStr">
         <is>
-          <t>f1b63a344c49d28c6a5a0a1a5e438c472aaccd36e984d4b44aab002d75c4e3ac</t>
+          <t>ad28a3708d425765846879bb19ac957368c05654dc67c8c768bb0b1442d2075f</t>
         </is>
       </c>
       <c r="U20" s="83" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="T21" s="83" t="inlineStr">
         <is>
-          <t>77cce4279a46a2ca32984cec8f9a232d3d50ff00198a5aaa9484e82fc9933e5d</t>
+          <t>a8a3dfd8c35cd864cee5145be9e07c1234e9eac617be08fb566ba6d8589d1d5b</t>
         </is>
       </c>
       <c r="U21" s="83" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="T22" s="83" t="inlineStr">
         <is>
-          <t>54d8b92ae5e448613fd9f9971cd56a1fe26deb76fdfae70a9e2adcdfbefc2f02</t>
+          <t>273c47338a3dcdf9ef7630a052662e5b5fc674c9b8b1d2e1190222dcb59261ca</t>
         </is>
       </c>
       <c r="U22" s="83" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="T23" s="83" t="inlineStr">
         <is>
-          <t>3ae4028754d49b8790f7852121f7f12fcbafaa84e3eee4a9a35994cf6ace2d07</t>
+          <t>c734ad7d05d41ff0135862266393e9360a125ed3c8736b181441ea36a9b0e715</t>
         </is>
       </c>
       <c r="U23" s="83" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="T24" s="83" t="inlineStr">
         <is>
-          <t>e30407ccfc3b4e5d48a1236d388ca91ba1862458b43c206a84d3c861e8e6b6c8</t>
+          <t>3b64fcb6841718b1eb44b72b5a09e3a71b737b3eed8610573d71d8ae8167d03a</t>
         </is>
       </c>
       <c r="U24" s="83" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="T25" s="83" t="inlineStr">
         <is>
-          <t>6ccb6a810717b40f8f1de56e3de87fdcebebc66ae4c187d4ff30e909eed5afd7</t>
+          <t>13c728e68826704dc6c0e41345c14ed0a105763ee1486a9c779a758176086245</t>
         </is>
       </c>
       <c r="U25" s="83" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="T27" s="81" t="inlineStr">
         <is>
-          <t>0f60c1333330feaaef984b64539c73d284fd13fd3b89cd3df5497394c85442ca</t>
+          <t>857a75adbd1272605e44e571891ada187ec31048c49bd218206093304a894228</t>
         </is>
       </c>
       <c r="U27" s="81" t="inlineStr">
@@ -7821,7 +7821,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="51">
       <c r="A4" s="86" t="inlineStr">
         <is>
